--- a/Data/FlightPlan/FPL_09OCT26.xlsx
+++ b/Data/FlightPlan/FPL_09OCT26.xlsx
@@ -137,756 +137,759 @@
     <t>VN-A203</t>
   </si>
   <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A204</t>
+  </si>
+  <si>
+    <t>XFW</t>
+  </si>
+  <si>
+    <t>NQZ</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>HAN</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>10/10/26</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
     <t>CGK</t>
   </si>
   <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A204</t>
-  </si>
-  <si>
-    <t>XFW</t>
-  </si>
-  <si>
-    <t>NQZ</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>HAN</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>10/10/26</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
     <t>22:15</t>
   </si>
   <si>
@@ -950,9 +953,6 @@
     <t>VN-A650</t>
   </si>
   <si>
-    <t>08:35</t>
-  </si>
-  <si>
     <t>17:55</t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>Total Record(s): 345</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 00:52</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 02:34</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c t="s" r="C18" s="7">
         <v>14</v>
@@ -2113,7 +2113,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="7">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c t="s" r="C19" s="7">
         <v>14</v>
@@ -2918,7 +2918,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2948,10 +2948,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I47" s="7">
+        <v>107</v>
+      </c>
+      <c t="s" r="J47" s="7">
         <v>108</v>
-      </c>
-      <c t="s" r="J47" s="7">
-        <v>109</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3014,10 +3014,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
+        <v>109</v>
+      </c>
+      <c t="s" r="J49" s="7">
         <v>110</v>
-      </c>
-      <c t="s" r="J49" s="7">
-        <v>111</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3062,10 +3062,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3095,7 +3095,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c t="s" r="J52" s="7">
         <v>102</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3125,13 +3125,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H53" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="I53" s="7">
+        <v>115</v>
+      </c>
+      <c t="s" r="J53" s="7">
         <v>116</v>
-      </c>
-      <c t="s" r="I53" s="7">
-        <v>117</v>
-      </c>
-      <c t="s" r="J53" s="7">
-        <v>118</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3149,13 +3149,13 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>17</v>
@@ -3164,7 +3164,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3197,7 +3197,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3227,10 +3227,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3263,22 +3263,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
+        <v>121</v>
+      </c>
+      <c r="F58" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G58" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H58" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I58" s="7">
+        <v>122</v>
+      </c>
+      <c t="s" r="J58" s="7">
         <v>123</v>
-      </c>
-      <c r="F58" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G58" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H58" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I58" s="7">
-        <v>124</v>
-      </c>
-      <c t="s" r="J58" s="7">
-        <v>125</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3308,10 +3308,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3338,13 +3338,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H60" s="8">
+        <v>126</v>
+      </c>
+      <c t="s" r="I60" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="J60" s="7">
         <v>128</v>
-      </c>
-      <c t="s" r="I60" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="J60" s="7">
-        <v>130</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3362,19 +3362,19 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>89</v>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3404,13 +3404,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3428,19 +3428,19 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>38</v>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3488,10 +3488,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3521,10 +3521,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3551,13 +3551,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H67" s="8">
+        <v>137</v>
+      </c>
+      <c t="s" r="I67" s="7">
+        <v>138</v>
+      </c>
+      <c t="s" r="J67" s="7">
         <v>139</v>
-      </c>
-      <c t="s" r="I67" s="7">
-        <v>140</v>
-      </c>
-      <c t="s" r="J67" s="7">
-        <v>141</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3575,19 +3575,19 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>97</v>
@@ -3623,22 +3623,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
+        <v>141</v>
+      </c>
+      <c r="F70" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G70" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H70" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I70" s="7">
+        <v>142</v>
+      </c>
+      <c t="s" r="J70" s="7">
         <v>143</v>
-      </c>
-      <c r="F70" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G70" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H70" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I70" s="7">
-        <v>144</v>
-      </c>
-      <c t="s" r="J70" s="7">
-        <v>145</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3668,10 +3668,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3701,10 +3701,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3731,10 +3731,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H73" s="8">
+        <v>147</v>
+      </c>
+      <c t="s" r="I73" s="7">
         <v>148</v>
-      </c>
-      <c t="s" r="I73" s="7">
-        <v>149</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>35</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3803,13 +3803,13 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
+        <v>150</v>
+      </c>
+      <c r="F76" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G76" s="8">
         <v>151</v>
-      </c>
-      <c r="F76" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G76" s="8">
-        <v>152</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>60</v>
@@ -3818,7 +3818,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3848,10 +3848,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I77" s="7">
+        <v>153</v>
+      </c>
+      <c t="s" r="J77" s="7">
         <v>154</v>
-      </c>
-      <c t="s" r="J77" s="7">
-        <v>155</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3881,10 +3881,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I78" s="7">
+        <v>155</v>
+      </c>
+      <c t="s" r="J78" s="7">
         <v>156</v>
-      </c>
-      <c t="s" r="J78" s="7">
-        <v>157</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3911,13 +3911,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="I79" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3935,22 +3935,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -3995,10 +3995,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4028,10 +4028,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I83" s="7">
+        <v>162</v>
+      </c>
+      <c t="s" r="J83" s="7">
         <v>163</v>
-      </c>
-      <c t="s" r="J83" s="7">
-        <v>164</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4058,13 +4058,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H84" s="8">
+        <v>164</v>
+      </c>
+      <c t="s" r="I84" s="7">
         <v>165</v>
       </c>
-      <c t="s" r="I84" s="7">
+      <c t="s" r="J84" s="7">
         <v>166</v>
-      </c>
-      <c t="s" r="J84" s="7">
-        <v>167</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4082,22 +4082,22 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I85" s="7">
+        <v>167</v>
+      </c>
+      <c t="s" r="J85" s="7">
         <v>168</v>
-      </c>
-      <c t="s" r="J85" s="7">
-        <v>169</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4127,7 +4127,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>25</v>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4175,17 +4175,17 @@
         <v>20</v>
       </c>
       <c t="s" r="I88" s="7">
+        <v>171</v>
+      </c>
+      <c t="s" r="J88" s="7">
         <v>172</v>
       </c>
-      <c t="s" r="J88" s="7">
+      <c t="s" r="K88" s="7">
         <v>173</v>
-      </c>
-      <c t="s" r="K88" s="7">
-        <v>174</v>
       </c>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>65</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4245,10 +4245,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4278,7 +4278,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>177</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4389,7 +4389,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I95" s="7">
         <v>183</v>
@@ -4419,7 +4419,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>17</v>
@@ -4428,7 +4428,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4734,14 +4734,18 @@
         <v>86</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>137</v>
-      </c>
-      <c r="K107" s="7"/>
+        <v>135</v>
+      </c>
+      <c t="s" r="K107" s="7">
+        <v>134</v>
+      </c>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
@@ -4770,7 +4774,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4797,13 +4801,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4827,16 +4831,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4869,7 +4873,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4878,13 +4882,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4902,13 +4906,13 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>17</v>
@@ -4935,7 +4939,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4947,10 +4951,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4968,7 +4972,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -4980,7 +4984,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>98</v>
@@ -5016,7 +5020,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5049,7 +5053,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5058,13 +5062,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5082,22 +5086,22 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I119" s="7">
+        <v>46</v>
+      </c>
+      <c t="s" r="J119" s="7">
         <v>209</v>
-      </c>
-      <c t="s" r="J119" s="7">
-        <v>210</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5115,7 +5119,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5127,10 +5131,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5148,7 +5152,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5163,7 +5167,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5196,22 +5200,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
+        <v>212</v>
+      </c>
+      <c r="F123" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G123" s="8">
         <v>213</v>
       </c>
-      <c r="F123" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G123" s="8">
+      <c t="s" r="H123" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I123" s="7">
         <v>214</v>
       </c>
-      <c t="s" r="H123" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I123" s="7">
-        <v>215</v>
-      </c>
       <c t="s" r="J123" s="7">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5241,7 +5245,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>90</v>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5274,10 +5278,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5325,7 +5329,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5343,7 +5347,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5358,7 +5362,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5376,7 +5380,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5388,10 +5392,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5409,7 +5413,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5424,7 +5428,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5442,7 +5446,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5451,13 +5455,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5490,7 +5494,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5502,17 +5506,17 @@
         <v>86</v>
       </c>
       <c t="s" r="I133" s="7">
+        <v>223</v>
+      </c>
+      <c t="s" r="J133" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="K133" s="7">
         <v>225</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>43</v>
-      </c>
-      <c t="s" r="K133" s="7">
-        <v>226</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5527,7 +5531,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5536,20 +5540,20 @@
         <v>86</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>103</v>
       </c>
       <c t="s" r="K134" s="7">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5564,29 +5568,29 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c t="s" r="J135" s="7">
+        <v>228</v>
+      </c>
+      <c t="s" r="K135" s="7">
         <v>229</v>
-      </c>
-      <c t="s" r="K135" s="7">
-        <v>230</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5601,7 +5605,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5616,7 +5620,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5634,7 +5638,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5646,10 +5650,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5667,7 +5671,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5679,10 +5683,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5715,7 +5719,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5724,10 +5728,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>30</v>
@@ -5748,13 +5752,13 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
@@ -5763,7 +5767,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5781,7 +5785,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5793,10 +5797,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I142" s="7">
+        <v>235</v>
+      </c>
+      <c t="s" r="J142" s="7">
         <v>236</v>
-      </c>
-      <c t="s" r="J142" s="7">
-        <v>237</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5814,7 +5818,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5823,13 +5827,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5847,22 +5851,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>86</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5880,7 +5884,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5892,7 +5896,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>28</v>
@@ -5928,19 +5932,19 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
+        <v>240</v>
+      </c>
+      <c r="F147" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G147" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H147" s="8">
         <v>241</v>
       </c>
-      <c r="F147" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G147" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H147" s="8">
+      <c t="s" r="I147" s="7">
         <v>242</v>
-      </c>
-      <c t="s" r="I147" s="7">
-        <v>243</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>19</v>
@@ -5961,19 +5965,19 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
+        <v>240</v>
+      </c>
+      <c r="F148" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G148" s="8">
         <v>241</v>
       </c>
-      <c r="F148" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G148" s="8">
-        <v>242</v>
-      </c>
       <c t="s" r="H148" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>35</v>
@@ -5994,7 +5998,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6009,7 +6013,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6027,7 +6031,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6039,10 +6043,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6075,16 +6079,16 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
+        <v>244</v>
+      </c>
+      <c r="F152" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G152" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H152" s="8">
         <v>245</v>
-      </c>
-      <c r="F152" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G152" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H152" s="8">
-        <v>246</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>94</v>
@@ -6108,19 +6112,19 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
+        <v>244</v>
+      </c>
+      <c r="F153" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G153" s="8">
         <v>245</v>
       </c>
-      <c r="F153" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G153" s="8">
+      <c t="s" r="H153" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I153" s="7">
         <v>246</v>
-      </c>
-      <c t="s" r="H153" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I153" s="7">
-        <v>247</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>18</v>
@@ -6141,7 +6145,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6150,13 +6154,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6174,22 +6178,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
+        <v>248</v>
+      </c>
+      <c t="s" r="J155" s="7">
         <v>44</v>
-      </c>
-      <c t="s" r="J155" s="7">
-        <v>138</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6207,7 +6211,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6216,7 +6220,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>249</v>
@@ -6240,13 +6244,13 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>17</v>
@@ -6255,7 +6259,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6273,7 +6277,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6306,7 +6310,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6369,7 +6373,7 @@
         <v>257</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>43</v>
+        <v>224</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6399,10 +6403,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6432,7 +6436,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>19</v>
@@ -6465,10 +6469,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6498,7 +6502,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>56</v>
@@ -6582,7 +6586,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6681,7 +6685,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6714,7 +6718,7 @@
         <v>262</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6792,7 +6796,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>185</v>
@@ -6828,7 +6832,7 @@
         <v>264</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6858,10 +6862,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6891,7 +6895,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>82</v>
@@ -6942,7 +6946,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7008,7 +7012,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7089,7 +7093,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7122,7 +7126,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7152,7 +7156,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>269</v>
@@ -7218,10 +7222,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7251,7 +7255,7 @@
         <v>271</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>25</v>
@@ -7365,10 +7369,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7398,10 +7402,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7467,7 +7471,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7545,7 +7549,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>280</v>
@@ -7578,10 +7582,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7614,7 +7618,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7644,10 +7648,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I203" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="J203" s="7">
         <v>46</v>
-      </c>
-      <c t="s" r="J203" s="7">
-        <v>209</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7689,7 +7693,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>98</v>
@@ -7719,13 +7723,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>282</v>
@@ -7755,13 +7759,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7785,7 +7789,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>17</v>
@@ -7839,7 +7843,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>285</v>
@@ -7908,7 +7912,7 @@
         <v>286</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8022,14 +8026,14 @@
         <v>289</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8059,7 +8063,7 @@
         <v>290</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8134,10 +8138,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>42</v>
+        <v>292</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>19</v>
@@ -8164,13 +8168,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>42</v>
+        <v>292</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>37</v>
@@ -8206,7 +8210,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8236,10 +8240,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8272,22 +8276,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8305,7 +8309,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8317,10 +8321,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8338,7 +8342,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8353,7 +8357,7 @@
         <v>270</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8371,7 +8375,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8380,13 +8384,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>192</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8419,7 +8423,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8431,10 +8435,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8452,7 +8456,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8464,7 +8468,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>21</v>
@@ -8485,7 +8489,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8497,10 +8501,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8518,7 +8522,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8527,13 +8531,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8551,19 +8555,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>81</v>
@@ -8599,7 +8603,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8608,13 +8612,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8632,19 +8636,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>87</v>
@@ -8665,7 +8669,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8674,13 +8678,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8698,13 +8702,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>27</v>
@@ -8731,7 +8735,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8743,7 +8747,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>51</v>
@@ -8779,7 +8783,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8794,7 +8798,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8812,7 +8816,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8824,10 +8828,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8845,7 +8849,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8854,13 +8858,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8878,22 +8882,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8926,7 +8930,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F247" s="7">
         <v>320</v>
@@ -8941,7 +8945,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>313</v>
+        <v>174</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8959,7 +8963,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F248" s="7">
         <v>320</v>
@@ -8971,10 +8975,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -8992,7 +8996,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F249" s="7">
         <v>320</v>
@@ -9004,10 +9008,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9025,7 +9029,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F250" s="7">
         <v>320</v>
@@ -9037,10 +9041,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9058,7 +9062,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -9091,7 +9095,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
@@ -9103,10 +9107,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9124,7 +9128,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9220,7 +9224,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9250,10 +9254,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9283,7 +9287,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>106</v>
@@ -9349,10 +9353,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I260" s="7">
+        <v>46</v>
+      </c>
+      <c t="s" r="J260" s="7">
         <v>209</v>
-      </c>
-      <c t="s" r="J260" s="7">
-        <v>210</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9391,16 +9395,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9430,7 +9434,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>78</v>
@@ -9475,10 +9479,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>175</v>
@@ -9505,7 +9509,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>60</v>
@@ -9514,7 +9518,7 @@
         <v>320</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9544,10 +9548,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9580,7 +9584,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9688,10 +9692,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>183</v>
@@ -9718,7 +9722,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>96</v>
@@ -9754,13 +9758,13 @@
         <v>96</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9784,13 +9788,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>19</v>
@@ -9820,7 +9824,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>324</v>
@@ -9850,16 +9854,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9886,13 +9890,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9916,7 +9920,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
@@ -9925,7 +9929,7 @@
         <v>325</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10003,7 +10007,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>196</v>
@@ -10066,7 +10070,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>283</v>
@@ -10096,7 +10100,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>60</v>
@@ -10105,7 +10109,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10219,7 +10223,7 @@
         <v>267</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10249,10 +10253,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10399,7 +10403,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10429,7 +10433,7 @@
         <v>337</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>83</v>
@@ -10465,7 +10469,7 @@
         <v>181</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10510,7 +10514,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>340</v>
@@ -10540,13 +10544,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10570,7 +10574,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>60</v>
@@ -10579,7 +10583,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10609,10 +10613,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10657,10 +10661,10 @@
         <v>330</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10693,7 +10697,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10723,10 +10727,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10756,10 +10760,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10807,7 +10811,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10903,7 +10907,7 @@
         <v>327</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>266</v>
@@ -10936,7 +10940,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>269</v>
@@ -11047,10 +11051,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>266</v>
@@ -11077,7 +11081,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
@@ -11113,10 +11117,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>81</v>
@@ -11143,13 +11147,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>92</v>
@@ -11296,7 +11300,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>249</v>
@@ -11362,10 +11366,10 @@
         <v>327</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11424,7 +11428,7 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
@@ -11440,13 +11444,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>208</v>
+        <v>292</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>138</v>
+        <v>248</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11457,7 +11461,7 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
@@ -11470,65 +11474,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>208</v>
+        <v>292</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>209</v>
+        <v>136</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c r="M331" s="7"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
-      <c r="A332" s="6"/>
-      <c r="B332" s="7"/>
-      <c r="C332" s="7"/>
+      <c t="s" r="A332" s="6">
+        <v>13</v>
+      </c>
+      <c r="B332" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="C332" s="7">
+        <v>14</v>
+      </c>
       <c r="D332" s="7"/>
-      <c r="E332" s="7"/>
-      <c r="F332" s="7"/>
-      <c r="G332" s="8"/>
-      <c r="H332" s="8"/>
-      <c r="I332" s="7"/>
-      <c r="J332" s="7"/>
+      <c t="s" r="E332" s="7">
+        <v>349</v>
+      </c>
+      <c r="F332" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G332" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H332" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I332" s="7">
+        <v>165</v>
+      </c>
+      <c t="s" r="J332" s="7">
+        <v>209</v>
+      </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c r="M332" s="7"/>
     </row>
     <row r="333" ht="14.25" customHeight="1">
-      <c t="s" r="A333" s="6">
-        <v>13</v>
-      </c>
-      <c r="B333" s="7">
-        <v>447</v>
-      </c>
-      <c t="s" r="C333" s="7">
-        <v>14</v>
-      </c>
+      <c r="A333" s="6"/>
+      <c r="B333" s="7"/>
+      <c r="C333" s="7"/>
       <c r="D333" s="7"/>
-      <c t="s" r="E333" s="7">
-        <v>350</v>
-      </c>
-      <c r="F333" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G333" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H333" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I333" s="7">
-        <v>175</v>
-      </c>
-      <c t="s" r="J333" s="7">
-        <v>115</v>
-      </c>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
+      <c r="G333" s="8"/>
+      <c r="H333" s="8"/>
+      <c r="I333" s="7"/>
+      <c r="J333" s="7"/>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c r="M333" s="7"/>
@@ -11538,7 +11542,7 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
@@ -11551,16 +11555,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H334" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H334" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I334" s="7">
-        <v>340</v>
+        <v>175</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11571,7 +11575,7 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
@@ -11584,16 +11588,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>149</v>
+        <v>340</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11604,7 +11608,7 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
@@ -11617,16 +11621,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H336" s="8">
         <v>105</v>
       </c>
-      <c t="s" r="H336" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I336" s="7">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11637,7 +11641,7 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>7712</v>
+        <v>408</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
@@ -11650,16 +11654,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>351</v>
+        <v>149</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11667,10 +11671,10 @@
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>7713</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
@@ -11683,65 +11687,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H338" s="8">
         <v>337</v>
       </c>
-      <c t="s" r="H338" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I338" s="7">
-        <v>64</v>
+        <v>238</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c r="A339" s="6"/>
-      <c r="B339" s="7"/>
-      <c r="C339" s="7"/>
+      <c t="s" r="A339" s="6">
+        <v>63</v>
+      </c>
+      <c r="B339" s="7">
+        <v>7713</v>
+      </c>
+      <c t="s" r="C339" s="7">
+        <v>14</v>
+      </c>
       <c r="D339" s="7"/>
-      <c r="E339" s="7"/>
-      <c r="F339" s="7"/>
-      <c r="G339" s="8"/>
-      <c r="H339" s="8"/>
-      <c r="I339" s="7"/>
-      <c r="J339" s="7"/>
+      <c t="s" r="E339" s="7">
+        <v>350</v>
+      </c>
+      <c r="F339" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G339" s="8">
+        <v>337</v>
+      </c>
+      <c t="s" r="H339" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I339" s="7">
+        <v>64</v>
+      </c>
+      <c t="s" r="J339" s="7">
+        <v>352</v>
+      </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
     </row>
     <row r="340" ht="15" customHeight="1">
-      <c t="s" r="A340" s="6">
-        <v>13</v>
-      </c>
-      <c r="B340" s="7">
-        <v>973</v>
-      </c>
-      <c t="s" r="C340" s="7">
-        <v>14</v>
-      </c>
+      <c r="A340" s="6"/>
+      <c r="B340" s="7"/>
+      <c r="C340" s="7"/>
       <c r="D340" s="7"/>
-      <c t="s" r="E340" s="7">
-        <v>353</v>
-      </c>
-      <c r="F340" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G340" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H340" s="8">
-        <v>303</v>
-      </c>
-      <c t="s" r="I340" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J340" s="7">
-        <v>109</v>
-      </c>
+      <c r="E340" s="7"/>
+      <c r="F340" s="7"/>
+      <c r="G340" s="8"/>
+      <c r="H340" s="8"/>
+      <c r="I340" s="7"/>
+      <c r="J340" s="7"/>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c r="M340" s="7"/>
@@ -11751,7 +11755,7 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>814</v>
+        <v>973</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
@@ -11764,16 +11768,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>17</v>
+        <v>304</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>314</v>
+        <v>87</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11784,7 +11788,7 @@
         <v>13</v>
       </c>
       <c r="B342" s="7">
-        <v>3908</v>
+        <v>814</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
@@ -11797,16 +11801,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>17</v>
+        <v>304</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>271</v>
+        <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>355</v>
+        <v>56</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11814,10 +11818,10 @@
     </row>
     <row r="343" ht="14.25" customHeight="1">
       <c t="s" r="A343" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
@@ -11830,65 +11834,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H343" s="8">
         <v>271</v>
       </c>
-      <c t="s" r="H343" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I343" s="7">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c r="A344" s="6"/>
-      <c r="B344" s="7"/>
-      <c r="C344" s="7"/>
+      <c t="s" r="A344" s="6">
+        <v>63</v>
+      </c>
+      <c r="B344" s="7">
+        <v>3909</v>
+      </c>
+      <c t="s" r="C344" s="7">
+        <v>14</v>
+      </c>
       <c r="D344" s="7"/>
-      <c r="E344" s="7"/>
-      <c r="F344" s="7"/>
-      <c r="G344" s="8"/>
-      <c r="H344" s="8"/>
-      <c r="I344" s="7"/>
-      <c r="J344" s="7"/>
+      <c t="s" r="E344" s="7">
+        <v>353</v>
+      </c>
+      <c r="F344" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G344" s="8">
+        <v>271</v>
+      </c>
+      <c t="s" r="H344" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I344" s="7">
+        <v>356</v>
+      </c>
+      <c t="s" r="J344" s="7">
+        <v>357</v>
+      </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
     </row>
     <row r="345" ht="15" customHeight="1">
-      <c t="s" r="A345" s="6">
-        <v>13</v>
-      </c>
-      <c r="B345" s="7">
-        <v>461</v>
-      </c>
-      <c t="s" r="C345" s="7">
-        <v>14</v>
-      </c>
+      <c r="A345" s="6"/>
+      <c r="B345" s="7"/>
+      <c r="C345" s="7"/>
       <c r="D345" s="7"/>
-      <c t="s" r="E345" s="7">
-        <v>358</v>
-      </c>
-      <c r="F345" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G345" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H345" s="8">
-        <v>330</v>
-      </c>
-      <c t="s" r="I345" s="7">
-        <v>225</v>
-      </c>
-      <c t="s" r="J345" s="7">
-        <v>299</v>
-      </c>
+      <c r="E345" s="7"/>
+      <c r="F345" s="7"/>
+      <c r="G345" s="8"/>
+      <c r="H345" s="8"/>
+      <c r="I345" s="7"/>
+      <c r="J345" s="7"/>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c r="M345" s="7"/>
@@ -11898,7 +11902,7 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
@@ -11911,16 +11915,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H346" s="8">
         <v>330</v>
       </c>
-      <c t="s" r="H346" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I346" s="7">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11931,7 +11935,7 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>515</v>
+        <v>462</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
@@ -11944,16 +11948,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>282</v>
+        <v>18</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -11964,7 +11968,7 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
@@ -11977,16 +11981,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H348" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H348" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I348" s="7">
-        <v>154</v>
+        <v>282</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11997,7 +12001,7 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>441</v>
+        <v>508</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
@@ -12010,16 +12014,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12030,7 +12034,7 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
@@ -12043,16 +12047,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H350" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H350" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I350" s="7">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>359</v>
+        <v>132</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12060,10 +12064,10 @@
     </row>
     <row r="351" ht="14.25" customHeight="1">
       <c t="s" r="A351" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>958</v>
+        <v>442</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
@@ -12076,65 +12080,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>339</v>
+        <v>60</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>360</v>
+        <v>48</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>223</v>
+        <v>359</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
-      <c r="A352" s="6"/>
-      <c r="B352" s="7"/>
-      <c r="C352" s="7"/>
+      <c t="s" r="A352" s="6">
+        <v>63</v>
+      </c>
+      <c r="B352" s="7">
+        <v>958</v>
+      </c>
+      <c t="s" r="C352" s="7">
+        <v>14</v>
+      </c>
       <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
-      <c r="G352" s="8"/>
-      <c r="H352" s="8"/>
-      <c r="I352" s="7"/>
-      <c r="J352" s="7"/>
+      <c t="s" r="E352" s="7">
+        <v>358</v>
+      </c>
+      <c r="F352" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G352" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H352" s="8">
+        <v>339</v>
+      </c>
+      <c t="s" r="I352" s="7">
+        <v>360</v>
+      </c>
+      <c t="s" r="J352" s="7">
+        <v>221</v>
+      </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c t="s" r="A353" s="6">
-        <v>13</v>
-      </c>
-      <c r="B353" s="7">
-        <v>849</v>
-      </c>
-      <c t="s" r="C353" s="7">
-        <v>14</v>
-      </c>
+      <c r="A353" s="6"/>
+      <c r="B353" s="7"/>
+      <c r="C353" s="7"/>
       <c r="D353" s="7"/>
-      <c t="s" r="E353" s="7">
-        <v>361</v>
-      </c>
-      <c r="F353" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G353" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H353" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I353" s="7">
-        <v>223</v>
-      </c>
-      <c t="s" r="J353" s="7">
-        <v>130</v>
-      </c>
+      <c r="E353" s="7"/>
+      <c r="F353" s="7"/>
+      <c r="G353" s="8"/>
+      <c r="H353" s="8"/>
+      <c r="I353" s="7"/>
+      <c r="J353" s="7"/>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
@@ -12144,7 +12148,7 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
@@ -12157,16 +12161,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H354" s="8">
         <v>67</v>
       </c>
-      <c t="s" r="H354" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I354" s="7">
-        <v>149</v>
+        <v>221</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12177,7 +12181,7 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>352</v>
+        <v>848</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
@@ -12190,16 +12194,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12210,7 +12214,7 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
@@ -12223,16 +12227,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H356" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H356" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I356" s="7">
-        <v>61</v>
+        <v>314</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12243,7 +12247,7 @@
         <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>652</v>
+        <v>353</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
@@ -12256,16 +12260,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>122</v>
+        <v>216</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12276,7 +12280,7 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
@@ -12289,65 +12293,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H358" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H358" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I358" s="7">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>351</v>
+        <v>120</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
-      <c r="A359" s="6"/>
-      <c r="B359" s="7"/>
-      <c r="C359" s="7"/>
+      <c t="s" r="A359" s="6">
+        <v>13</v>
+      </c>
+      <c r="B359" s="7">
+        <v>631</v>
+      </c>
+      <c t="s" r="C359" s="7">
+        <v>14</v>
+      </c>
       <c r="D359" s="7"/>
-      <c r="E359" s="7"/>
-      <c r="F359" s="7"/>
-      <c r="G359" s="8"/>
-      <c r="H359" s="8"/>
-      <c r="I359" s="7"/>
-      <c r="J359" s="7"/>
+      <c t="s" r="E359" s="7">
+        <v>361</v>
+      </c>
+      <c r="F359" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G359" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H359" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I359" s="7">
+        <v>169</v>
+      </c>
+      <c t="s" r="J359" s="7">
+        <v>351</v>
+      </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
-      <c t="s" r="A360" s="6">
-        <v>13</v>
-      </c>
-      <c r="B360" s="7">
-        <v>925</v>
-      </c>
-      <c t="s" r="C360" s="7">
-        <v>14</v>
-      </c>
+      <c r="A360" s="6"/>
+      <c r="B360" s="7"/>
+      <c r="C360" s="7"/>
       <c r="D360" s="7"/>
-      <c t="s" r="E360" s="7">
-        <v>362</v>
-      </c>
-      <c r="F360" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G360" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="H360" s="8">
-        <v>116</v>
-      </c>
-      <c t="s" r="I360" s="7">
-        <v>226</v>
-      </c>
-      <c t="s" r="J360" s="7">
-        <v>343</v>
-      </c>
+      <c r="E360" s="7"/>
+      <c r="F360" s="7"/>
+      <c r="G360" s="8"/>
+      <c r="H360" s="8"/>
+      <c r="I360" s="7"/>
+      <c r="J360" s="7"/>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c r="M360" s="7"/>
@@ -12357,7 +12361,7 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>693</v>
+        <v>925</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
@@ -12370,16 +12374,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12390,7 +12394,7 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
@@ -12403,16 +12407,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="H362" s="8">
         <v>105</v>
       </c>
-      <c t="s" r="H362" s="8">
-        <v>116</v>
-      </c>
       <c t="s" r="I362" s="7">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>110</v>
+        <v>314</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12423,7 +12427,7 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>926</v>
+        <v>692</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
@@ -12436,65 +12440,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>363</v>
+        <v>117</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>202</v>
+        <v>109</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c r="A364" s="6"/>
-      <c r="B364" s="7"/>
-      <c r="C364" s="7"/>
+      <c t="s" r="A364" s="6">
+        <v>13</v>
+      </c>
+      <c r="B364" s="7">
+        <v>926</v>
+      </c>
+      <c t="s" r="C364" s="7">
+        <v>14</v>
+      </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
-      <c r="F364" s="7"/>
-      <c r="G364" s="8"/>
-      <c r="H364" s="8"/>
-      <c r="I364" s="7"/>
-      <c r="J364" s="7"/>
+      <c t="s" r="E364" s="7">
+        <v>362</v>
+      </c>
+      <c r="F364" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G364" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="H364" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="I364" s="7">
+        <v>363</v>
+      </c>
+      <c t="s" r="J364" s="7">
+        <v>203</v>
+      </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c t="s" r="A365" s="6">
-        <v>13</v>
-      </c>
-      <c r="B365" s="7">
-        <v>501</v>
-      </c>
-      <c t="s" r="C365" s="7">
-        <v>14</v>
-      </c>
+      <c r="A365" s="6"/>
+      <c r="B365" s="7"/>
+      <c r="C365" s="7"/>
       <c r="D365" s="7"/>
-      <c t="s" r="E365" s="7">
-        <v>364</v>
-      </c>
-      <c r="F365" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G365" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H365" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I365" s="7">
-        <v>365</v>
-      </c>
-      <c t="s" r="J365" s="7">
-        <v>29</v>
-      </c>
+      <c r="E365" s="7"/>
+      <c r="F365" s="7"/>
+      <c r="G365" s="8"/>
+      <c r="H365" s="8"/>
+      <c r="I365" s="7"/>
+      <c r="J365" s="7"/>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
@@ -12504,7 +12508,7 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
@@ -12517,16 +12521,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H366" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H366" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I366" s="7">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12537,7 +12541,7 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>563</v>
+        <v>514</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
@@ -12550,16 +12554,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>227</v>
+        <v>31</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12570,7 +12574,7 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
@@ -12583,16 +12587,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H368" s="8">
         <v>100</v>
       </c>
-      <c t="s" r="H368" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I368" s="7">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12603,7 +12607,7 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>453</v>
+        <v>564</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
@@ -12616,16 +12620,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12636,7 +12640,7 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
@@ -12649,16 +12653,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H370" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H370" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I370" s="7">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12669,7 +12673,7 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>519</v>
+        <v>456</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
@@ -12682,16 +12686,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>61</v>
+        <v>287</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>321</v>
+        <v>24</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12702,7 +12706,7 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
@@ -12715,65 +12719,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H372" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H372" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I372" s="7">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>49</v>
+        <v>321</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c r="M372" s="7"/>
     </row>
     <row r="373" ht="14.25" customHeight="1">
-      <c r="A373" s="6"/>
-      <c r="B373" s="7"/>
-      <c r="C373" s="7"/>
+      <c t="s" r="A373" s="6">
+        <v>13</v>
+      </c>
+      <c r="B373" s="7">
+        <v>522</v>
+      </c>
+      <c t="s" r="C373" s="7">
+        <v>14</v>
+      </c>
       <c r="D373" s="7"/>
-      <c r="E373" s="7"/>
-      <c r="F373" s="7"/>
-      <c r="G373" s="8"/>
-      <c r="H373" s="8"/>
-      <c r="I373" s="7"/>
-      <c r="J373" s="7"/>
+      <c t="s" r="E373" s="7">
+        <v>364</v>
+      </c>
+      <c r="F373" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G373" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H373" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I373" s="7">
+        <v>186</v>
+      </c>
+      <c t="s" r="J373" s="7">
+        <v>49</v>
+      </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c t="s" r="A374" s="6">
-        <v>13</v>
-      </c>
-      <c r="B374" s="7">
-        <v>771</v>
-      </c>
-      <c t="s" r="C374" s="7">
-        <v>14</v>
-      </c>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
       <c r="D374" s="7"/>
-      <c t="s" r="E374" s="7">
-        <v>366</v>
-      </c>
-      <c r="F374" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G374" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H374" s="8">
-        <v>86</v>
-      </c>
-      <c t="s" r="I374" s="7">
-        <v>367</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>173</v>
-      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="7"/>
+      <c r="G374" s="8"/>
+      <c r="H374" s="8"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7"/>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
@@ -12783,7 +12787,7 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
@@ -12796,16 +12800,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H375" s="8">
         <v>86</v>
       </c>
-      <c t="s" r="H375" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I375" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>343</v>
+        <v>172</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12816,7 +12820,7 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>403</v>
+        <v>770</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
@@ -12829,16 +12833,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>68</v>
+        <v>368</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>33</v>
+        <v>343</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12849,7 +12853,7 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
@@ -12862,16 +12866,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H377" s="8">
         <v>105</v>
       </c>
-      <c t="s" r="H377" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I377" s="7">
-        <v>286</v>
+        <v>68</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>309</v>
+        <v>33</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12882,7 +12886,7 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
@@ -12895,16 +12899,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>246</v>
+        <v>60</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12915,7 +12919,7 @@
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
@@ -12928,16 +12932,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>246</v>
+        <v>60</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>60</v>
+        <v>245</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>261</v>
+        <v>136</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12948,7 +12952,7 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>7238</v>
+        <v>424</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
@@ -12961,16 +12965,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>60</v>
+        <v>245</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>331</v>
+        <v>60</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>186</v>
+        <v>298</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>369</v>
+        <v>261</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12978,10 +12982,10 @@
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B381" s="7">
-        <v>7239</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
@@ -12994,65 +12998,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H381" s="8">
         <v>331</v>
       </c>
-      <c t="s" r="H381" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I381" s="7">
-        <v>370</v>
+        <v>186</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c r="A382" s="6"/>
-      <c r="B382" s="7"/>
-      <c r="C382" s="7"/>
+      <c t="s" r="A382" s="6">
+        <v>63</v>
+      </c>
+      <c r="B382" s="7">
+        <v>7239</v>
+      </c>
+      <c t="s" r="C382" s="7">
+        <v>14</v>
+      </c>
       <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
-      <c r="F382" s="7"/>
-      <c r="G382" s="8"/>
-      <c r="H382" s="8"/>
-      <c r="I382" s="7"/>
-      <c r="J382" s="7"/>
+      <c t="s" r="E382" s="7">
+        <v>366</v>
+      </c>
+      <c r="F382" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G382" s="8">
+        <v>331</v>
+      </c>
+      <c t="s" r="H382" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I382" s="7">
+        <v>370</v>
+      </c>
+      <c t="s" r="J382" s="7">
+        <v>371</v>
+      </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c r="M382" s="7"/>
     </row>
     <row r="383" ht="14.25" customHeight="1">
-      <c t="s" r="A383" s="6">
-        <v>13</v>
-      </c>
-      <c r="B383" s="7">
-        <v>335</v>
-      </c>
-      <c t="s" r="C383" s="7">
-        <v>14</v>
-      </c>
+      <c r="A383" s="6"/>
+      <c r="B383" s="7"/>
+      <c r="C383" s="7"/>
       <c r="D383" s="7"/>
-      <c t="s" r="E383" s="7">
-        <v>372</v>
-      </c>
-      <c r="F383" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G383" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H383" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I383" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="J383" s="7">
-        <v>185</v>
-      </c>
+      <c r="E383" s="7"/>
+      <c r="F383" s="7"/>
+      <c r="G383" s="8"/>
+      <c r="H383" s="8"/>
+      <c r="I383" s="7"/>
+      <c r="J383" s="7"/>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c r="M383" s="7"/>
@@ -13062,7 +13066,7 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>766</v>
+        <v>335</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
@@ -13075,16 +13079,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H384" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H384" s="8">
-        <v>116</v>
-      </c>
       <c t="s" r="I384" s="7">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13095,7 +13099,7 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
@@ -13108,16 +13112,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13128,7 +13132,7 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>976</v>
+        <v>767</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
@@ -13141,65 +13145,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="H386" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H386" s="8">
-        <v>23</v>
-      </c>
       <c t="s" r="I386" s="7">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c r="M386" s="7"/>
     </row>
     <row r="387" ht="14.25" customHeight="1">
-      <c r="A387" s="6"/>
-      <c r="B387" s="7"/>
-      <c r="C387" s="7"/>
+      <c t="s" r="A387" s="6">
+        <v>13</v>
+      </c>
+      <c r="B387" s="7">
+        <v>976</v>
+      </c>
+      <c t="s" r="C387" s="7">
+        <v>14</v>
+      </c>
       <c r="D387" s="7"/>
-      <c r="E387" s="7"/>
-      <c r="F387" s="7"/>
-      <c r="G387" s="8"/>
-      <c r="H387" s="8"/>
-      <c r="I387" s="7"/>
-      <c r="J387" s="7"/>
+      <c t="s" r="E387" s="7">
+        <v>372</v>
+      </c>
+      <c r="F387" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G387" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H387" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="I387" s="7">
+        <v>62</v>
+      </c>
+      <c t="s" r="J387" s="7">
+        <v>373</v>
+      </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c r="M387" s="7"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c t="s" r="A388" s="6">
-        <v>13</v>
-      </c>
-      <c r="B388" s="7">
-        <v>934</v>
-      </c>
-      <c t="s" r="C388" s="7">
-        <v>14</v>
-      </c>
+      <c r="A388" s="6"/>
+      <c r="B388" s="7"/>
+      <c r="C388" s="7"/>
       <c r="D388" s="7"/>
-      <c t="s" r="E388" s="7">
-        <v>374</v>
-      </c>
-      <c r="F388" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G388" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H388" s="8">
-        <v>152</v>
-      </c>
-      <c t="s" r="I388" s="7">
-        <v>223</v>
-      </c>
-      <c t="s" r="J388" s="7">
-        <v>107</v>
-      </c>
+      <c r="E388" s="7"/>
+      <c r="F388" s="7"/>
+      <c r="G388" s="8"/>
+      <c r="H388" s="8"/>
+      <c r="I388" s="7"/>
+      <c r="J388" s="7"/>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
@@ -13209,7 +13213,7 @@
         <v>13</v>
       </c>
       <c r="B389" s="7">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
@@ -13222,16 +13226,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13239,10 +13243,10 @@
     </row>
     <row r="390" ht="15" customHeight="1">
       <c t="s" r="A390" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
@@ -13255,65 +13259,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c r="A391" s="6"/>
-      <c r="B391" s="7"/>
-      <c r="C391" s="7"/>
+      <c t="s" r="A391" s="6">
+        <v>63</v>
+      </c>
+      <c r="B391" s="7">
+        <v>932</v>
+      </c>
+      <c t="s" r="C391" s="7">
+        <v>14</v>
+      </c>
       <c r="D391" s="7"/>
-      <c r="E391" s="7"/>
-      <c r="F391" s="7"/>
-      <c r="G391" s="8"/>
-      <c r="H391" s="8"/>
-      <c r="I391" s="7"/>
-      <c r="J391" s="7"/>
+      <c t="s" r="E391" s="7">
+        <v>374</v>
+      </c>
+      <c r="F391" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G391" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H391" s="8">
+        <v>151</v>
+      </c>
+      <c t="s" r="I391" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J391" s="7">
+        <v>98</v>
+      </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c r="M391" s="7"/>
     </row>
     <row r="392" ht="14.25" customHeight="1">
-      <c t="s" r="A392" s="6">
-        <v>13</v>
-      </c>
-      <c r="B392" s="7">
-        <v>1382</v>
-      </c>
-      <c t="s" r="C392" s="7">
-        <v>14</v>
-      </c>
+      <c r="A392" s="6"/>
+      <c r="B392" s="7"/>
+      <c r="C392" s="7"/>
       <c r="D392" s="7"/>
-      <c t="s" r="E392" s="7">
-        <v>375</v>
-      </c>
-      <c r="F392" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G392" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H392" s="8">
-        <v>256</v>
-      </c>
-      <c t="s" r="I392" s="7">
-        <v>28</v>
-      </c>
-      <c t="s" r="J392" s="7">
-        <v>225</v>
-      </c>
+      <c r="E392" s="7"/>
+      <c r="F392" s="7"/>
+      <c r="G392" s="8"/>
+      <c r="H392" s="8"/>
+      <c r="I392" s="7"/>
+      <c r="J392" s="7"/>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c r="M392" s="7"/>
@@ -13323,7 +13327,7 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
@@ -13336,16 +13340,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H393" s="8">
         <v>256</v>
       </c>
-      <c t="s" r="H393" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I393" s="7">
-        <v>226</v>
+        <v>28</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13356,7 +13360,7 @@
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>1813</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
@@ -13369,16 +13373,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>274</v>
+        <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>45</v>
+        <v>246</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13389,7 +13393,7 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
@@ -13402,16 +13406,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H395" s="8">
         <v>274</v>
       </c>
-      <c t="s" r="H395" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I395" s="7">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13422,7 +13426,7 @@
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>1831</v>
+        <v>1814</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
@@ -13435,16 +13439,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>17</v>
+        <v>274</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>119</v>
+        <v>249</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13455,7 +13459,7 @@
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
@@ -13468,65 +13472,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H397" s="8">
         <v>59</v>
       </c>
-      <c t="s" r="H397" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I397" s="7">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c r="M397" s="7"/>
     </row>
     <row r="398" ht="14.25" customHeight="1">
-      <c r="A398" s="6"/>
-      <c r="B398" s="7"/>
-      <c r="C398" s="7"/>
+      <c t="s" r="A398" s="6">
+        <v>13</v>
+      </c>
+      <c r="B398" s="7">
+        <v>1832</v>
+      </c>
+      <c t="s" r="C398" s="7">
+        <v>14</v>
+      </c>
       <c r="D398" s="7"/>
-      <c r="E398" s="7"/>
-      <c r="F398" s="7"/>
-      <c r="G398" s="8"/>
-      <c r="H398" s="8"/>
-      <c r="I398" s="7"/>
-      <c r="J398" s="7"/>
+      <c t="s" r="E398" s="7">
+        <v>375</v>
+      </c>
+      <c r="F398" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G398" s="8">
+        <v>59</v>
+      </c>
+      <c t="s" r="H398" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I398" s="7">
+        <v>138</v>
+      </c>
+      <c t="s" r="J398" s="7">
+        <v>119</v>
+      </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c r="M398" s="7"/>
     </row>
     <row r="399" ht="14.25" customHeight="1">
-      <c t="s" r="A399" s="6">
-        <v>13</v>
-      </c>
-      <c r="B399" s="7">
-        <v>801</v>
-      </c>
-      <c t="s" r="C399" s="7">
-        <v>14</v>
-      </c>
+      <c r="A399" s="6"/>
+      <c r="B399" s="7"/>
+      <c r="C399" s="7"/>
       <c r="D399" s="7"/>
-      <c t="s" r="E399" s="7">
-        <v>376</v>
-      </c>
-      <c r="F399" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G399" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H399" s="8">
-        <v>242</v>
-      </c>
-      <c t="s" r="I399" s="7">
-        <v>313</v>
-      </c>
-      <c t="s" r="J399" s="7">
-        <v>215</v>
-      </c>
+      <c r="E399" s="7"/>
+      <c r="F399" s="7"/>
+      <c r="G399" s="8"/>
+      <c r="H399" s="8"/>
+      <c r="I399" s="7"/>
+      <c r="J399" s="7"/>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c r="M399" s="7"/>
@@ -13536,7 +13540,7 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
@@ -13549,16 +13553,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>242</v>
+        <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>17</v>
+        <v>241</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>276</v>
+        <v>174</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13569,7 +13573,7 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>308</v>
+        <v>802</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
@@ -13582,16 +13586,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>17</v>
+        <v>241</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>283</v>
+        <v>19</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13602,7 +13606,7 @@
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
@@ -13615,79 +13619,75 @@
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H402" s="8">
         <v>100</v>
       </c>
-      <c t="s" r="H402" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I402" s="7">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>166</v>
+        <v>283</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c r="A403" s="6"/>
-      <c r="B403" s="7"/>
-      <c r="C403" s="7"/>
+      <c t="s" r="A403" s="6">
+        <v>13</v>
+      </c>
+      <c r="B403" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="C403" s="7">
+        <v>14</v>
+      </c>
       <c r="D403" s="7"/>
-      <c r="E403" s="7"/>
-      <c r="F403" s="7"/>
-      <c r="G403" s="8"/>
-      <c r="H403" s="8"/>
-      <c r="I403" s="7"/>
-      <c r="J403" s="7"/>
+      <c t="s" r="E403" s="7">
+        <v>376</v>
+      </c>
+      <c r="F403" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G403" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="H403" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I403" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J403" s="7">
+        <v>165</v>
+      </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c r="M403" s="7"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
-      <c t="s" r="A404" s="6">
-        <v>13</v>
-      </c>
-      <c r="B404" s="7">
-        <v>5073</v>
-      </c>
-      <c t="s" r="C404" s="7">
-        <v>14</v>
-      </c>
+      <c r="A404" s="6"/>
+      <c r="B404" s="7"/>
+      <c r="C404" s="7"/>
       <c r="D404" s="7"/>
-      <c t="s" r="E404" s="7">
-        <v>377</v>
-      </c>
-      <c r="F404" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G404" s="8">
-        <v>86</v>
-      </c>
-      <c t="s" r="H404" s="8">
-        <v>378</v>
-      </c>
-      <c t="s" r="I404" s="7">
-        <v>225</v>
-      </c>
-      <c t="s" r="J404" s="7">
-        <v>154</v>
-      </c>
-      <c t="s" r="K404" s="7">
-        <v>247</v>
-      </c>
+      <c r="E404" s="7"/>
+      <c r="F404" s="7"/>
+      <c r="G404" s="8"/>
+      <c r="H404" s="8"/>
+      <c r="I404" s="7"/>
+      <c r="J404" s="7"/>
+      <c r="K404" s="7"/>
       <c r="L404" s="7"/>
-      <c t="s" r="M404" s="7">
-        <v>287</v>
-      </c>
+      <c r="M404" s="7"/>
     </row>
     <row r="405" ht="15" customHeight="1">
       <c t="s" r="A405" s="6">
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>5074</v>
+        <v>5073</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
@@ -13700,131 +13700,135 @@
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
+        <v>86</v>
+      </c>
+      <c t="s" r="H405" s="8">
         <v>378</v>
       </c>
-      <c t="s" r="H405" s="8">
-        <v>86</v>
-      </c>
       <c t="s" r="I405" s="7">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c t="s" r="K405" s="7">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="406" ht="14.25" customHeight="1">
+      <c t="s" r="A406" s="6">
+        <v>13</v>
+      </c>
+      <c r="B406" s="7">
+        <v>5074</v>
+      </c>
+      <c t="s" r="C406" s="7">
+        <v>14</v>
+      </c>
+      <c r="D406" s="7"/>
+      <c t="s" r="E406" s="7">
+        <v>377</v>
+      </c>
+      <c r="F406" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G406" s="8">
+        <v>378</v>
+      </c>
+      <c t="s" r="H406" s="8">
+        <v>86</v>
+      </c>
+      <c t="s" r="I406" s="7">
+        <v>35</v>
+      </c>
+      <c t="s" r="J406" s="7">
+        <v>203</v>
+      </c>
+      <c t="s" r="K406" s="7">
+        <v>108</v>
+      </c>
+      <c r="L406" s="7"/>
+      <c t="s" r="M406" s="7">
         <v>279</v>
       </c>
     </row>
-    <row r="406" ht="14.25" customHeight="1">
-      <c r="A406" s="6"/>
-      <c r="B406" s="7"/>
-      <c r="C406" s="7"/>
-      <c r="D406" s="7"/>
-      <c r="E406" s="7"/>
-      <c r="F406" s="7"/>
-      <c r="G406" s="8"/>
-      <c r="H406" s="8"/>
-      <c r="I406" s="7"/>
-      <c r="J406" s="7"/>
-      <c r="K406" s="7"/>
-      <c r="L406" s="7"/>
-      <c r="M406" s="7"/>
-    </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c t="s" r="A407" s="6">
-        <v>13</v>
-      </c>
-      <c r="B407" s="7">
+      <c r="A407" s="6"/>
+      <c r="B407" s="7"/>
+      <c r="C407" s="7"/>
+      <c r="D407" s="7"/>
+      <c r="E407" s="7"/>
+      <c r="F407" s="7"/>
+      <c r="G407" s="8"/>
+      <c r="H407" s="8"/>
+      <c r="I407" s="7"/>
+      <c r="J407" s="7"/>
+      <c r="K407" s="7"/>
+      <c r="L407" s="7"/>
+      <c r="M407" s="7"/>
+    </row>
+    <row r="408" ht="14.25" customHeight="1">
+      <c t="s" r="A408" s="6">
+        <v>13</v>
+      </c>
+      <c r="B408" s="7">
         <v>81</v>
       </c>
-      <c t="s" r="C407" s="7">
-        <v>14</v>
-      </c>
-      <c r="D407" s="7"/>
-      <c t="s" r="E407" s="7">
+      <c t="s" r="C408" s="7">
+        <v>14</v>
+      </c>
+      <c r="D408" s="7"/>
+      <c t="s" r="E408" s="7">
         <v>379</v>
       </c>
-      <c r="F407" s="7">
+      <c r="F408" s="7">
         <v>330</v>
       </c>
-      <c t="s" r="G407" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H407" s="8">
+      <c t="s" r="G408" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H408" s="8">
         <v>380</v>
       </c>
-      <c t="s" r="I407" s="7">
-        <v>107</v>
-      </c>
-      <c t="s" r="J407" s="7">
+      <c t="s" r="I408" s="7">
+        <v>45</v>
+      </c>
+      <c t="s" r="J408" s="7">
         <v>352</v>
       </c>
-      <c t="s" r="K407" s="7">
-        <v>199</v>
-      </c>
-      <c r="L407" s="7"/>
-      <c t="s" r="M407" s="7">
+      <c t="s" r="K408" s="7">
+        <v>200</v>
+      </c>
+      <c r="L408" s="7"/>
+      <c t="s" r="M408" s="7">
         <v>334</v>
       </c>
     </row>
-    <row r="408" ht="14.25" customHeight="1">
-      <c r="A408" s="6"/>
-      <c r="B408" s="7"/>
-      <c r="C408" s="7"/>
-      <c r="D408" s="7"/>
-      <c r="E408" s="7"/>
-      <c r="F408" s="7"/>
-      <c r="G408" s="8"/>
-      <c r="H408" s="8"/>
-      <c r="I408" s="7"/>
-      <c r="J408" s="7"/>
-      <c r="K408" s="7"/>
-      <c r="L408" s="7"/>
-      <c r="M408" s="7"/>
-    </row>
     <row r="409" ht="14.25" customHeight="1">
-      <c t="s" r="A409" s="6">
-        <v>13</v>
-      </c>
-      <c r="B409" s="7">
-        <v>5060</v>
-      </c>
-      <c t="s" r="C409" s="7">
-        <v>14</v>
-      </c>
+      <c r="A409" s="6"/>
+      <c r="B409" s="7"/>
+      <c r="C409" s="7"/>
       <c r="D409" s="7"/>
-      <c t="s" r="E409" s="7">
-        <v>381</v>
-      </c>
-      <c r="F409" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G409" s="8">
-        <v>86</v>
-      </c>
-      <c t="s" r="H409" s="8">
-        <v>382</v>
-      </c>
-      <c t="s" r="I409" s="7">
-        <v>205</v>
-      </c>
-      <c t="s" r="J409" s="7">
-        <v>383</v>
-      </c>
+      <c r="E409" s="7"/>
+      <c r="F409" s="7"/>
+      <c r="G409" s="8"/>
+      <c r="H409" s="8"/>
+      <c r="I409" s="7"/>
+      <c r="J409" s="7"/>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c r="M409" s="7"/>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c t="s" r="A410" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B410" s="7">
-        <v>5061</v>
+        <v>5060</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
@@ -13837,79 +13841,75 @@
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
+        <v>86</v>
+      </c>
+      <c t="s" r="H410" s="8">
         <v>382</v>
       </c>
-      <c t="s" r="H410" s="8">
-        <v>86</v>
-      </c>
       <c t="s" r="I410" s="7">
-        <v>352</v>
+        <v>206</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c r="M410" s="7"/>
     </row>
     <row r="411" ht="14.25" customHeight="1">
-      <c r="A411" s="6"/>
-      <c r="B411" s="7"/>
-      <c r="C411" s="7"/>
+      <c t="s" r="A411" s="6">
+        <v>63</v>
+      </c>
+      <c r="B411" s="7">
+        <v>5061</v>
+      </c>
+      <c t="s" r="C411" s="7">
+        <v>14</v>
+      </c>
       <c r="D411" s="7"/>
-      <c r="E411" s="7"/>
-      <c r="F411" s="7"/>
-      <c r="G411" s="8"/>
-      <c r="H411" s="8"/>
-      <c r="I411" s="7"/>
-      <c r="J411" s="7"/>
+      <c t="s" r="E411" s="7">
+        <v>381</v>
+      </c>
+      <c r="F411" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G411" s="8">
+        <v>382</v>
+      </c>
+      <c t="s" r="H411" s="8">
+        <v>86</v>
+      </c>
+      <c t="s" r="I411" s="7">
+        <v>352</v>
+      </c>
+      <c t="s" r="J411" s="7">
+        <v>384</v>
+      </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c r="M411" s="7"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
-      <c t="s" r="A412" s="6">
-        <v>13</v>
-      </c>
-      <c r="B412" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="C412" s="7">
-        <v>14</v>
-      </c>
+      <c r="A412" s="6"/>
+      <c r="B412" s="7"/>
+      <c r="C412" s="7"/>
       <c r="D412" s="7"/>
-      <c t="s" r="E412" s="7">
-        <v>385</v>
-      </c>
-      <c r="F412" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G412" s="8">
-        <v>386</v>
-      </c>
-      <c t="s" r="H412" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I412" s="7">
-        <v>305</v>
-      </c>
-      <c t="s" r="J412" s="7">
-        <v>269</v>
-      </c>
-      <c t="s" r="K412" s="7">
-        <v>336</v>
-      </c>
+      <c r="E412" s="7"/>
+      <c r="F412" s="7"/>
+      <c r="G412" s="8"/>
+      <c r="H412" s="8"/>
+      <c r="I412" s="7"/>
+      <c r="J412" s="7"/>
+      <c r="K412" s="7"/>
       <c r="L412" s="7"/>
-      <c t="s" r="M412" s="7">
-        <v>46</v>
-      </c>
+      <c r="M412" s="7"/>
     </row>
     <row r="413" ht="14.25" customHeight="1">
       <c t="s" r="A413" s="6">
         <v>13</v>
       </c>
       <c r="B413" s="7">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c t="s" r="C413" s="7">
         <v>14</v>
@@ -13922,20 +13922,24 @@
         <v>330</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>17</v>
+        <v>386</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>166</v>
+        <v>306</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>210</v>
-      </c>
-      <c r="K413" s="7"/>
+        <v>269</v>
+      </c>
+      <c t="s" r="K413" s="7">
+        <v>336</v>
+      </c>
       <c r="L413" s="7"/>
-      <c r="M413" s="7"/>
+      <c t="s" r="M413" s="7">
+        <v>136</v>
+      </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
       <c r="A414" s="6"/>
@@ -13979,14 +13983,14 @@
         <v>285</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c t="s" r="K415" s="7">
         <v>68</v>
       </c>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14013,17 +14017,17 @@
         <v>86</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>94</v>
       </c>
       <c t="s" r="K416" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14098,7 +14102,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>77</v>
@@ -14134,7 +14138,7 @@
         <v>290</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14197,7 +14201,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>40</v>
@@ -14245,10 +14249,10 @@
         <v>393</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14281,7 +14285,7 @@
         <v>394</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>

--- a/Data/FlightPlan/FPL_09OCT26.xlsx
+++ b/Data/FlightPlan/FPL_09OCT26.xlsx
@@ -533,426 +533,426 @@
     <t>04:20</t>
   </si>
   <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
     <t>08:35</t>
   </si>
   <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
     <t>17:55</t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>Total Record(s): 345</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 02:34</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 02:57</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5461,7 +5461,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5506,13 +5506,13 @@
         <v>86</v>
       </c>
       <c t="s" r="I133" s="7">
+        <v>222</v>
+      </c>
+      <c t="s" r="J133" s="7">
         <v>223</v>
       </c>
-      <c t="s" r="J133" s="7">
+      <c t="s" r="K133" s="7">
         <v>224</v>
-      </c>
-      <c t="s" r="K133" s="7">
-        <v>225</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5543,7 +5543,7 @@
         <v>114</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>103</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5583,14 +5583,14 @@
         <v>128</v>
       </c>
       <c t="s" r="J135" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="K135" s="7">
         <v>228</v>
-      </c>
-      <c t="s" r="K135" s="7">
-        <v>229</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5653,7 +5653,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5683,7 +5683,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>142</v>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5767,7 +5767,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5797,10 +5797,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I142" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J142" s="7">
         <v>235</v>
-      </c>
-      <c t="s" r="J142" s="7">
-        <v>236</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5827,7 +5827,7 @@
         <v>86</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>77</v>
@@ -5851,13 +5851,13 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>86</v>
@@ -5866,7 +5866,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5896,7 +5896,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>28</v>
@@ -5932,19 +5932,19 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
+        <v>239</v>
+      </c>
+      <c r="F147" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G147" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H147" s="8">
         <v>240</v>
       </c>
-      <c r="F147" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G147" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H147" s="8">
+      <c t="s" r="I147" s="7">
         <v>241</v>
-      </c>
-      <c t="s" r="I147" s="7">
-        <v>242</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>19</v>
@@ -5965,13 +5965,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
+        <v>239</v>
+      </c>
+      <c r="F148" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G148" s="8">
         <v>240</v>
-      </c>
-      <c r="F148" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G148" s="8">
-        <v>241</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>60</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6046,7 +6046,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6079,16 +6079,16 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
+        <v>243</v>
+      </c>
+      <c r="F152" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G152" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H152" s="8">
         <v>244</v>
-      </c>
-      <c r="F152" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G152" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H152" s="8">
-        <v>245</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>94</v>
@@ -6112,19 +6112,19 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
+        <v>243</v>
+      </c>
+      <c r="F153" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G153" s="8">
         <v>244</v>
       </c>
-      <c r="F153" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G153" s="8">
+      <c t="s" r="H153" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I153" s="7">
         <v>245</v>
-      </c>
-      <c t="s" r="H153" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I153" s="7">
-        <v>246</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>18</v>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6157,10 +6157,10 @@
         <v>114</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6190,7 +6190,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>44</v>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6223,7 +6223,7 @@
         <v>114</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>90</v>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6286,13 +6286,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
+        <v>249</v>
+      </c>
+      <c t="s" r="I158" s="7">
         <v>250</v>
       </c>
-      <c t="s" r="I158" s="7">
+      <c t="s" r="J158" s="7">
         <v>251</v>
-      </c>
-      <c t="s" r="J158" s="7">
-        <v>252</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6310,22 +6310,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
+        <v>252</v>
+      </c>
+      <c t="s" r="J159" s="7">
         <v>253</v>
-      </c>
-      <c t="s" r="J159" s="7">
-        <v>254</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6358,22 +6358,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
+        <v>254</v>
+      </c>
+      <c r="F161" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G161" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H161" s="8">
         <v>255</v>
       </c>
-      <c r="F161" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G161" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H161" s="8">
+      <c t="s" r="I161" s="7">
         <v>256</v>
       </c>
-      <c t="s" r="I161" s="7">
-        <v>257</v>
-      </c>
       <c t="s" r="J161" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6391,13 +6391,13 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
+        <v>254</v>
+      </c>
+      <c r="F162" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G162" s="8">
         <v>255</v>
-      </c>
-      <c r="F162" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G162" s="8">
-        <v>256</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>17</v>
@@ -6406,7 +6406,7 @@
         <v>214</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6436,7 +6436,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>19</v>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6538,22 +6538,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
+        <v>257</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H167" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I167" s="7">
         <v>258</v>
       </c>
-      <c r="F167" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G167" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H167" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I167" s="7">
+      <c t="s" r="J167" s="7">
         <v>259</v>
-      </c>
-      <c t="s" r="J167" s="7">
-        <v>260</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6682,7 +6682,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>210</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6715,7 +6715,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>140</v>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6817,19 +6817,19 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
+        <v>262</v>
+      </c>
+      <c r="F176" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G176" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H176" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I176" s="7">
         <v>263</v>
-      </c>
-      <c r="F176" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G176" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H176" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I176" s="7">
-        <v>264</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>45</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6976,10 +6976,10 @@
         <v>105</v>
       </c>
       <c t="s" r="I181" s="7">
+        <v>265</v>
+      </c>
+      <c t="s" r="J181" s="7">
         <v>266</v>
-      </c>
-      <c t="s" r="J181" s="7">
-        <v>267</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7093,7 +7093,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7159,7 +7159,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7192,7 +7192,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7252,7 +7252,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>120</v>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="H191" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I191" s="7">
+        <v>251</v>
+      </c>
+      <c t="s" r="J191" s="7">
         <v>271</v>
-      </c>
-      <c t="s" r="H191" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I191" s="7">
-        <v>252</v>
-      </c>
-      <c t="s" r="J191" s="7">
-        <v>272</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7324,22 +7324,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
+        <v>272</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H193" s="8">
         <v>273</v>
       </c>
-      <c r="F193" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G193" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H193" s="8">
+      <c t="s" r="I193" s="7">
         <v>274</v>
       </c>
-      <c t="s" r="I193" s="7">
+      <c t="s" r="J193" s="7">
         <v>275</v>
-      </c>
-      <c t="s" r="J193" s="7">
-        <v>276</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7357,19 +7357,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
+        <v>272</v>
+      </c>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
         <v>273</v>
       </c>
-      <c r="F194" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G194" s="8">
-        <v>274</v>
-      </c>
       <c t="s" r="H194" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>162</v>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7399,7 +7399,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>130</v>
@@ -7423,19 +7423,19 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>38</v>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7504,19 +7504,19 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
+        <v>277</v>
+      </c>
+      <c r="F199" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G199" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H199" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I199" s="7">
         <v>278</v>
-      </c>
-      <c r="F199" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G199" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H199" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I199" s="7">
-        <v>279</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>18</v>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7549,10 +7549,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7582,7 +7582,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>148</v>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7732,7 +7732,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7759,13 +7759,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7783,19 +7783,19 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>90</v>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7846,7 +7846,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7909,7 +7909,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>44</v>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7939,10 +7939,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>90</v>
@@ -7963,13 +7963,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>60</v>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8023,7 +8023,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>43</v>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8060,7 +8060,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>116</v>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8129,16 +8129,16 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
+        <v>290</v>
+      </c>
+      <c r="F220" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G220" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H220" s="8">
         <v>291</v>
-      </c>
-      <c r="F220" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G220" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H220" s="8">
-        <v>292</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>144</v>
@@ -8162,13 +8162,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
+        <v>290</v>
+      </c>
+      <c r="F221" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G221" s="8">
         <v>291</v>
-      </c>
-      <c r="F221" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G221" s="8">
-        <v>292</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>60</v>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8210,7 +8210,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8240,10 +8240,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I223" s="7">
+        <v>292</v>
+      </c>
+      <c t="s" r="J223" s="7">
         <v>293</v>
-      </c>
-      <c t="s" r="J223" s="7">
-        <v>294</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8276,22 +8276,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
+        <v>294</v>
+      </c>
+      <c r="F225" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G225" s="8">
         <v>295</v>
       </c>
-      <c r="F225" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G225" s="8">
+      <c t="s" r="H225" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I225" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J225" s="7">
         <v>296</v>
-      </c>
-      <c t="s" r="H225" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I225" s="7">
-        <v>226</v>
-      </c>
-      <c t="s" r="J225" s="7">
-        <v>297</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8321,7 +8321,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>215</v>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8354,10 +8354,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8375,22 +8375,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
+        <v>294</v>
+      </c>
+      <c r="F228" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G228" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H228" s="8">
         <v>295</v>
-      </c>
-      <c r="F228" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G228" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H228" s="8">
-        <v>296</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>192</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8438,7 +8438,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8501,7 +8501,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>130</v>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8531,7 +8531,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>163</v>
@@ -8555,13 +8555,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>17</v>
@@ -8596,29 +8596,29 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
+        <v>302</v>
+      </c>
+      <c r="F236" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G236" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H236" s="8">
+        <v>273</v>
+      </c>
+      <c t="s" r="I236" s="7">
+        <v>18</v>
+      </c>
+      <c t="s" r="J236" s="7">
         <v>303</v>
-      </c>
-      <c r="F236" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G236" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H236" s="8">
-        <v>304</v>
-      </c>
-      <c t="s" r="I236" s="7">
-        <v>123</v>
-      </c>
-      <c t="s" r="J236" s="7">
-        <v>305</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8629,29 +8629,29 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>970</v>
+        <v>826</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
+        <v>273</v>
+      </c>
+      <c t="s" r="H237" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I237" s="7">
+        <v>135</v>
+      </c>
+      <c t="s" r="J237" s="7">
         <v>304</v>
-      </c>
-      <c t="s" r="H237" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I237" s="7">
-        <v>306</v>
-      </c>
-      <c t="s" r="J237" s="7">
-        <v>87</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8662,29 +8662,29 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>8510</v>
+        <v>876</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>42</v>
+        <v>305</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>44</v>
+        <v>306</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8695,78 +8695,78 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>8511</v>
+        <v>877</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>42</v>
+        <v>305</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>56</v>
+        <v>209</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c t="s" r="A240" s="6">
-        <v>13</v>
-      </c>
-      <c r="B240" s="7">
-        <v>878</v>
-      </c>
-      <c t="s" r="C240" s="7">
-        <v>14</v>
-      </c>
+      <c r="A240" s="6"/>
+      <c r="B240" s="7"/>
+      <c r="C240" s="7"/>
       <c r="D240" s="7"/>
-      <c t="s" r="E240" s="7">
-        <v>303</v>
-      </c>
-      <c r="F240" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G240" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H240" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="I240" s="7">
-        <v>307</v>
-      </c>
-      <c t="s" r="J240" s="7">
-        <v>51</v>
-      </c>
+      <c r="E240" s="7"/>
+      <c r="F240" s="7"/>
+      <c r="G240" s="8"/>
+      <c r="H240" s="8"/>
+      <c r="I240" s="7"/>
+      <c r="J240" s="7"/>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c r="M240" s="7"/>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c r="A241" s="6"/>
-      <c r="B241" s="7"/>
-      <c r="C241" s="7"/>
+      <c t="s" r="A241" s="6">
+        <v>13</v>
+      </c>
+      <c r="B241" s="7">
+        <v>813</v>
+      </c>
+      <c t="s" r="C241" s="7">
+        <v>14</v>
+      </c>
       <c r="D241" s="7"/>
-      <c r="E241" s="7"/>
-      <c r="F241" s="7"/>
-      <c r="G241" s="8"/>
-      <c r="H241" s="8"/>
-      <c r="I241" s="7"/>
-      <c r="J241" s="7"/>
+      <c t="s" r="E241" s="7">
+        <v>307</v>
+      </c>
+      <c r="F241" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G241" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H241" s="8">
+        <v>308</v>
+      </c>
+      <c t="s" r="I241" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="J241" s="7">
+        <v>309</v>
+      </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c r="M241" s="7"/>
@@ -8776,29 +8776,29 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>825</v>
+        <v>970</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
+        <v>307</v>
+      </c>
+      <c r="F242" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G242" s="8">
         <v>308</v>
       </c>
-      <c r="F242" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G242" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="H242" s="8">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>309</v>
+        <v>87</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8809,29 +8809,29 @@
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>826</v>
+        <v>8510</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>310</v>
+        <v>46</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8842,29 +8842,29 @@
         <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>876</v>
+        <v>8511</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>311</v>
+        <v>27</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>312</v>
+        <v>56</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8875,29 +8875,29 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H245" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="I245" s="7">
         <v>311</v>
       </c>
-      <c t="s" r="H245" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I245" s="7">
-        <v>209</v>
-      </c>
       <c t="s" r="J245" s="7">
-        <v>243</v>
+        <v>51</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F247" s="7">
         <v>320</v>
@@ -8945,7 +8945,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F248" s="7">
         <v>320</v>
@@ -8978,7 +8978,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F249" s="7">
         <v>320</v>
@@ -9008,7 +9008,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>135</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F250" s="7">
         <v>320</v>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9254,10 +9254,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9287,7 +9287,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>106</v>
@@ -9320,7 +9320,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>70</v>
@@ -9401,7 +9401,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>128</v>
@@ -9434,7 +9434,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>78</v>
@@ -9479,7 +9479,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>123</v>
@@ -9509,7 +9509,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>60</v>
@@ -9548,7 +9548,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>115</v>
@@ -9614,7 +9614,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>91</v>
@@ -9728,7 +9728,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>175</v>
@@ -9794,7 +9794,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>19</v>
@@ -9830,7 +9830,7 @@
         <v>324</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9860,7 +9860,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>149</v>
@@ -9896,7 +9896,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10070,10 +10070,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>24</v>
@@ -10100,13 +10100,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>216</v>
@@ -10187,7 +10187,7 @@
         <v>330</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>34</v>
@@ -10220,7 +10220,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>163</v>
@@ -10514,7 +10514,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>340</v>
@@ -10544,7 +10544,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>21</v>
@@ -10574,7 +10574,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>60</v>
@@ -10616,7 +10616,7 @@
         <v>207</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10664,7 +10664,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10697,7 +10697,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10730,7 +10730,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10877,7 +10877,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10910,7 +10910,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10940,10 +10940,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10970,7 +10970,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>36</v>
@@ -11000,7 +11000,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>17</v>
@@ -11051,13 +11051,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11081,7 +11081,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
@@ -11234,7 +11234,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>101</v>
@@ -11303,7 +11303,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11333,7 +11333,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>314</v>
@@ -11444,13 +11444,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11474,7 +11474,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>17</v>
@@ -11693,7 +11693,7 @@
         <v>337</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>351</v>
@@ -11771,7 +11771,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>87</v>
@@ -11801,7 +11801,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
@@ -11837,7 +11837,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>354</v>
@@ -11867,7 +11867,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
@@ -11921,10 +11921,10 @@
         <v>330</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>146</v>
@@ -12122,7 +12122,7 @@
         <v>360</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12167,7 +12167,7 @@
         <v>67</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>128</v>
@@ -12380,7 +12380,7 @@
         <v>114</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>343</v>
@@ -12413,7 +12413,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>314</v>
@@ -12596,7 +12596,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12662,7 +12662,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12692,7 +12692,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>24</v>
@@ -12905,10 +12905,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12935,10 +12935,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>136</v>
@@ -12965,16 +12965,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13121,7 +13121,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13151,7 +13151,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>24</v>
@@ -13232,7 +13232,7 @@
         <v>151</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>45</v>
@@ -13343,13 +13343,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13373,16 +13373,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13409,7 +13409,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>68</v>
@@ -13439,7 +13439,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>17</v>
@@ -13448,7 +13448,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13556,10 +13556,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>214</v>
@@ -13586,13 +13586,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>19</v>
@@ -13625,10 +13625,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13706,17 +13706,17 @@
         <v>378</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>153</v>
       </c>
       <c t="s" r="K405" s="7">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -13928,10 +13928,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="K413" s="7">
         <v>336</v>
@@ -13980,7 +13980,7 @@
         <v>388</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>45</v>
@@ -14017,7 +14017,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>94</v>
@@ -14135,7 +14135,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>130</v>
@@ -14201,7 +14201,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>40</v>
@@ -14249,10 +14249,10 @@
         <v>393</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>

--- a/Data/FlightPlan/FPL_09OCT26.xlsx
+++ b/Data/FlightPlan/FPL_09OCT26.xlsx
@@ -806,243 +806,243 @@
     <t>VN-A637</t>
   </si>
   <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
     <t>14:15</t>
   </si>
   <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
     <t>VN-A670</t>
   </si>
   <si>
@@ -1199,7 +1199,7 @@
     <t>Total Record(s): 345</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 02:57</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 04:28</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6924,7 +6924,7 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>630</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
@@ -6940,13 +6940,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>125</v>
+        <v>222</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6957,7 +6957,7 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>1729</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
@@ -6970,16 +6970,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6990,7 +6990,7 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>1728</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
@@ -7003,32 +7003,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>27</v>
+        <v>265</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c r="A183" s="6"/>
-      <c r="B183" s="7"/>
-      <c r="C183" s="7"/>
+      <c t="s" r="A183" s="6">
+        <v>13</v>
+      </c>
+      <c r="B183" s="7">
+        <v>1814</v>
+      </c>
+      <c t="s" r="C183" s="7">
+        <v>14</v>
+      </c>
       <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7"/>
-      <c r="G183" s="8"/>
-      <c r="H183" s="8"/>
-      <c r="I183" s="7"/>
-      <c r="J183" s="7"/>
+      <c t="s" r="E183" s="7">
+        <v>264</v>
+      </c>
+      <c r="F183" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G183" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="H183" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I183" s="7">
+        <v>44</v>
+      </c>
+      <c t="s" r="J183" s="7">
+        <v>248</v>
+      </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
@@ -7038,14 +7056,14 @@
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>339</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7054,13 +7072,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>31</v>
+        <v>117</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7071,63 +7089,45 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>718</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>241</v>
+        <v>119</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c t="s" r="A186" s="6">
-        <v>13</v>
-      </c>
-      <c r="B186" s="7">
-        <v>719</v>
-      </c>
-      <c t="s" r="C186" s="7">
-        <v>14</v>
-      </c>
+      <c r="A186" s="6"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
       <c r="D186" s="7"/>
-      <c t="s" r="E186" s="7">
-        <v>267</v>
-      </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H186" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>190</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>129</v>
-      </c>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="7"/>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c r="M186" s="7"/>
@@ -7137,29 +7137,29 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>452</v>
+        <v>339</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H187" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H187" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I187" s="7">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>268</v>
+        <v>31</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7170,29 +7170,29 @@
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>517</v>
+        <v>718</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7203,14 +7203,14 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>520</v>
+        <v>719</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7219,13 +7219,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7236,29 +7236,29 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>7526</v>
+        <v>452</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
+        <v>266</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H190" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I190" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="J190" s="7">
         <v>267</v>
-      </c>
-      <c r="F190" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G190" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H190" s="8">
-        <v>270</v>
-      </c>
-      <c t="s" r="I190" s="7">
-        <v>120</v>
-      </c>
-      <c t="s" r="J190" s="7">
-        <v>25</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7266,48 +7266,66 @@
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c t="s" r="A191" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>7527</v>
+        <v>517</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>251</v>
+        <v>24</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c r="A192" s="6"/>
-      <c r="B192" s="7"/>
-      <c r="C192" s="7"/>
+      <c t="s" r="A192" s="6">
+        <v>13</v>
+      </c>
+      <c r="B192" s="7">
+        <v>520</v>
+      </c>
+      <c t="s" r="C192" s="7">
+        <v>14</v>
+      </c>
       <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="7"/>
-      <c r="G192" s="8"/>
-      <c r="H192" s="8"/>
-      <c r="I192" s="7"/>
-      <c r="J192" s="7"/>
+      <c t="s" r="E192" s="7">
+        <v>266</v>
+      </c>
+      <c r="F192" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G192" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H192" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I192" s="7">
+        <v>209</v>
+      </c>
+      <c t="s" r="J192" s="7">
+        <v>119</v>
+      </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
@@ -7317,14 +7335,14 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>905</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7333,13 +7351,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>274</v>
+        <v>120</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>275</v>
+        <v>25</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7347,66 +7365,48 @@
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c t="s" r="A194" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B194" s="7">
-        <v>906</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c r="M194" s="7"/>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c t="s" r="A195" s="6">
-        <v>13</v>
-      </c>
-      <c r="B195" s="7">
-        <v>913</v>
-      </c>
-      <c t="s" r="C195" s="7">
-        <v>14</v>
-      </c>
+      <c r="A195" s="6"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
       <c r="D195" s="7"/>
-      <c t="s" r="E195" s="7">
-        <v>272</v>
-      </c>
-      <c r="F195" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G195" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H195" s="8">
-        <v>276</v>
-      </c>
-      <c t="s" r="I195" s="7">
-        <v>130</v>
-      </c>
-      <c t="s" r="J195" s="7">
-        <v>206</v>
-      </c>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="8"/>
+      <c r="H195" s="8"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c r="M195" s="7"/>
@@ -7416,29 +7416,29 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
+        <v>271</v>
+      </c>
+      <c r="F196" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G196" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H196" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="I196" s="7">
         <v>272</v>
       </c>
-      <c r="F196" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G196" s="8">
-        <v>276</v>
-      </c>
-      <c t="s" r="H196" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I196" s="7">
-        <v>269</v>
-      </c>
       <c t="s" r="J196" s="7">
-        <v>38</v>
+        <v>273</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7446,48 +7446,66 @@
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c t="s" r="A197" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>982</v>
+        <v>906</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>60</v>
+        <v>265</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="A198" s="6"/>
-      <c r="B198" s="7"/>
-      <c r="C198" s="7"/>
+      <c t="s" r="A198" s="6">
+        <v>13</v>
+      </c>
+      <c r="B198" s="7">
+        <v>913</v>
+      </c>
+      <c t="s" r="C198" s="7">
+        <v>14</v>
+      </c>
       <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
-      <c r="G198" s="8"/>
-      <c r="H198" s="8"/>
-      <c r="I198" s="7"/>
-      <c r="J198" s="7"/>
+      <c t="s" r="E198" s="7">
+        <v>271</v>
+      </c>
+      <c r="F198" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G198" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H198" s="8">
+        <v>274</v>
+      </c>
+      <c t="s" r="I198" s="7">
+        <v>130</v>
+      </c>
+      <c t="s" r="J198" s="7">
+        <v>206</v>
+      </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
@@ -7497,29 +7515,29 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>197</v>
+        <v>914</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>60</v>
+        <v>274</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7527,66 +7545,48 @@
     </row>
     <row r="200" ht="15" customHeight="1">
       <c t="s" r="A200" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B200" s="7">
-        <v>634</v>
+        <v>982</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>279</v>
+        <v>123</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c t="s" r="A201" s="6">
-        <v>13</v>
-      </c>
-      <c r="B201" s="7">
-        <v>1504</v>
-      </c>
-      <c t="s" r="C201" s="7">
-        <v>14</v>
-      </c>
+      <c r="A201" s="6"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="7"/>
       <c r="D201" s="7"/>
-      <c t="s" r="E201" s="7">
-        <v>277</v>
-      </c>
-      <c r="F201" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G201" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H201" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I201" s="7">
-        <v>226</v>
-      </c>
-      <c t="s" r="J201" s="7">
-        <v>148</v>
-      </c>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="8"/>
+      <c r="H201" s="8"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
@@ -7596,14 +7596,14 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>1505</v>
+        <v>197</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7612,13 +7612,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7629,45 +7629,63 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
+        <v>275</v>
+      </c>
+      <c r="F203" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G203" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H203" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I203" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J203" s="7">
         <v>277</v>
-      </c>
-      <c r="F203" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G203" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H203" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I203" s="7">
-        <v>136</v>
-      </c>
-      <c t="s" r="J203" s="7">
-        <v>46</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="6"/>
-      <c r="B204" s="7"/>
-      <c r="C204" s="7"/>
+      <c t="s" r="A204" s="6">
+        <v>13</v>
+      </c>
+      <c r="B204" s="7">
+        <v>1504</v>
+      </c>
+      <c t="s" r="C204" s="7">
+        <v>14</v>
+      </c>
       <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
-      <c r="G204" s="8"/>
-      <c r="H204" s="8"/>
-      <c r="I204" s="7"/>
-      <c r="J204" s="7"/>
+      <c t="s" r="E204" s="7">
+        <v>275</v>
+      </c>
+      <c r="F204" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G204" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H204" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I204" s="7">
+        <v>226</v>
+      </c>
+      <c t="s" r="J204" s="7">
+        <v>148</v>
+      </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
@@ -7677,29 +7695,29 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>212</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7710,63 +7728,45 @@
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>215</v>
+        <v>637</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>281</v>
+        <v>46</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c r="M206" s="7"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
-      <c t="s" r="A207" s="6">
-        <v>13</v>
-      </c>
-      <c r="B207" s="7">
-        <v>807</v>
-      </c>
-      <c t="s" r="C207" s="7">
-        <v>14</v>
-      </c>
+      <c r="A207" s="6"/>
+      <c r="B207" s="7"/>
+      <c r="C207" s="7"/>
       <c r="D207" s="7"/>
-      <c t="s" r="E207" s="7">
-        <v>280</v>
-      </c>
-      <c r="F207" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G207" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H207" s="8">
-        <v>240</v>
-      </c>
-      <c t="s" r="I207" s="7">
-        <v>228</v>
-      </c>
-      <c t="s" r="J207" s="7">
-        <v>227</v>
-      </c>
+      <c r="E207" s="7"/>
+      <c r="F207" s="7"/>
+      <c r="G207" s="8"/>
+      <c r="H207" s="8"/>
+      <c r="I207" s="7"/>
+      <c r="J207" s="7"/>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c r="M207" s="7"/>
@@ -7776,45 +7776,63 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>800</v>
+        <v>212</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>282</v>
+        <v>98</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="6"/>
-      <c r="B209" s="7"/>
-      <c r="C209" s="7"/>
+      <c t="s" r="A209" s="6">
+        <v>13</v>
+      </c>
+      <c r="B209" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="C209" s="7">
+        <v>14</v>
+      </c>
       <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
-      <c r="F209" s="7"/>
-      <c r="G209" s="8"/>
-      <c r="H209" s="8"/>
-      <c r="I209" s="7"/>
-      <c r="J209" s="7"/>
+      <c t="s" r="E209" s="7">
+        <v>278</v>
+      </c>
+      <c r="F209" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G209" s="8">
+        <v>147</v>
+      </c>
+      <c t="s" r="H209" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I209" s="7">
+        <v>125</v>
+      </c>
+      <c t="s" r="J209" s="7">
+        <v>279</v>
+      </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
@@ -7824,14 +7842,14 @@
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>122</v>
+        <v>807</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7840,13 +7858,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7857,63 +7875,45 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>1491</v>
+        <v>800</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c t="s" r="A212" s="6">
-        <v>13</v>
-      </c>
-      <c r="B212" s="7">
-        <v>1492</v>
-      </c>
-      <c t="s" r="C212" s="7">
-        <v>14</v>
-      </c>
+      <c r="A212" s="6"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
       <c r="D212" s="7"/>
-      <c t="s" r="E212" s="7">
-        <v>283</v>
-      </c>
-      <c r="F212" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G212" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="H212" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I212" s="7">
-        <v>285</v>
-      </c>
-      <c t="s" r="J212" s="7">
-        <v>44</v>
-      </c>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="8"/>
+      <c r="H212" s="8"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
@@ -7923,29 +7923,29 @@
         <v>13</v>
       </c>
       <c r="B213" s="7">
-        <v>439</v>
+        <v>122</v>
       </c>
       <c t="s" r="C213" s="7">
         <v>14</v>
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>90</v>
+        <v>282</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7956,45 +7956,63 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>438</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
+      <c t="s" r="A215" s="6">
+        <v>13</v>
+      </c>
+      <c r="B215" s="7">
+        <v>1492</v>
+      </c>
+      <c t="s" r="C215" s="7">
+        <v>14</v>
+      </c>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c t="s" r="E215" s="7">
+        <v>281</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H215" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I215" s="7">
+        <v>283</v>
+      </c>
+      <c t="s" r="J215" s="7">
+        <v>44</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
@@ -8004,147 +8022,147 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>989</v>
+        <v>439</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>43</v>
-      </c>
-      <c t="s" r="K216" s="7">
-        <v>144</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="K216" s="7"/>
       <c r="L216" s="7"/>
-      <c t="s" r="M216" s="7">
-        <v>241</v>
-      </c>
+      <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>715</v>
+        <v>438</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>27</v>
+        <v>255</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c t="s" r="A218" s="6">
-        <v>13</v>
-      </c>
-      <c r="B218" s="7">
-        <v>714</v>
-      </c>
-      <c t="s" r="C218" s="7">
-        <v>14</v>
-      </c>
+      <c r="A218" s="6"/>
+      <c r="B218" s="7"/>
+      <c r="C218" s="7"/>
       <c r="D218" s="7"/>
-      <c t="s" r="E218" s="7">
-        <v>287</v>
-      </c>
-      <c r="F218" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G218" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H218" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I218" s="7">
-        <v>78</v>
-      </c>
-      <c t="s" r="J218" s="7">
-        <v>37</v>
-      </c>
+      <c r="E218" s="7"/>
+      <c r="F218" s="7"/>
+      <c r="G218" s="8"/>
+      <c r="H218" s="8"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="7"/>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c r="M218" s="7"/>
     </row>
     <row r="219" ht="14.25" customHeight="1">
-      <c r="A219" s="6"/>
-      <c r="B219" s="7"/>
-      <c r="C219" s="7"/>
+      <c t="s" r="A219" s="6">
+        <v>13</v>
+      </c>
+      <c r="B219" s="7">
+        <v>989</v>
+      </c>
+      <c t="s" r="C219" s="7">
+        <v>14</v>
+      </c>
       <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
-      <c r="G219" s="8"/>
-      <c r="H219" s="8"/>
-      <c r="I219" s="7"/>
-      <c r="J219" s="7"/>
-      <c r="K219" s="7"/>
+      <c t="s" r="E219" s="7">
+        <v>285</v>
+      </c>
+      <c r="F219" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G219" s="8">
+        <v>93</v>
+      </c>
+      <c t="s" r="H219" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I219" s="7">
+        <v>286</v>
+      </c>
+      <c t="s" r="J219" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="K219" s="7">
+        <v>144</v>
+      </c>
       <c r="L219" s="7"/>
-      <c r="M219" s="7"/>
+      <c t="s" r="M219" s="7">
+        <v>241</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c t="s" r="A220" s="6">
         <v>13</v>
       </c>
       <c r="B220" s="7">
-        <v>929</v>
+        <v>715</v>
       </c>
       <c t="s" r="C220" s="7">
         <v>14</v>
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>144</v>
+        <v>287</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8155,26 +8173,26 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>928</v>
+        <v>714</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>37</v>
@@ -8184,34 +8202,16 @@
       <c r="M221" s="7"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c t="s" r="A222" s="6">
-        <v>13</v>
-      </c>
-      <c r="B222" s="7">
-        <v>1127</v>
-      </c>
-      <c t="s" r="C222" s="7">
-        <v>14</v>
-      </c>
+      <c r="A222" s="6"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="7"/>
       <c r="D222" s="7"/>
-      <c t="s" r="E222" s="7">
-        <v>290</v>
-      </c>
-      <c r="F222" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G222" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H222" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I222" s="7">
-        <v>48</v>
-      </c>
-      <c t="s" r="J222" s="7">
-        <v>242</v>
-      </c>
+      <c r="E222" s="7"/>
+      <c r="F222" s="7"/>
+      <c r="G222" s="8"/>
+      <c r="H222" s="8"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="7"/>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
@@ -8221,45 +8221,63 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>1128</v>
+        <v>929</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>60</v>
+        <v>289</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>292</v>
+        <v>144</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c r="M223" s="7"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
-      <c r="A224" s="6"/>
-      <c r="B224" s="7"/>
-      <c r="C224" s="7"/>
+      <c t="s" r="A224" s="6">
+        <v>13</v>
+      </c>
+      <c r="B224" s="7">
+        <v>928</v>
+      </c>
+      <c t="s" r="C224" s="7">
+        <v>14</v>
+      </c>
       <c r="D224" s="7"/>
-      <c r="E224" s="7"/>
-      <c r="F224" s="7"/>
-      <c r="G224" s="8"/>
-      <c r="H224" s="8"/>
-      <c r="I224" s="7"/>
-      <c r="J224" s="7"/>
+      <c t="s" r="E224" s="7">
+        <v>288</v>
+      </c>
+      <c r="F224" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G224" s="8">
+        <v>289</v>
+      </c>
+      <c t="s" r="H224" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I224" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="J224" s="7">
+        <v>37</v>
+      </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c r="M224" s="7"/>
@@ -8269,29 +8287,29 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>92</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>295</v>
+        <v>60</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>225</v>
+        <v>48</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8302,14 +8320,14 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>310</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8318,95 +8336,95 @@
         <v>17</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c r="M226" s="7"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
-      <c t="s" r="A227" s="6">
-        <v>13</v>
-      </c>
-      <c r="B227" s="7">
-        <v>309</v>
-      </c>
-      <c t="s" r="C227" s="7">
-        <v>14</v>
-      </c>
+      <c r="A227" s="6"/>
+      <c r="B227" s="7"/>
+      <c r="C227" s="7"/>
       <c r="D227" s="7"/>
-      <c t="s" r="E227" s="7">
-        <v>294</v>
-      </c>
-      <c r="F227" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G227" s="8">
-        <v>100</v>
-      </c>
-      <c t="s" r="H227" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I227" s="7">
-        <v>269</v>
-      </c>
-      <c t="s" r="J227" s="7">
-        <v>298</v>
-      </c>
+      <c r="E227" s="7"/>
+      <c r="F227" s="7"/>
+      <c r="G227" s="8"/>
+      <c r="H227" s="8"/>
+      <c r="I227" s="7"/>
+      <c r="J227" s="7"/>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
+        <v>292</v>
+      </c>
+      <c r="F228" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G228" s="8">
+        <v>293</v>
+      </c>
+      <c t="s" r="H228" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I228" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J228" s="7">
         <v>294</v>
-      </c>
-      <c r="F228" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G228" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H228" s="8">
-        <v>295</v>
-      </c>
-      <c t="s" r="I228" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J228" s="7">
-        <v>299</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="6"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
+      <c t="s" r="A229" s="6">
+        <v>13</v>
+      </c>
+      <c r="B229" s="7">
+        <v>310</v>
+      </c>
+      <c t="s" r="C229" s="7">
+        <v>14</v>
+      </c>
       <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c t="s" r="E229" s="7">
+        <v>292</v>
+      </c>
+      <c r="F229" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G229" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H229" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="I229" s="7">
+        <v>295</v>
+      </c>
+      <c t="s" r="J229" s="7">
+        <v>215</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
@@ -8416,29 +8434,29 @@
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>629</v>
+        <v>309</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8446,17 +8464,17 @@
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c t="s" r="A231" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B231" s="7">
-        <v>636</v>
+        <v>91</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8465,47 +8483,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>27</v>
+        <v>293</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c r="M231" s="7"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c t="s" r="A232" s="6">
-        <v>13</v>
-      </c>
-      <c r="B232" s="7">
-        <v>633</v>
-      </c>
-      <c t="s" r="C232" s="7">
-        <v>14</v>
-      </c>
+      <c r="A232" s="6"/>
+      <c r="B232" s="7"/>
+      <c r="C232" s="7"/>
       <c r="D232" s="7"/>
-      <c t="s" r="E232" s="7">
-        <v>300</v>
-      </c>
-      <c r="F232" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G232" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H232" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I232" s="7">
-        <v>301</v>
-      </c>
-      <c t="s" r="J232" s="7">
-        <v>130</v>
-      </c>
+      <c r="E232" s="7"/>
+      <c r="F232" s="7"/>
+      <c r="G232" s="8"/>
+      <c r="H232" s="8"/>
+      <c r="I232" s="7"/>
+      <c r="J232" s="7"/>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c r="M232" s="7"/>
@@ -8515,29 +8515,29 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>394</v>
+        <v>629</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>46</v>
+        <v>247</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8548,45 +8548,63 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>395</v>
+        <v>636</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="6"/>
-      <c r="B235" s="7"/>
-      <c r="C235" s="7"/>
+      <c t="s" r="A235" s="6">
+        <v>13</v>
+      </c>
+      <c r="B235" s="7">
+        <v>633</v>
+      </c>
+      <c t="s" r="C235" s="7">
+        <v>14</v>
+      </c>
       <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
-      <c r="G235" s="8"/>
-      <c r="H235" s="8"/>
-      <c r="I235" s="7"/>
-      <c r="J235" s="7"/>
+      <c t="s" r="E235" s="7">
+        <v>298</v>
+      </c>
+      <c r="F235" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G235" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H235" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I235" s="7">
+        <v>299</v>
+      </c>
+      <c t="s" r="J235" s="7">
+        <v>130</v>
+      </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
@@ -8596,14 +8614,14 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>825</v>
+        <v>394</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8612,13 +8630,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>303</v>
+        <v>46</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8629,63 +8647,45 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>826</v>
+        <v>395</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c r="M237" s="7"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c t="s" r="A238" s="6">
-        <v>13</v>
-      </c>
-      <c r="B238" s="7">
-        <v>876</v>
-      </c>
-      <c t="s" r="C238" s="7">
-        <v>14</v>
-      </c>
+      <c r="A238" s="6"/>
+      <c r="B238" s="7"/>
+      <c r="C238" s="7"/>
       <c r="D238" s="7"/>
-      <c t="s" r="E238" s="7">
-        <v>302</v>
-      </c>
-      <c r="F238" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G238" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H238" s="8">
-        <v>305</v>
-      </c>
-      <c t="s" r="I238" s="7">
-        <v>306</v>
-      </c>
-      <c t="s" r="J238" s="7">
-        <v>132</v>
-      </c>
+      <c r="E238" s="7"/>
+      <c r="F238" s="7"/>
+      <c r="G238" s="8"/>
+      <c r="H238" s="8"/>
+      <c r="I238" s="7"/>
+      <c r="J238" s="7"/>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c r="M238" s="7"/>
@@ -8695,45 +8695,63 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>877</v>
+        <v>825</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>305</v>
+        <v>17</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>17</v>
+        <v>265</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="A240" s="6"/>
-      <c r="B240" s="7"/>
-      <c r="C240" s="7"/>
+      <c t="s" r="A240" s="6">
+        <v>13</v>
+      </c>
+      <c r="B240" s="7">
+        <v>826</v>
+      </c>
+      <c t="s" r="C240" s="7">
+        <v>14</v>
+      </c>
       <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
-      <c r="F240" s="7"/>
-      <c r="G240" s="8"/>
-      <c r="H240" s="8"/>
-      <c r="I240" s="7"/>
-      <c r="J240" s="7"/>
+      <c t="s" r="E240" s="7">
+        <v>300</v>
+      </c>
+      <c r="F240" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G240" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="H240" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I240" s="7">
+        <v>135</v>
+      </c>
+      <c t="s" r="J240" s="7">
+        <v>302</v>
+      </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c r="M240" s="7"/>
@@ -8743,14 +8761,14 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>813</v>
+        <v>876</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8759,13 +8777,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>309</v>
+        <v>132</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8776,63 +8794,45 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>970</v>
+        <v>877</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>310</v>
+        <v>209</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c t="s" r="A243" s="6">
-        <v>13</v>
-      </c>
-      <c r="B243" s="7">
-        <v>8510</v>
-      </c>
-      <c t="s" r="C243" s="7">
-        <v>14</v>
-      </c>
+      <c r="A243" s="6"/>
+      <c r="B243" s="7"/>
+      <c r="C243" s="7"/>
       <c r="D243" s="7"/>
-      <c t="s" r="E243" s="7">
-        <v>307</v>
-      </c>
-      <c r="F243" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G243" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H243" s="8">
-        <v>42</v>
-      </c>
-      <c t="s" r="I243" s="7">
-        <v>44</v>
-      </c>
-      <c t="s" r="J243" s="7">
-        <v>46</v>
-      </c>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
+      <c r="G243" s="8"/>
+      <c r="H243" s="8"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="7"/>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
@@ -8842,29 +8842,29 @@
         <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>8511</v>
+        <v>813</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
+        <v>305</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H244" s="8">
+        <v>306</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="J244" s="7">
         <v>307</v>
-      </c>
-      <c r="F244" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>42</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>56</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>62</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8875,45 +8875,63 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>878</v>
+        <v>970</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
+        <v>306</v>
+      </c>
+      <c t="s" r="H245" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H245" s="8">
-        <v>23</v>
-      </c>
       <c t="s" r="I245" s="7">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
-      <c r="A246" s="6"/>
-      <c r="B246" s="7"/>
-      <c r="C246" s="7"/>
+      <c t="s" r="A246" s="6">
+        <v>13</v>
+      </c>
+      <c r="B246" s="7">
+        <v>8510</v>
+      </c>
+      <c t="s" r="C246" s="7">
+        <v>14</v>
+      </c>
       <c r="D246" s="7"/>
-      <c r="E246" s="7"/>
-      <c r="F246" s="7"/>
-      <c r="G246" s="8"/>
-      <c r="H246" s="8"/>
-      <c r="I246" s="7"/>
-      <c r="J246" s="7"/>
+      <c t="s" r="E246" s="7">
+        <v>305</v>
+      </c>
+      <c r="F246" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G246" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H246" s="8">
+        <v>42</v>
+      </c>
+      <c t="s" r="I246" s="7">
+        <v>44</v>
+      </c>
+      <c t="s" r="J246" s="7">
+        <v>46</v>
+      </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
@@ -8923,29 +8941,29 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>449</v>
+        <v>8511</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F247" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>313</v>
+        <v>62</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8956,63 +8974,45 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>450</v>
+        <v>878</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F248" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>112</v>
+        <v>309</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>310</v>
+        <v>51</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c t="s" r="A249" s="6">
-        <v>13</v>
-      </c>
-      <c r="B249" s="7">
-        <v>775</v>
-      </c>
-      <c t="s" r="C249" s="7">
-        <v>14</v>
-      </c>
+      <c r="A249" s="6"/>
+      <c r="B249" s="7"/>
+      <c r="C249" s="7"/>
       <c r="D249" s="7"/>
-      <c t="s" r="E249" s="7">
-        <v>312</v>
-      </c>
-      <c r="F249" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G249" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H249" s="8">
-        <v>86</v>
-      </c>
-      <c t="s" r="I249" s="7">
-        <v>235</v>
-      </c>
-      <c t="s" r="J249" s="7">
-        <v>135</v>
-      </c>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
+      <c r="G249" s="8"/>
+      <c r="H249" s="8"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="7"/>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
@@ -9022,29 +9022,29 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>772</v>
+        <v>449</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F250" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>116</v>
+        <v>311</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9055,29 +9055,29 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>1511</v>
+        <v>450</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9088,29 +9088,29 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>1518</v>
+        <v>775</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>117</v>
+        <v>235</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9121,45 +9121,63 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>169</v>
+        <v>772</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>315</v>
+        <v>153</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>316</v>
+        <v>116</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c r="A254" s="6"/>
-      <c r="B254" s="7"/>
-      <c r="C254" s="7"/>
+      <c t="s" r="A254" s="6">
+        <v>13</v>
+      </c>
+      <c r="B254" s="7">
+        <v>1511</v>
+      </c>
+      <c t="s" r="C254" s="7">
+        <v>14</v>
+      </c>
       <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
-      <c r="F254" s="7"/>
-      <c r="G254" s="8"/>
-      <c r="H254" s="8"/>
-      <c r="I254" s="7"/>
-      <c r="J254" s="7"/>
+      <c t="s" r="E254" s="7">
+        <v>310</v>
+      </c>
+      <c r="F254" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G254" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H254" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I254" s="7">
+        <v>36</v>
+      </c>
+      <c t="s" r="J254" s="7">
+        <v>312</v>
+      </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
@@ -9169,29 +9187,29 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>503</v>
+        <v>1518</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F255" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9202,63 +9220,45 @@
         <v>13</v>
       </c>
       <c r="B256" s="7">
-        <v>524</v>
+        <v>169</v>
       </c>
       <c t="s" r="C256" s="7">
         <v>14</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F256" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>184</v>
+        <v>313</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>161</v>
+        <v>314</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
-      <c t="s" r="A257" s="6">
-        <v>13</v>
-      </c>
-      <c r="B257" s="7">
-        <v>507</v>
-      </c>
-      <c t="s" r="C257" s="7">
-        <v>14</v>
-      </c>
+      <c r="A257" s="6"/>
+      <c r="B257" s="7"/>
+      <c r="C257" s="7"/>
       <c r="D257" s="7"/>
-      <c t="s" r="E257" s="7">
-        <v>317</v>
-      </c>
-      <c r="F257" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G257" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H257" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I257" s="7">
-        <v>241</v>
-      </c>
-      <c t="s" r="J257" s="7">
-        <v>247</v>
-      </c>
+      <c r="E257" s="7"/>
+      <c r="F257" s="7"/>
+      <c r="G257" s="8"/>
+      <c r="H257" s="8"/>
+      <c r="I257" s="7"/>
+      <c r="J257" s="7"/>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
@@ -9268,29 +9268,29 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H258" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H258" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="I258" s="7">
-        <v>228</v>
+        <v>30</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9301,29 +9301,29 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>405</v>
+        <v>524</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9334,45 +9334,63 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>406</v>
+        <v>507</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>46</v>
+        <v>241</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="6"/>
-      <c r="B261" s="7"/>
-      <c r="C261" s="7"/>
+      <c t="s" r="A261" s="6">
+        <v>13</v>
+      </c>
+      <c r="B261" s="7">
+        <v>510</v>
+      </c>
+      <c t="s" r="C261" s="7">
+        <v>14</v>
+      </c>
       <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
-      <c r="F261" s="7"/>
-      <c r="G261" s="8"/>
-      <c r="H261" s="8"/>
-      <c r="I261" s="7"/>
-      <c r="J261" s="7"/>
+      <c t="s" r="E261" s="7">
+        <v>315</v>
+      </c>
+      <c r="F261" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G261" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H261" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I261" s="7">
+        <v>228</v>
+      </c>
+      <c t="s" r="J261" s="7">
+        <v>106</v>
+      </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
@@ -9382,29 +9400,29 @@
         <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>823</v>
+        <v>405</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9415,29 +9433,29 @@
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>640</v>
+        <v>406</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>306</v>
+        <v>46</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9463,29 +9481,29 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>421</v>
+        <v>823</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F265" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>123</v>
+        <v>297</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9496,63 +9514,45 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>422</v>
+        <v>640</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F266" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>244</v>
+        <v>17</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c t="s" r="A267" s="6">
-        <v>13</v>
-      </c>
-      <c r="B267" s="7">
-        <v>451</v>
-      </c>
-      <c t="s" r="C267" s="7">
-        <v>14</v>
-      </c>
+      <c r="A267" s="6"/>
+      <c r="B267" s="7"/>
+      <c r="C267" s="7"/>
       <c r="D267" s="7"/>
-      <c t="s" r="E267" s="7">
-        <v>319</v>
-      </c>
-      <c r="F267" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G267" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H267" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I267" s="7">
-        <v>235</v>
-      </c>
-      <c t="s" r="J267" s="7">
-        <v>115</v>
-      </c>
+      <c r="E267" s="7"/>
+      <c r="F267" s="7"/>
+      <c r="G267" s="8"/>
+      <c r="H267" s="8"/>
+      <c r="I267" s="7"/>
+      <c r="J267" s="7"/>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
@@ -9562,29 +9562,29 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9595,29 +9595,29 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>521</v>
+        <v>422</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9628,45 +9628,63 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>518</v>
+        <v>451</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>321</v>
+        <v>235</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>322</v>
+        <v>115</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c r="M270" s="7"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="6"/>
-      <c r="B271" s="7"/>
-      <c r="C271" s="7"/>
+      <c t="s" r="A271" s="6">
+        <v>13</v>
+      </c>
+      <c r="B271" s="7">
+        <v>454</v>
+      </c>
+      <c t="s" r="C271" s="7">
+        <v>14</v>
+      </c>
       <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
-      <c r="G271" s="8"/>
-      <c r="H271" s="8"/>
-      <c r="I271" s="7"/>
-      <c r="J271" s="7"/>
+      <c t="s" r="E271" s="7">
+        <v>317</v>
+      </c>
+      <c r="F271" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G271" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H271" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I271" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J271" s="7">
+        <v>155</v>
+      </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c r="M271" s="7"/>
@@ -9676,29 +9694,29 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>224</v>
+        <v>521</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F272" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9709,63 +9727,45 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>741</v>
+        <v>518</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F273" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
-      <c t="s" r="A274" s="6">
-        <v>13</v>
-      </c>
-      <c r="B274" s="7">
-        <v>740</v>
-      </c>
-      <c t="s" r="C274" s="7">
-        <v>14</v>
-      </c>
+      <c r="A274" s="6"/>
+      <c r="B274" s="7"/>
+      <c r="C274" s="7"/>
       <c r="D274" s="7"/>
-      <c t="s" r="E274" s="7">
-        <v>323</v>
-      </c>
-      <c r="F274" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G274" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="H274" s="8">
-        <v>147</v>
-      </c>
-      <c t="s" r="I274" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="J274" s="7">
-        <v>161</v>
-      </c>
+      <c r="E274" s="7"/>
+      <c r="F274" s="7"/>
+      <c r="G274" s="8"/>
+      <c r="H274" s="8"/>
+      <c r="I274" s="7"/>
+      <c r="J274" s="7"/>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="7"/>
@@ -9775,29 +9775,29 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H275" s="8">
         <v>147</v>
       </c>
-      <c t="s" r="H275" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I275" s="7">
-        <v>241</v>
+        <v>122</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9808,29 +9808,29 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>252</v>
+        <v>741</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>286</v>
+        <v>175</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9841,29 +9841,29 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>253</v>
+        <v>740</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9874,29 +9874,29 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>298</v>
+        <v>19</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9907,45 +9907,63 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>139</v>
+        <v>284</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c r="M279" s="7"/>
     </row>
     <row r="280" ht="15" customHeight="1">
-      <c r="A280" s="6"/>
-      <c r="B280" s="7"/>
-      <c r="C280" s="7"/>
+      <c t="s" r="A280" s="6">
+        <v>13</v>
+      </c>
+      <c r="B280" s="7">
+        <v>253</v>
+      </c>
+      <c t="s" r="C280" s="7">
+        <v>14</v>
+      </c>
       <c r="D280" s="7"/>
-      <c r="E280" s="7"/>
-      <c r="F280" s="7"/>
-      <c r="G280" s="8"/>
-      <c r="H280" s="8"/>
-      <c r="I280" s="7"/>
-      <c r="J280" s="7"/>
+      <c t="s" r="E280" s="7">
+        <v>321</v>
+      </c>
+      <c r="F280" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G280" s="8">
+        <v>126</v>
+      </c>
+      <c t="s" r="H280" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I280" s="7">
+        <v>294</v>
+      </c>
+      <c t="s" r="J280" s="7">
+        <v>149</v>
+      </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c r="M280" s="7"/>
@@ -9955,29 +9973,29 @@
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>1372</v>
+        <v>216</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F281" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -9988,63 +10006,45 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>1373</v>
+        <v>217</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F282" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>123</v>
+        <v>323</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>196</v>
+        <v>139</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c r="M282" s="7"/>
     </row>
     <row r="283" ht="14.25" customHeight="1">
-      <c t="s" r="A283" s="6">
-        <v>13</v>
-      </c>
-      <c r="B283" s="7">
-        <v>136</v>
-      </c>
-      <c t="s" r="C283" s="7">
-        <v>14</v>
-      </c>
+      <c r="A283" s="6"/>
+      <c r="B283" s="7"/>
+      <c r="C283" s="7"/>
       <c r="D283" s="7"/>
-      <c t="s" r="E283" s="7">
-        <v>326</v>
-      </c>
-      <c r="F283" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G283" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H283" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I283" s="7">
-        <v>33</v>
-      </c>
-      <c t="s" r="J283" s="7">
-        <v>21</v>
-      </c>
+      <c r="E283" s="7"/>
+      <c r="F283" s="7"/>
+      <c r="G283" s="8"/>
+      <c r="H283" s="8"/>
+      <c r="I283" s="7"/>
+      <c r="J283" s="7"/>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c r="M283" s="7"/>
@@ -10054,29 +10054,29 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>903</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>240</v>
+        <v>325</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>282</v>
+        <v>326</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10087,45 +10087,63 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>904</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>240</v>
+        <v>325</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="6"/>
-      <c r="B286" s="7"/>
-      <c r="C286" s="7"/>
+      <c t="s" r="A286" s="6">
+        <v>13</v>
+      </c>
+      <c r="B286" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="C286" s="7">
+        <v>14</v>
+      </c>
       <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
-      <c r="F286" s="7"/>
-      <c r="G286" s="8"/>
-      <c r="H286" s="8"/>
-      <c r="I286" s="7"/>
-      <c r="J286" s="7"/>
+      <c t="s" r="E286" s="7">
+        <v>324</v>
+      </c>
+      <c r="F286" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G286" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H286" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I286" s="7">
+        <v>33</v>
+      </c>
+      <c t="s" r="J286" s="7">
+        <v>21</v>
+      </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c r="M286" s="7"/>
@@ -10135,29 +10153,29 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F287" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>29</v>
+        <v>280</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10168,63 +10186,45 @@
         <v>13</v>
       </c>
       <c r="B288" s="7">
-        <v>703</v>
+        <v>904</v>
       </c>
       <c t="s" r="C288" s="7">
         <v>14</v>
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F288" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
     </row>
     <row r="289" ht="14.25" customHeight="1">
-      <c t="s" r="A289" s="6">
-        <v>13</v>
-      </c>
-      <c r="B289" s="7">
-        <v>704</v>
-      </c>
-      <c t="s" r="C289" s="7">
-        <v>14</v>
-      </c>
+      <c r="A289" s="6"/>
+      <c r="B289" s="7"/>
+      <c r="C289" s="7"/>
       <c r="D289" s="7"/>
-      <c t="s" r="E289" s="7">
-        <v>329</v>
-      </c>
-      <c r="F289" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G289" s="8">
-        <v>330</v>
-      </c>
-      <c t="s" r="H289" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I289" s="7">
-        <v>266</v>
-      </c>
-      <c t="s" r="J289" s="7">
-        <v>163</v>
-      </c>
+      <c r="E289" s="7"/>
+      <c r="F289" s="7"/>
+      <c r="G289" s="8"/>
+      <c r="H289" s="8"/>
+      <c r="I289" s="7"/>
+      <c r="J289" s="7"/>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c r="M289" s="7"/>
@@ -10234,29 +10234,29 @@
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>639</v>
+        <v>879</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H290" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H290" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I290" s="7">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10267,29 +10267,29 @@
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>3900</v>
+        <v>703</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>332</v>
+        <v>263</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10297,48 +10297,66 @@
     </row>
     <row r="292" ht="14.25" customHeight="1">
       <c t="s" r="A292" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>3901</v>
+        <v>704</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
+        <v>327</v>
+      </c>
+      <c r="F292" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G292" s="8">
+        <v>328</v>
+      </c>
+      <c t="s" r="H292" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I292" s="7">
         <v>329</v>
       </c>
-      <c r="F292" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G292" s="8">
-        <v>331</v>
-      </c>
-      <c t="s" r="H292" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I292" s="7">
-        <v>333</v>
-      </c>
       <c t="s" r="J292" s="7">
-        <v>334</v>
+        <v>163</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c r="M292" s="7"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="6"/>
-      <c r="B293" s="7"/>
-      <c r="C293" s="7"/>
+      <c t="s" r="A293" s="6">
+        <v>13</v>
+      </c>
+      <c r="B293" s="7">
+        <v>639</v>
+      </c>
+      <c t="s" r="C293" s="7">
+        <v>14</v>
+      </c>
       <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
-      <c r="F293" s="7"/>
-      <c r="G293" s="8"/>
-      <c r="H293" s="8"/>
-      <c r="I293" s="7"/>
-      <c r="J293" s="7"/>
+      <c t="s" r="E293" s="7">
+        <v>327</v>
+      </c>
+      <c r="F293" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G293" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H293" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I293" s="7">
+        <v>218</v>
+      </c>
+      <c t="s" r="J293" s="7">
+        <v>132</v>
+      </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c r="M293" s="7"/>
@@ -10348,29 +10366,29 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>128</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F294" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>188</v>
+        <v>331</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>336</v>
+        <v>192</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10378,114 +10396,114 @@
     </row>
     <row r="295" ht="15" customHeight="1">
       <c t="s" r="A295" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B295" s="7">
-        <v>137</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F295" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>185</v>
+        <v>332</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>44</v>
+        <v>333</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c t="s" r="A296" s="6">
-        <v>13</v>
-      </c>
-      <c r="B296" s="7">
-        <v>3948</v>
-      </c>
-      <c t="s" r="C296" s="7">
-        <v>14</v>
-      </c>
+      <c r="A296" s="6"/>
+      <c r="B296" s="7"/>
+      <c r="C296" s="7"/>
       <c r="D296" s="7"/>
-      <c t="s" r="E296" s="7">
-        <v>335</v>
-      </c>
-      <c r="F296" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G296" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H296" s="8">
-        <v>337</v>
-      </c>
-      <c t="s" r="I296" s="7">
-        <v>206</v>
-      </c>
-      <c t="s" r="J296" s="7">
-        <v>83</v>
-      </c>
+      <c r="E296" s="7"/>
+      <c r="F296" s="7"/>
+      <c r="G296" s="8"/>
+      <c r="H296" s="8"/>
+      <c r="I296" s="7"/>
+      <c r="J296" s="7"/>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
     </row>
     <row r="297" ht="14.25" customHeight="1">
       <c t="s" r="A297" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>3949</v>
+        <v>128</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>337</v>
+        <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>122</v>
+        <v>335</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c r="M297" s="7"/>
     </row>
     <row r="298" ht="14.25" customHeight="1">
-      <c r="A298" s="6"/>
-      <c r="B298" s="7"/>
-      <c r="C298" s="7"/>
+      <c t="s" r="A298" s="6">
+        <v>13</v>
+      </c>
+      <c r="B298" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="C298" s="7">
+        <v>14</v>
+      </c>
       <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
-      <c r="F298" s="7"/>
-      <c r="G298" s="8"/>
-      <c r="H298" s="8"/>
-      <c r="I298" s="7"/>
-      <c r="J298" s="7"/>
+      <c t="s" r="E298" s="7">
+        <v>334</v>
+      </c>
+      <c r="F298" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G298" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H298" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I298" s="7">
+        <v>185</v>
+      </c>
+      <c t="s" r="J298" s="7">
+        <v>44</v>
+      </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c r="M298" s="7"/>
@@ -10495,29 +10513,29 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>959</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F299" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>339</v>
+        <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>60</v>
+        <v>336</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>299</v>
+        <v>206</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10525,114 +10543,114 @@
     </row>
     <row r="300" ht="15" customHeight="1">
       <c t="s" r="A300" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B300" s="7">
-        <v>942</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F300" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>60</v>
+        <v>336</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>236</v>
+        <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c r="M300" s="7"/>
     </row>
     <row r="301" ht="14.25" customHeight="1">
-      <c t="s" r="A301" s="6">
-        <v>13</v>
-      </c>
-      <c r="B301" s="7">
-        <v>943</v>
-      </c>
-      <c t="s" r="C301" s="7">
-        <v>14</v>
-      </c>
+      <c r="A301" s="6"/>
+      <c r="B301" s="7"/>
+      <c r="C301" s="7"/>
       <c r="D301" s="7"/>
-      <c t="s" r="E301" s="7">
-        <v>338</v>
-      </c>
-      <c r="F301" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G301" s="8">
-        <v>236</v>
-      </c>
-      <c t="s" r="H301" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I301" s="7">
-        <v>56</v>
-      </c>
-      <c t="s" r="J301" s="7">
-        <v>210</v>
-      </c>
+      <c r="E301" s="7"/>
+      <c r="F301" s="7"/>
+      <c r="G301" s="8"/>
+      <c r="H301" s="8"/>
+      <c r="I301" s="7"/>
+      <c r="J301" s="7"/>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c r="M301" s="7"/>
     </row>
     <row r="302" ht="14.25" customHeight="1">
       <c t="s" r="A302" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B302" s="7">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
+        <v>337</v>
+      </c>
+      <c r="F302" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G302" s="8">
         <v>338</v>
       </c>
-      <c r="F302" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G302" s="8">
-        <v>60</v>
-      </c>
       <c t="s" r="H302" s="8">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>174</v>
+        <v>339</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c r="M302" s="7"/>
     </row>
     <row r="303" ht="14.25" customHeight="1">
-      <c r="A303" s="6"/>
-      <c r="B303" s="7"/>
-      <c r="C303" s="7"/>
+      <c t="s" r="A303" s="6">
+        <v>13</v>
+      </c>
+      <c r="B303" s="7">
+        <v>942</v>
+      </c>
+      <c t="s" r="C303" s="7">
+        <v>14</v>
+      </c>
       <c r="D303" s="7"/>
-      <c r="E303" s="7"/>
-      <c r="F303" s="7"/>
-      <c r="G303" s="8"/>
-      <c r="H303" s="8"/>
-      <c r="I303" s="7"/>
-      <c r="J303" s="7"/>
+      <c t="s" r="E303" s="7">
+        <v>337</v>
+      </c>
+      <c r="F303" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G303" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H303" s="8">
+        <v>236</v>
+      </c>
+      <c t="s" r="I303" s="7">
+        <v>21</v>
+      </c>
+      <c t="s" r="J303" s="7">
+        <v>46</v>
+      </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c r="M303" s="7"/>
@@ -10642,29 +10660,29 @@
         <v>13</v>
       </c>
       <c r="B304" s="7">
-        <v>463</v>
+        <v>943</v>
       </c>
       <c t="s" r="C304" s="7">
         <v>14</v>
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F304" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10672,66 +10690,48 @@
     </row>
     <row r="305" ht="15" customHeight="1">
       <c t="s" r="A305" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B305" s="7">
-        <v>464</v>
+        <v>960</v>
       </c>
       <c t="s" r="C305" s="7">
         <v>14</v>
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F305" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>306</v>
+        <v>174</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c r="M305" s="7"/>
     </row>
     <row r="306" ht="14.25" customHeight="1">
-      <c t="s" r="A306" s="6">
-        <v>13</v>
-      </c>
-      <c r="B306" s="7">
-        <v>567</v>
-      </c>
-      <c t="s" r="C306" s="7">
-        <v>14</v>
-      </c>
+      <c r="A306" s="6"/>
+      <c r="B306" s="7"/>
+      <c r="C306" s="7"/>
       <c r="D306" s="7"/>
-      <c t="s" r="E306" s="7">
-        <v>341</v>
-      </c>
-      <c r="F306" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G306" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H306" s="8">
-        <v>100</v>
-      </c>
-      <c t="s" r="I306" s="7">
-        <v>116</v>
-      </c>
-      <c t="s" r="J306" s="7">
-        <v>297</v>
-      </c>
+      <c r="E306" s="7"/>
+      <c r="F306" s="7"/>
+      <c r="G306" s="8"/>
+      <c r="H306" s="8"/>
+      <c r="I306" s="7"/>
+      <c r="J306" s="7"/>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c r="M306" s="7"/>
@@ -10741,45 +10741,63 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>568</v>
+        <v>463</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>60</v>
+        <v>328</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>156</v>
+        <v>247</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c r="M307" s="7"/>
     </row>
     <row r="308" ht="14.25" customHeight="1">
-      <c r="A308" s="6"/>
-      <c r="B308" s="7"/>
-      <c r="C308" s="7"/>
+      <c t="s" r="A308" s="6">
+        <v>13</v>
+      </c>
+      <c r="B308" s="7">
+        <v>464</v>
+      </c>
+      <c t="s" r="C308" s="7">
+        <v>14</v>
+      </c>
       <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
-      <c r="F308" s="7"/>
-      <c r="G308" s="8"/>
-      <c r="H308" s="8"/>
-      <c r="I308" s="7"/>
-      <c r="J308" s="7"/>
+      <c t="s" r="E308" s="7">
+        <v>340</v>
+      </c>
+      <c r="F308" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G308" s="8">
+        <v>328</v>
+      </c>
+      <c t="s" r="H308" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I308" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J308" s="7">
+        <v>304</v>
+      </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c r="M308" s="7"/>
@@ -10789,14 +10807,14 @@
         <v>13</v>
       </c>
       <c r="B309" s="7">
-        <v>121</v>
+        <v>567</v>
       </c>
       <c t="s" r="C309" s="7">
         <v>14</v>
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10805,13 +10823,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>124</v>
+        <v>295</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10822,63 +10840,45 @@
         <v>13</v>
       </c>
       <c r="B310" s="7">
-        <v>321</v>
+        <v>568</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>343</v>
+        <v>156</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c r="M310" s="7"/>
     </row>
     <row r="311" ht="14.25" customHeight="1">
-      <c t="s" r="A311" s="6">
-        <v>13</v>
-      </c>
-      <c r="B311" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="C311" s="7">
-        <v>14</v>
-      </c>
+      <c r="A311" s="6"/>
+      <c r="B311" s="7"/>
+      <c r="C311" s="7"/>
       <c r="D311" s="7"/>
-      <c t="s" r="E311" s="7">
-        <v>342</v>
-      </c>
-      <c r="F311" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G311" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H311" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I311" s="7">
-        <v>101</v>
-      </c>
-      <c t="s" r="J311" s="7">
-        <v>275</v>
-      </c>
+      <c r="E311" s="7"/>
+      <c r="F311" s="7"/>
+      <c r="G311" s="8"/>
+      <c r="H311" s="8"/>
+      <c r="I311" s="7"/>
+      <c r="J311" s="7"/>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c r="M311" s="7"/>
@@ -10888,29 +10888,29 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>374</v>
+        <v>121</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10921,29 +10921,29 @@
         <v>13</v>
       </c>
       <c r="B313" s="7">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c t="s" r="C313" s="7">
         <v>14</v>
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>227</v>
+        <v>31</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>268</v>
+        <v>342</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10954,29 +10954,29 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>384</v>
+        <v>330</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>255</v>
+        <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -10987,45 +10987,63 @@
         <v>13</v>
       </c>
       <c r="B315" s="7">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c t="s" r="C315" s="7">
         <v>14</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>255</v>
+        <v>17</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>17</v>
+        <v>325</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>48</v>
+        <v>343</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
     </row>
     <row r="316" ht="14.25" customHeight="1">
-      <c r="A316" s="6"/>
-      <c r="B316" s="7"/>
-      <c r="C316" s="7"/>
+      <c t="s" r="A316" s="6">
+        <v>13</v>
+      </c>
+      <c r="B316" s="7">
+        <v>375</v>
+      </c>
+      <c t="s" r="C316" s="7">
+        <v>14</v>
+      </c>
       <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
-      <c r="F316" s="7"/>
-      <c r="G316" s="8"/>
-      <c r="H316" s="8"/>
-      <c r="I316" s="7"/>
-      <c r="J316" s="7"/>
+      <c t="s" r="E316" s="7">
+        <v>341</v>
+      </c>
+      <c r="F316" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G316" s="8">
+        <v>325</v>
+      </c>
+      <c t="s" r="H316" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I316" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="J316" s="7">
+        <v>267</v>
+      </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c r="M316" s="7"/>
@@ -11035,29 +11053,29 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>887</v>
+        <v>384</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F317" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>241</v>
+        <v>36</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11068,63 +11086,45 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>882</v>
+        <v>385</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F318" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c r="M318" s="7"/>
     </row>
     <row r="319" ht="14.25" customHeight="1">
-      <c t="s" r="A319" s="6">
-        <v>13</v>
-      </c>
-      <c r="B319" s="7">
-        <v>282</v>
-      </c>
-      <c t="s" r="C319" s="7">
-        <v>14</v>
-      </c>
+      <c r="A319" s="6"/>
+      <c r="B319" s="7"/>
+      <c r="C319" s="7"/>
       <c r="D319" s="7"/>
-      <c t="s" r="E319" s="7">
-        <v>344</v>
-      </c>
-      <c r="F319" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G319" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H319" s="8">
-        <v>114</v>
-      </c>
-      <c t="s" r="I319" s="7">
-        <v>165</v>
-      </c>
-      <c t="s" r="J319" s="7">
-        <v>81</v>
-      </c>
+      <c r="E319" s="7"/>
+      <c r="F319" s="7"/>
+      <c r="G319" s="8"/>
+      <c r="H319" s="8"/>
+      <c r="I319" s="7"/>
+      <c r="J319" s="7"/>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c r="M319" s="7"/>
@@ -11134,7 +11134,7 @@
         <v>13</v>
       </c>
       <c r="B320" s="7">
-        <v>283</v>
+        <v>887</v>
       </c>
       <c t="s" r="C320" s="7">
         <v>14</v>
@@ -11147,16 +11147,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>92</v>
+        <v>343</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11167,7 +11167,7 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>162</v>
+        <v>882</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
@@ -11180,32 +11180,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c r="M321" s="7"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c r="A322" s="6"/>
-      <c r="B322" s="7"/>
-      <c r="C322" s="7"/>
+      <c t="s" r="A322" s="6">
+        <v>13</v>
+      </c>
+      <c r="B322" s="7">
+        <v>282</v>
+      </c>
+      <c t="s" r="C322" s="7">
+        <v>14</v>
+      </c>
       <c r="D322" s="7"/>
-      <c r="E322" s="7"/>
-      <c r="F322" s="7"/>
-      <c r="G322" s="8"/>
-      <c r="H322" s="8"/>
-      <c r="I322" s="7"/>
-      <c r="J322" s="7"/>
+      <c t="s" r="E322" s="7">
+        <v>344</v>
+      </c>
+      <c r="F322" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G322" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H322" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="I322" s="7">
+        <v>165</v>
+      </c>
+      <c t="s" r="J322" s="7">
+        <v>81</v>
+      </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c r="M322" s="7"/>
@@ -11215,29 +11233,29 @@
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F323" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>284</v>
+        <v>109</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11248,63 +11266,45 @@
         <v>13</v>
       </c>
       <c r="B324" s="7">
-        <v>303</v>
+        <v>162</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F324" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>347</v>
+        <v>40</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>103</v>
+        <v>345</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c r="M324" s="7"/>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c t="s" r="A325" s="6">
-        <v>13</v>
-      </c>
-      <c r="B325" s="7">
-        <v>138</v>
-      </c>
-      <c t="s" r="C325" s="7">
-        <v>14</v>
-      </c>
+      <c r="A325" s="6"/>
+      <c r="B325" s="7"/>
+      <c r="C325" s="7"/>
       <c r="D325" s="7"/>
-      <c t="s" r="E325" s="7">
-        <v>346</v>
-      </c>
-      <c r="F325" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G325" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H325" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I325" s="7">
-        <v>152</v>
-      </c>
-      <c t="s" r="J325" s="7">
-        <v>248</v>
-      </c>
+      <c r="E325" s="7"/>
+      <c r="F325" s="7"/>
+      <c r="G325" s="8"/>
+      <c r="H325" s="8"/>
+      <c r="I325" s="7"/>
+      <c r="J325" s="7"/>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c r="M325" s="7"/>
@@ -11314,7 +11314,7 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
@@ -11327,16 +11327,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>282</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>314</v>
+        <v>101</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11347,7 +11347,7 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>376</v>
+        <v>303</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
@@ -11360,16 +11360,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>117</v>
+        <v>347</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11380,7 +11380,7 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>377</v>
+        <v>138</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
@@ -11393,32 +11393,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>327</v>
+        <v>17</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>348</v>
+        <v>152</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>71</v>
+        <v>248</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c r="M328" s="7"/>
     </row>
     <row r="329" ht="14.25" customHeight="1">
-      <c r="A329" s="6"/>
-      <c r="B329" s="7"/>
-      <c r="C329" s="7"/>
+      <c t="s" r="A329" s="6">
+        <v>13</v>
+      </c>
+      <c r="B329" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="C329" s="7">
+        <v>14</v>
+      </c>
       <c r="D329" s="7"/>
-      <c r="E329" s="7"/>
-      <c r="F329" s="7"/>
-      <c r="G329" s="8"/>
-      <c r="H329" s="8"/>
-      <c r="I329" s="7"/>
-      <c r="J329" s="7"/>
+      <c t="s" r="E329" s="7">
+        <v>346</v>
+      </c>
+      <c r="F329" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G329" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H329" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I329" s="7">
+        <v>280</v>
+      </c>
+      <c t="s" r="J329" s="7">
+        <v>312</v>
+      </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c r="M329" s="7"/>
@@ -11428,29 +11446,29 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>855</v>
+        <v>376</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F330" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>247</v>
+        <v>167</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11461,78 +11479,78 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>854</v>
+        <v>377</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F331" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>146</v>
+        <v>348</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c r="M331" s="7"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
-      <c t="s" r="A332" s="6">
-        <v>13</v>
-      </c>
-      <c r="B332" s="7">
-        <v>150</v>
-      </c>
-      <c t="s" r="C332" s="7">
-        <v>14</v>
-      </c>
+      <c r="A332" s="6"/>
+      <c r="B332" s="7"/>
+      <c r="C332" s="7"/>
       <c r="D332" s="7"/>
-      <c t="s" r="E332" s="7">
-        <v>349</v>
-      </c>
-      <c r="F332" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G332" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H332" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I332" s="7">
-        <v>165</v>
-      </c>
-      <c t="s" r="J332" s="7">
-        <v>209</v>
-      </c>
+      <c r="E332" s="7"/>
+      <c r="F332" s="7"/>
+      <c r="G332" s="8"/>
+      <c r="H332" s="8"/>
+      <c r="I332" s="7"/>
+      <c r="J332" s="7"/>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c r="M332" s="7"/>
     </row>
     <row r="333" ht="14.25" customHeight="1">
-      <c r="A333" s="6"/>
-      <c r="B333" s="7"/>
-      <c r="C333" s="7"/>
+      <c t="s" r="A333" s="6">
+        <v>13</v>
+      </c>
+      <c r="B333" s="7">
+        <v>855</v>
+      </c>
+      <c t="s" r="C333" s="7">
+        <v>14</v>
+      </c>
       <c r="D333" s="7"/>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7"/>
-      <c r="G333" s="8"/>
-      <c r="H333" s="8"/>
-      <c r="I333" s="7"/>
-      <c r="J333" s="7"/>
+      <c t="s" r="E333" s="7">
+        <v>349</v>
+      </c>
+      <c r="F333" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G333" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H333" s="8">
+        <v>289</v>
+      </c>
+      <c t="s" r="I333" s="7">
+        <v>223</v>
+      </c>
+      <c t="s" r="J333" s="7">
+        <v>247</v>
+      </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c r="M333" s="7"/>
@@ -11542,29 +11560,29 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>447</v>
+        <v>854</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F334" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>60</v>
+        <v>289</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11575,63 +11593,45 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F335" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>146</v>
+        <v>209</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c r="M335" s="7"/>
     </row>
     <row r="336" ht="14.25" customHeight="1">
-      <c t="s" r="A336" s="6">
-        <v>13</v>
-      </c>
-      <c r="B336" s="7">
-        <v>407</v>
-      </c>
-      <c t="s" r="C336" s="7">
-        <v>14</v>
-      </c>
+      <c r="A336" s="6"/>
+      <c r="B336" s="7"/>
+      <c r="C336" s="7"/>
       <c r="D336" s="7"/>
-      <c t="s" r="E336" s="7">
-        <v>350</v>
-      </c>
-      <c r="F336" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G336" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H336" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="I336" s="7">
-        <v>148</v>
-      </c>
-      <c t="s" r="J336" s="7">
-        <v>35</v>
-      </c>
+      <c r="E336" s="7"/>
+      <c r="F336" s="7"/>
+      <c r="G336" s="8"/>
+      <c r="H336" s="8"/>
+      <c r="I336" s="7"/>
+      <c r="J336" s="7"/>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c r="M336" s="7"/>
@@ -11641,7 +11641,7 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
@@ -11654,16 +11654,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11674,7 +11674,7 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>7712</v>
+        <v>440</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
@@ -11687,16 +11687,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>351</v>
+        <v>146</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11704,10 +11704,10 @@
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c t="s" r="A339" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B339" s="7">
-        <v>7713</v>
+        <v>407</v>
       </c>
       <c t="s" r="C339" s="7">
         <v>14</v>
@@ -11720,32 +11720,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>337</v>
+        <v>60</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>352</v>
+        <v>35</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
     </row>
     <row r="340" ht="15" customHeight="1">
-      <c r="A340" s="6"/>
-      <c r="B340" s="7"/>
-      <c r="C340" s="7"/>
+      <c t="s" r="A340" s="6">
+        <v>13</v>
+      </c>
+      <c r="B340" s="7">
+        <v>408</v>
+      </c>
+      <c t="s" r="C340" s="7">
+        <v>14</v>
+      </c>
       <c r="D340" s="7"/>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7"/>
-      <c r="G340" s="8"/>
-      <c r="H340" s="8"/>
-      <c r="I340" s="7"/>
-      <c r="J340" s="7"/>
+      <c t="s" r="E340" s="7">
+        <v>350</v>
+      </c>
+      <c r="F340" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G340" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="H340" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I340" s="7">
+        <v>130</v>
+      </c>
+      <c t="s" r="J340" s="7">
+        <v>149</v>
+      </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c r="M340" s="7"/>
@@ -11755,29 +11773,29 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>973</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F341" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>87</v>
+        <v>237</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>108</v>
+        <v>351</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11785,76 +11803,58 @@
     </row>
     <row r="342" ht="14.25" customHeight="1">
       <c t="s" r="A342" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B342" s="7">
-        <v>814</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F342" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>314</v>
+        <v>64</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>56</v>
+        <v>352</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c r="M342" s="7"/>
     </row>
     <row r="343" ht="14.25" customHeight="1">
-      <c t="s" r="A343" s="6">
-        <v>13</v>
-      </c>
-      <c r="B343" s="7">
-        <v>3908</v>
-      </c>
-      <c t="s" r="C343" s="7">
-        <v>14</v>
-      </c>
+      <c r="A343" s="6"/>
+      <c r="B343" s="7"/>
+      <c r="C343" s="7"/>
       <c r="D343" s="7"/>
-      <c t="s" r="E343" s="7">
-        <v>353</v>
-      </c>
-      <c r="F343" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G343" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H343" s="8">
-        <v>270</v>
-      </c>
-      <c t="s" r="I343" s="7">
-        <v>354</v>
-      </c>
-      <c t="s" r="J343" s="7">
-        <v>355</v>
-      </c>
+      <c r="E343" s="7"/>
+      <c r="F343" s="7"/>
+      <c r="G343" s="8"/>
+      <c r="H343" s="8"/>
+      <c r="I343" s="7"/>
+      <c r="J343" s="7"/>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c t="s" r="A344" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B344" s="7">
-        <v>3909</v>
+        <v>973</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
@@ -11867,32 +11867,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>270</v>
+        <v>27</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>356</v>
+        <v>87</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>357</v>
+        <v>108</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
     </row>
     <row r="345" ht="15" customHeight="1">
-      <c r="A345" s="6"/>
-      <c r="B345" s="7"/>
-      <c r="C345" s="7"/>
+      <c t="s" r="A345" s="6">
+        <v>13</v>
+      </c>
+      <c r="B345" s="7">
+        <v>814</v>
+      </c>
+      <c t="s" r="C345" s="7">
+        <v>14</v>
+      </c>
       <c r="D345" s="7"/>
-      <c r="E345" s="7"/>
-      <c r="F345" s="7"/>
-      <c r="G345" s="8"/>
-      <c r="H345" s="8"/>
-      <c r="I345" s="7"/>
-      <c r="J345" s="7"/>
+      <c t="s" r="E345" s="7">
+        <v>353</v>
+      </c>
+      <c r="F345" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G345" s="8">
+        <v>306</v>
+      </c>
+      <c t="s" r="H345" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I345" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="J345" s="7">
+        <v>56</v>
+      </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c r="M345" s="7"/>
@@ -11902,29 +11920,29 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>461</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>222</v>
+        <v>354</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11932,66 +11950,48 @@
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B347" s="7">
-        <v>462</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>18</v>
+        <v>356</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>190</v>
+        <v>357</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
     </row>
     <row r="348" ht="14.25" customHeight="1">
-      <c t="s" r="A348" s="6">
-        <v>13</v>
-      </c>
-      <c r="B348" s="7">
-        <v>515</v>
-      </c>
-      <c t="s" r="C348" s="7">
-        <v>14</v>
-      </c>
+      <c r="A348" s="6"/>
+      <c r="B348" s="7"/>
+      <c r="C348" s="7"/>
       <c r="D348" s="7"/>
-      <c t="s" r="E348" s="7">
-        <v>358</v>
-      </c>
-      <c r="F348" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G348" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H348" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I348" s="7">
-        <v>281</v>
-      </c>
-      <c t="s" r="J348" s="7">
-        <v>146</v>
-      </c>
+      <c r="E348" s="7"/>
+      <c r="F348" s="7"/>
+      <c r="G348" s="8"/>
+      <c r="H348" s="8"/>
+      <c r="I348" s="7"/>
+      <c r="J348" s="7"/>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
@@ -12001,7 +12001,7 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>508</v>
+        <v>461</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
@@ -12014,16 +12014,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>60</v>
+        <v>328</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>89</v>
+        <v>297</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12034,7 +12034,7 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
@@ -12047,16 +12047,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>60</v>
+        <v>328</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12067,7 +12067,7 @@
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>442</v>
+        <v>515</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
@@ -12080,16 +12080,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>48</v>
+        <v>279</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>359</v>
+        <v>146</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12097,10 +12097,10 @@
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>958</v>
+        <v>508</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
@@ -12113,32 +12113,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>339</v>
+        <v>60</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>360</v>
+        <v>153</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c r="A353" s="6"/>
-      <c r="B353" s="7"/>
-      <c r="C353" s="7"/>
+      <c t="s" r="A353" s="6">
+        <v>13</v>
+      </c>
+      <c r="B353" s="7">
+        <v>441</v>
+      </c>
+      <c t="s" r="C353" s="7">
+        <v>14</v>
+      </c>
       <c r="D353" s="7"/>
-      <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
-      <c r="G353" s="8"/>
-      <c r="H353" s="8"/>
-      <c r="I353" s="7"/>
-      <c r="J353" s="7"/>
+      <c t="s" r="E353" s="7">
+        <v>358</v>
+      </c>
+      <c r="F353" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G353" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H353" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I353" s="7">
+        <v>155</v>
+      </c>
+      <c t="s" r="J353" s="7">
+        <v>132</v>
+      </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
@@ -12148,29 +12166,29 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>849</v>
+        <v>442</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>174</v>
+        <v>48</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>128</v>
+        <v>359</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12178,66 +12196,48 @@
     </row>
     <row r="355" ht="15" customHeight="1">
       <c t="s" r="A355" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B355" s="7">
-        <v>848</v>
+        <v>958</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>17</v>
+        <v>338</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c t="s" r="A356" s="6">
-        <v>13</v>
-      </c>
-      <c r="B356" s="7">
-        <v>352</v>
-      </c>
-      <c t="s" r="C356" s="7">
-        <v>14</v>
-      </c>
+      <c r="A356" s="6"/>
+      <c r="B356" s="7"/>
+      <c r="C356" s="7"/>
       <c r="D356" s="7"/>
-      <c t="s" r="E356" s="7">
-        <v>361</v>
-      </c>
-      <c r="F356" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G356" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H356" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I356" s="7">
-        <v>314</v>
-      </c>
-      <c t="s" r="J356" s="7">
-        <v>156</v>
-      </c>
+      <c r="E356" s="7"/>
+      <c r="F356" s="7"/>
+      <c r="G356" s="8"/>
+      <c r="H356" s="8"/>
+      <c r="I356" s="7"/>
+      <c r="J356" s="7"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
@@ -12247,7 +12247,7 @@
         <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>353</v>
+        <v>849</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
@@ -12260,16 +12260,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12280,7 +12280,7 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>652</v>
+        <v>848</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
@@ -12293,16 +12293,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12313,7 +12313,7 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>631</v>
+        <v>352</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
@@ -12326,32 +12326,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>169</v>
+        <v>312</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>351</v>
+        <v>156</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
-      <c r="A360" s="6"/>
-      <c r="B360" s="7"/>
-      <c r="C360" s="7"/>
+      <c t="s" r="A360" s="6">
+        <v>13</v>
+      </c>
+      <c r="B360" s="7">
+        <v>353</v>
+      </c>
+      <c t="s" r="C360" s="7">
+        <v>14</v>
+      </c>
       <c r="D360" s="7"/>
-      <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
-      <c r="G360" s="8"/>
-      <c r="H360" s="8"/>
-      <c r="I360" s="7"/>
-      <c r="J360" s="7"/>
+      <c t="s" r="E360" s="7">
+        <v>361</v>
+      </c>
+      <c r="F360" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G360" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H360" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I360" s="7">
+        <v>61</v>
+      </c>
+      <c t="s" r="J360" s="7">
+        <v>216</v>
+      </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c r="M360" s="7"/>
@@ -12361,29 +12379,29 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>925</v>
+        <v>652</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>224</v>
+        <v>119</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>343</v>
+        <v>120</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12394,63 +12412,45 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>693</v>
+        <v>631</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>296</v>
+        <v>169</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c r="M362" s="7"/>
     </row>
     <row r="363" ht="14.25" customHeight="1">
-      <c t="s" r="A363" s="6">
-        <v>13</v>
-      </c>
-      <c r="B363" s="7">
-        <v>692</v>
-      </c>
-      <c t="s" r="C363" s="7">
-        <v>14</v>
-      </c>
+      <c r="A363" s="6"/>
+      <c r="B363" s="7"/>
+      <c r="C363" s="7"/>
       <c r="D363" s="7"/>
-      <c t="s" r="E363" s="7">
-        <v>362</v>
-      </c>
-      <c r="F363" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G363" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="H363" s="8">
-        <v>114</v>
-      </c>
-      <c t="s" r="I363" s="7">
-        <v>117</v>
-      </c>
-      <c t="s" r="J363" s="7">
-        <v>109</v>
-      </c>
+      <c r="E363" s="7"/>
+      <c r="F363" s="7"/>
+      <c r="G363" s="8"/>
+      <c r="H363" s="8"/>
+      <c r="I363" s="7"/>
+      <c r="J363" s="7"/>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
@@ -12460,7 +12460,7 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
@@ -12473,32 +12473,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H364" s="8">
         <v>114</v>
       </c>
-      <c t="s" r="H364" s="8">
-        <v>23</v>
-      </c>
       <c t="s" r="I364" s="7">
-        <v>363</v>
+        <v>224</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>203</v>
+        <v>342</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c r="A365" s="6"/>
-      <c r="B365" s="7"/>
-      <c r="C365" s="7"/>
+      <c t="s" r="A365" s="6">
+        <v>13</v>
+      </c>
+      <c r="B365" s="7">
+        <v>693</v>
+      </c>
+      <c t="s" r="C365" s="7">
+        <v>14</v>
+      </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
-      <c r="F365" s="7"/>
-      <c r="G365" s="8"/>
-      <c r="H365" s="8"/>
-      <c r="I365" s="7"/>
-      <c r="J365" s="7"/>
+      <c t="s" r="E365" s="7">
+        <v>362</v>
+      </c>
+      <c r="F365" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G365" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="H365" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="I365" s="7">
+        <v>294</v>
+      </c>
+      <c t="s" r="J365" s="7">
+        <v>312</v>
+      </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
@@ -12508,29 +12526,29 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>501</v>
+        <v>692</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>365</v>
+        <v>117</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12541,63 +12559,45 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>514</v>
+        <v>926</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>30</v>
+        <v>363</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c t="s" r="A368" s="6">
-        <v>13</v>
-      </c>
-      <c r="B368" s="7">
-        <v>563</v>
-      </c>
-      <c t="s" r="C368" s="7">
-        <v>14</v>
-      </c>
+      <c r="A368" s="6"/>
+      <c r="B368" s="7"/>
+      <c r="C368" s="7"/>
       <c r="D368" s="7"/>
-      <c t="s" r="E368" s="7">
-        <v>364</v>
-      </c>
-      <c r="F368" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G368" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H368" s="8">
-        <v>100</v>
-      </c>
-      <c t="s" r="I368" s="7">
-        <v>184</v>
-      </c>
-      <c t="s" r="J368" s="7">
-        <v>225</v>
-      </c>
+      <c r="E368" s="7"/>
+      <c r="F368" s="7"/>
+      <c r="G368" s="8"/>
+      <c r="H368" s="8"/>
+      <c r="I368" s="7"/>
+      <c r="J368" s="7"/>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c r="M368" s="7"/>
@@ -12607,7 +12607,7 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>564</v>
+        <v>501</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
@@ -12620,16 +12620,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>134</v>
+        <v>365</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12640,7 +12640,7 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>453</v>
+        <v>514</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
@@ -12653,16 +12653,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>229</v>
+        <v>31</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12673,7 +12673,7 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>456</v>
+        <v>563</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
@@ -12686,16 +12686,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>286</v>
+        <v>184</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>24</v>
+        <v>225</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12706,7 +12706,7 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
@@ -12719,16 +12719,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>321</v>
+        <v>185</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12739,7 +12739,7 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>522</v>
+        <v>453</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
@@ -12752,32 +12752,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c r="A374" s="6"/>
-      <c r="B374" s="7"/>
-      <c r="C374" s="7"/>
+      <c t="s" r="A374" s="6">
+        <v>13</v>
+      </c>
+      <c r="B374" s="7">
+        <v>456</v>
+      </c>
+      <c t="s" r="C374" s="7">
+        <v>14</v>
+      </c>
       <c r="D374" s="7"/>
-      <c r="E374" s="7"/>
-      <c r="F374" s="7"/>
-      <c r="G374" s="8"/>
-      <c r="H374" s="8"/>
-      <c r="I374" s="7"/>
-      <c r="J374" s="7"/>
+      <c t="s" r="E374" s="7">
+        <v>364</v>
+      </c>
+      <c r="F374" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G374" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H374" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I374" s="7">
+        <v>284</v>
+      </c>
+      <c t="s" r="J374" s="7">
+        <v>24</v>
+      </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
@@ -12787,29 +12805,29 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>771</v>
+        <v>519</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F375" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
         <v>60</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>367</v>
+        <v>61</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>172</v>
+        <v>319</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12820,63 +12838,45 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>770</v>
+        <v>522</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F376" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>368</v>
+        <v>186</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>343</v>
+        <v>49</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c r="M376" s="7"/>
     </row>
     <row r="377" ht="14.25" customHeight="1">
-      <c t="s" r="A377" s="6">
-        <v>13</v>
-      </c>
-      <c r="B377" s="7">
-        <v>403</v>
-      </c>
-      <c t="s" r="C377" s="7">
-        <v>14</v>
-      </c>
+      <c r="A377" s="6"/>
+      <c r="B377" s="7"/>
+      <c r="C377" s="7"/>
       <c r="D377" s="7"/>
-      <c t="s" r="E377" s="7">
-        <v>366</v>
-      </c>
-      <c r="F377" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G377" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H377" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="I377" s="7">
-        <v>68</v>
-      </c>
-      <c t="s" r="J377" s="7">
-        <v>33</v>
-      </c>
+      <c r="E377" s="7"/>
+      <c r="F377" s="7"/>
+      <c r="G377" s="8"/>
+      <c r="H377" s="8"/>
+      <c r="I377" s="7"/>
+      <c r="J377" s="7"/>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c r="M377" s="7"/>
@@ -12886,7 +12886,7 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>404</v>
+        <v>771</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
@@ -12899,16 +12899,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>285</v>
+        <v>367</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>304</v>
+        <v>172</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12919,7 +12919,7 @@
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>423</v>
+        <v>770</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
@@ -12932,16 +12932,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>244</v>
+        <v>60</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>229</v>
+        <v>368</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>136</v>
+        <v>342</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12952,7 +12952,7 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
@@ -12965,16 +12965,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>244</v>
+        <v>60</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>297</v>
+        <v>68</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>260</v>
+        <v>33</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12985,7 +12985,7 @@
         <v>13</v>
       </c>
       <c r="B381" s="7">
-        <v>7238</v>
+        <v>404</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
@@ -12998,16 +12998,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>331</v>
+        <v>60</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>186</v>
+        <v>283</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>369</v>
+        <v>302</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13015,10 +13015,10 @@
     </row>
     <row r="382" ht="14.25" customHeight="1">
       <c t="s" r="A382" s="6">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>7239</v>
+        <v>423</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
@@ -13031,32 +13031,50 @@
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>331</v>
+        <v>60</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>370</v>
+        <v>229</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c r="M382" s="7"/>
     </row>
     <row r="383" ht="14.25" customHeight="1">
-      <c r="A383" s="6"/>
-      <c r="B383" s="7"/>
-      <c r="C383" s="7"/>
+      <c t="s" r="A383" s="6">
+        <v>13</v>
+      </c>
+      <c r="B383" s="7">
+        <v>424</v>
+      </c>
+      <c t="s" r="C383" s="7">
+        <v>14</v>
+      </c>
       <c r="D383" s="7"/>
-      <c r="E383" s="7"/>
-      <c r="F383" s="7"/>
-      <c r="G383" s="8"/>
-      <c r="H383" s="8"/>
-      <c r="I383" s="7"/>
-      <c r="J383" s="7"/>
+      <c t="s" r="E383" s="7">
+        <v>366</v>
+      </c>
+      <c r="F383" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G383" s="8">
+        <v>244</v>
+      </c>
+      <c t="s" r="H383" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I383" s="7">
+        <v>295</v>
+      </c>
+      <c t="s" r="J383" s="7">
+        <v>260</v>
+      </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c r="M383" s="7"/>
@@ -13066,29 +13084,29 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>335</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="F384" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>185</v>
+        <v>369</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13096,66 +13114,48 @@
     </row>
     <row r="385" ht="15" customHeight="1">
       <c t="s" r="A385" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B385" s="7">
-        <v>766</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="F385" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>19</v>
+        <v>370</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c r="M385" s="7"/>
     </row>
     <row r="386" ht="14.25" customHeight="1">
-      <c t="s" r="A386" s="6">
-        <v>13</v>
-      </c>
-      <c r="B386" s="7">
-        <v>767</v>
-      </c>
-      <c t="s" r="C386" s="7">
-        <v>14</v>
-      </c>
+      <c r="A386" s="6"/>
+      <c r="B386" s="7"/>
+      <c r="C386" s="7"/>
       <c r="D386" s="7"/>
-      <c t="s" r="E386" s="7">
-        <v>372</v>
-      </c>
-      <c r="F386" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G386" s="8">
-        <v>114</v>
-      </c>
-      <c t="s" r="H386" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I386" s="7">
-        <v>286</v>
-      </c>
-      <c t="s" r="J386" s="7">
-        <v>24</v>
-      </c>
+      <c r="E386" s="7"/>
+      <c r="F386" s="7"/>
+      <c r="G386" s="8"/>
+      <c r="H386" s="8"/>
+      <c r="I386" s="7"/>
+      <c r="J386" s="7"/>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c r="M386" s="7"/>
@@ -13165,7 +13165,7 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>976</v>
+        <v>335</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
@@ -13178,32 +13178,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H387" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H387" s="8">
-        <v>23</v>
-      </c>
       <c t="s" r="I387" s="7">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>373</v>
+        <v>185</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c r="M387" s="7"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c r="A388" s="6"/>
-      <c r="B388" s="7"/>
-      <c r="C388" s="7"/>
+      <c t="s" r="A388" s="6">
+        <v>13</v>
+      </c>
+      <c r="B388" s="7">
+        <v>766</v>
+      </c>
+      <c t="s" r="C388" s="7">
+        <v>14</v>
+      </c>
       <c r="D388" s="7"/>
-      <c r="E388" s="7"/>
-      <c r="F388" s="7"/>
-      <c r="G388" s="8"/>
-      <c r="H388" s="8"/>
-      <c r="I388" s="7"/>
-      <c r="J388" s="7"/>
+      <c t="s" r="E388" s="7">
+        <v>372</v>
+      </c>
+      <c r="F388" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G388" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H388" s="8">
+        <v>114</v>
+      </c>
+      <c t="s" r="I388" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J388" s="7">
+        <v>229</v>
+      </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
@@ -13213,29 +13231,29 @@
         <v>13</v>
       </c>
       <c r="B389" s="7">
-        <v>934</v>
+        <v>767</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>174</v>
+        <v>284</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13246,78 +13264,78 @@
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>935</v>
+        <v>976</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>91</v>
+        <v>373</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c t="s" r="A391" s="6">
-        <v>63</v>
-      </c>
-      <c r="B391" s="7">
-        <v>932</v>
-      </c>
-      <c t="s" r="C391" s="7">
-        <v>14</v>
-      </c>
+      <c r="A391" s="6"/>
+      <c r="B391" s="7"/>
+      <c r="C391" s="7"/>
       <c r="D391" s="7"/>
-      <c t="s" r="E391" s="7">
-        <v>374</v>
-      </c>
-      <c r="F391" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G391" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H391" s="8">
-        <v>151</v>
-      </c>
-      <c t="s" r="I391" s="7">
-        <v>179</v>
-      </c>
-      <c t="s" r="J391" s="7">
-        <v>98</v>
-      </c>
+      <c r="E391" s="7"/>
+      <c r="F391" s="7"/>
+      <c r="G391" s="8"/>
+      <c r="H391" s="8"/>
+      <c r="I391" s="7"/>
+      <c r="J391" s="7"/>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c r="M391" s="7"/>
     </row>
     <row r="392" ht="14.25" customHeight="1">
-      <c r="A392" s="6"/>
-      <c r="B392" s="7"/>
-      <c r="C392" s="7"/>
+      <c t="s" r="A392" s="6">
+        <v>13</v>
+      </c>
+      <c r="B392" s="7">
+        <v>934</v>
+      </c>
+      <c t="s" r="C392" s="7">
+        <v>14</v>
+      </c>
       <c r="D392" s="7"/>
-      <c r="E392" s="7"/>
-      <c r="F392" s="7"/>
-      <c r="G392" s="8"/>
-      <c r="H392" s="8"/>
-      <c r="I392" s="7"/>
-      <c r="J392" s="7"/>
+      <c t="s" r="E392" s="7">
+        <v>374</v>
+      </c>
+      <c r="F392" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G392" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H392" s="8">
+        <v>151</v>
+      </c>
+      <c t="s" r="I392" s="7">
+        <v>174</v>
+      </c>
+      <c t="s" r="J392" s="7">
+        <v>45</v>
+      </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c r="M392" s="7"/>
@@ -13327,29 +13345,29 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>1382</v>
+        <v>935</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13357,66 +13375,48 @@
     </row>
     <row r="394" ht="14.25" customHeight="1">
       <c t="s" r="A394" s="6">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="B394" s="7">
-        <v>1383</v>
+        <v>932</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>255</v>
+        <v>60</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>245</v>
+        <v>98</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c t="s" r="A395" s="6">
-        <v>13</v>
-      </c>
-      <c r="B395" s="7">
-        <v>1813</v>
-      </c>
-      <c t="s" r="C395" s="7">
-        <v>14</v>
-      </c>
+      <c r="A395" s="6"/>
+      <c r="B395" s="7"/>
+      <c r="C395" s="7"/>
       <c r="D395" s="7"/>
-      <c t="s" r="E395" s="7">
-        <v>375</v>
-      </c>
-      <c r="F395" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G395" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H395" s="8">
-        <v>273</v>
-      </c>
-      <c t="s" r="I395" s="7">
-        <v>68</v>
-      </c>
-      <c t="s" r="J395" s="7">
-        <v>146</v>
-      </c>
+      <c r="E395" s="7"/>
+      <c r="F395" s="7"/>
+      <c r="G395" s="8"/>
+      <c r="H395" s="8"/>
+      <c r="I395" s="7"/>
+      <c r="J395" s="7"/>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c r="M395" s="7"/>
@@ -13426,7 +13426,7 @@
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>1814</v>
+        <v>630</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
@@ -13439,16 +13439,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>273</v>
+        <v>17</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>248</v>
+        <v>125</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13459,7 +13459,7 @@
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>1831</v>
+        <v>1729</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
@@ -13472,16 +13472,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>69</v>
+        <v>343</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>117</v>
+        <v>329</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13492,7 +13492,7 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>1832</v>
+        <v>1728</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
@@ -13505,16 +13505,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13559,7 +13559,7 @@
         <v>240</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>214</v>
@@ -13592,7 +13592,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>19</v>
@@ -13625,10 +13625,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -13928,13 +13928,13 @@
         <v>17</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="K413" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
@@ -13980,7 +13980,7 @@
         <v>388</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>45</v>
@@ -14017,7 +14017,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>94</v>
@@ -14135,7 +14135,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>130</v>
@@ -14201,7 +14201,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>40</v>
@@ -14249,7 +14249,7 @@
         <v>393</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>242</v>

--- a/Data/FlightPlan/FPL_09OCT26.xlsx
+++ b/Data/FlightPlan/FPL_09OCT26.xlsx
@@ -563,7 +563,7 @@
     <t>06:50</t>
   </si>
   <si>
-    <t>09:03</t>
+    <t>09:09</t>
   </si>
   <si>
     <t>09:20</t>
@@ -815,7 +815,7 @@
     <t>VN-A636</t>
   </si>
   <si>
-    <t>08:44</t>
+    <t>08:49</t>
   </si>
   <si>
     <t>13:20</t>
@@ -890,6 +890,9 @@
     <t>09:05</t>
   </si>
   <si>
+    <t>09:13</t>
+  </si>
+  <si>
     <t>12:45</t>
   </si>
   <si>
@@ -986,6 +989,9 @@
     <t>VN-A653</t>
   </si>
   <si>
+    <t>14:15</t>
+  </si>
+  <si>
     <t>VN-A656</t>
   </si>
   <si>
@@ -1001,9 +1007,6 @@
     <t>VN-A657</t>
   </si>
   <si>
-    <t>14:15</t>
-  </si>
-  <si>
     <t>00:50</t>
   </si>
   <si>
@@ -1019,6 +1022,9 @@
     <t>06:33</t>
   </si>
   <si>
+    <t>08:23</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1058,6 +1064,9 @@
     <t>11:25</t>
   </si>
   <si>
+    <t>12:57</t>
+  </si>
+  <si>
     <t>VN-A668</t>
   </si>
   <si>
@@ -1193,6 +1202,18 @@
     <t>VN-A812</t>
   </si>
   <si>
+    <t>KZN</t>
+  </si>
+  <si>
+    <t>VN-A814</t>
+  </si>
+  <si>
+    <t>SYD</t>
+  </si>
+  <si>
+    <t>VN-A815</t>
+  </si>
+  <si>
     <t>OVB</t>
   </si>
   <si>
@@ -1202,18 +1223,6 @@
     <t>11:35</t>
   </si>
   <si>
-    <t>VN-A814</t>
-  </si>
-  <si>
-    <t>SYD</t>
-  </si>
-  <si>
-    <t>VN-A815</t>
-  </si>
-  <si>
-    <t>KZN</t>
-  </si>
-  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1235,7 +1244,7 @@
     <t>Total Record(s): 344</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 07:00</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 07:36</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -7092,7 +7101,9 @@
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
-      <c r="M182" s="7"/>
+      <c t="s" r="M182" s="7">
+        <v>245</v>
+      </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c t="s" r="A183" s="6">
@@ -8058,7 +8069,9 @@
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>293</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c t="s" r="A215" s="6">
@@ -8117,7 +8130,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>45</v>
@@ -8219,7 +8232,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8231,7 +8244,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>44</v>
@@ -8241,7 +8254,7 @@
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8256,7 +8269,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8268,7 +8281,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>112</v>
@@ -8289,7 +8302,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8337,7 +8350,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8346,7 +8359,7 @@
         <v>56</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="I224" s="7">
         <v>142</v>
@@ -8370,13 +8383,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>56</v>
@@ -8403,7 +8416,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8436,7 +8449,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8448,10 +8461,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8484,13 +8497,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
@@ -8517,7 +8530,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8529,7 +8542,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>215</v>
@@ -8550,7 +8563,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8583,7 +8596,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8592,13 +8605,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I232" s="7">
         <v>193</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8631,7 +8644,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8664,7 +8677,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8697,7 +8710,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8709,7 +8722,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>127</v>
@@ -8730,7 +8743,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8763,7 +8776,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8811,7 +8824,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8826,7 +8839,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8844,7 +8857,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8859,7 +8872,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8877,7 +8890,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8886,10 +8899,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>129</v>
@@ -8910,13 +8923,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
@@ -8958,7 +8971,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8967,7 +8980,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>119</v>
@@ -8991,19 +9004,19 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>83</v>
@@ -9024,7 +9037,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9057,7 +9070,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9090,7 +9103,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9102,7 +9115,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>52</v>
@@ -9138,7 +9151,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -9153,12 +9166,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9173,7 +9186,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
@@ -9188,7 +9201,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9206,7 +9219,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9239,7 +9252,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -9272,7 +9285,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9287,7 +9300,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9305,7 +9318,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -9338,7 +9351,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9350,10 +9363,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9386,7 +9399,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9419,7 +9432,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9452,7 +9465,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9485,7 +9498,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9518,7 +9531,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9551,7 +9564,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9599,7 +9612,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9611,14 +9624,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>125</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
-      <c r="M266" s="7"/>
+      <c t="s" r="M266" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
       <c t="s" r="A267" s="6">
@@ -9632,7 +9647,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9644,7 +9659,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>74</v>
@@ -9680,7 +9695,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9699,7 +9714,9 @@
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
-      <c r="M269" s="7"/>
+      <c t="s" r="M269" s="7">
+        <v>32</v>
+      </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c t="s" r="A270" s="6">
@@ -9713,7 +9730,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9725,7 +9742,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>109</v>
@@ -9746,7 +9763,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9779,7 +9796,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9812,7 +9829,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9845,7 +9862,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9857,10 +9874,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9893,7 +9910,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9902,13 +9919,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>240</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9926,13 +9943,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>17</v>
@@ -9959,7 +9976,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9992,7 +10009,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10025,7 +10042,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10040,7 +10057,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10073,7 +10090,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10082,10 +10099,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>90</v>
@@ -10093,7 +10110,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10108,13 +10125,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>17</v>
@@ -10127,7 +10144,9 @@
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
-      <c r="M283" s="7"/>
+      <c t="s" r="M283" s="7">
+        <v>337</v>
+      </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
       <c t="s" r="A284" s="6">
@@ -10141,7 +10160,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10174,7 +10193,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10207,7 +10226,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10255,7 +10274,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10275,7 +10294,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10290,7 +10309,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10299,7 +10318,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>269</v>
@@ -10323,13 +10342,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>27</v>
@@ -10356,7 +10375,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10389,7 +10408,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10398,10 +10417,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>193</v>
@@ -10422,22 +10441,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10470,7 +10489,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10485,7 +10504,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10503,7 +10522,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10536,7 +10555,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10545,7 +10564,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>270</v>
@@ -10569,13 +10588,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
@@ -10617,26 +10636,28 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>56</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>351</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -10650,7 +10671,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10683,7 +10704,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10716,7 +10737,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10764,7 +10785,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10773,7 +10794,7 @@
         <v>56</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>122</v>
@@ -10797,13 +10818,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>56</v>
@@ -10812,7 +10833,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10830,7 +10851,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10845,7 +10866,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10863,7 +10884,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10911,7 +10932,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10931,7 +10952,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -10946,7 +10967,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10961,7 +10982,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10979,7 +11000,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11012,7 +11033,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11021,13 +11042,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11045,13 +11066,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>17</v>
@@ -11078,7 +11099,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11111,7 +11132,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11159,7 +11180,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11196,7 +11217,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11218,7 +11239,7 @@
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11233,7 +11254,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11245,7 +11266,7 @@
         <v>145</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>159</v>
@@ -11255,7 +11276,7 @@
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11270,7 +11291,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11307,7 +11328,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11329,7 +11350,7 @@
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11359,7 +11380,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11392,7 +11413,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11404,7 +11425,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>99</v>
@@ -11425,7 +11446,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11458,7 +11479,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11473,7 +11494,7 @@
         <v>290</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11491,7 +11512,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11500,7 +11521,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I328" s="7">
         <v>113</v>
@@ -11524,19 +11545,19 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>67</v>
@@ -11572,7 +11593,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11581,7 +11602,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="I331" s="7">
         <v>223</v>
@@ -11605,13 +11626,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
@@ -11638,7 +11659,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11686,7 +11707,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11719,7 +11740,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11731,7 +11752,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>144</v>
@@ -11752,7 +11773,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11785,7 +11806,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11818,7 +11839,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11827,13 +11848,13 @@
         <v>56</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>236</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11851,13 +11872,13 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>56</v>
@@ -11866,7 +11887,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11899,7 +11920,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -11908,7 +11929,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>83</v>
@@ -11932,19 +11953,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>257</v>
@@ -11965,7 +11986,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11977,10 +11998,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11998,7 +12019,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12010,10 +12031,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12046,7 +12067,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12055,13 +12076,13 @@
         <v>56</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>222</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12081,13 +12102,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>56</v>
@@ -12114,7 +12135,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12147,7 +12168,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12180,7 +12201,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12213,7 +12234,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12228,7 +12249,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12246,7 +12267,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12255,10 +12276,10 @@
         <v>56</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>173</v>
@@ -12294,7 +12315,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12327,7 +12348,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12360,7 +12381,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12372,7 +12393,7 @@
         <v>92</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>154</v>
@@ -12393,7 +12414,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12426,7 +12447,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12459,7 +12480,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12474,7 +12495,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12507,7 +12528,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12522,12 +12543,12 @@
         <v>224</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12542,7 +12563,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12557,7 +12578,7 @@
         <v>264</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12575,7 +12596,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12608,7 +12629,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12620,7 +12641,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>204</v>
@@ -12656,7 +12677,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12668,7 +12689,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>29</v>
@@ -12676,7 +12697,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -12691,7 +12712,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12724,7 +12745,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12757,7 +12778,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12790,7 +12811,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12805,7 +12826,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12823,7 +12844,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12856,7 +12877,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12871,7 +12892,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12889,7 +12910,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12937,7 +12958,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12949,7 +12970,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>171</v>
@@ -12957,7 +12978,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -12972,7 +12993,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12984,10 +13005,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13005,7 +13026,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13038,7 +13059,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13050,10 +13071,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13071,7 +13092,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13083,7 +13104,7 @@
         <v>244</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>133</v>
@@ -13104,7 +13125,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13116,7 +13137,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>207</v>
@@ -13137,7 +13158,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13146,13 +13167,13 @@
         <v>56</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>187</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13170,22 +13191,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>56</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13218,7 +13239,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13251,7 +13272,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13266,7 +13287,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13284,7 +13305,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13317,7 +13338,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13332,7 +13353,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13365,7 +13386,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13398,7 +13419,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13431,7 +13452,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13479,7 +13500,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13512,7 +13533,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13524,7 +13545,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>228</v>
@@ -13545,7 +13566,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13593,7 +13614,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13605,7 +13626,7 @@
         <v>239</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>214</v>
@@ -13626,7 +13647,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13659,7 +13680,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13671,7 +13692,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>290</v>
@@ -13692,7 +13713,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13740,7 +13761,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -13749,7 +13770,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>222</v>
@@ -13777,13 +13798,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>82</v>
@@ -13829,7 +13850,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -13838,20 +13859,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="K406" s="7">
         <v>201</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -13874,14 +13895,14 @@
         <v>13</v>
       </c>
       <c r="B408" s="7">
-        <v>5060</v>
+        <v>5805</v>
       </c>
       <c t="s" r="C408" s="7">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -13890,50 +13911,58 @@
         <v>82</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>395</v>
-      </c>
-      <c r="K408" s="7"/>
+        <v>46</v>
+      </c>
+      <c t="s" r="K408" s="7">
+        <v>64</v>
+      </c>
       <c r="L408" s="7"/>
-      <c r="M408" s="7"/>
+      <c t="s" r="M408" s="7">
+        <v>162</v>
+      </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
       <c t="s" r="A409" s="6">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>5061</v>
+        <v>5806</v>
       </c>
       <c t="s" r="C409" s="7">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>396</v>
-      </c>
-      <c r="K409" s="7"/>
+        <v>90</v>
+      </c>
+      <c t="s" r="K409" s="7">
+        <v>270</v>
+      </c>
       <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
+      <c t="s" r="M409" s="7">
+        <v>171</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c r="A410" s="6"/>
@@ -13962,25 +13991,25 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>275</v>
       </c>
       <c t="s" r="K411" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
@@ -14007,14 +14036,14 @@
         <v>13</v>
       </c>
       <c r="B413" s="7">
-        <v>5805</v>
+        <v>5060</v>
       </c>
       <c t="s" r="C413" s="7">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14023,58 +14052,50 @@
         <v>82</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>46</v>
-      </c>
-      <c t="s" r="K413" s="7">
-        <v>64</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="K413" s="7"/>
       <c r="L413" s="7"/>
-      <c t="s" r="M413" s="7">
-        <v>162</v>
-      </c>
+      <c r="M413" s="7"/>
     </row>
     <row r="414" ht="14.25" customHeight="1">
       <c t="s" r="A414" s="6">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="B414" s="7">
-        <v>5806</v>
+        <v>5061</v>
       </c>
       <c t="s" r="C414" s="7">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>90</v>
-      </c>
-      <c t="s" r="K414" s="7">
-        <v>270</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="K414" s="7"/>
       <c r="L414" s="7"/>
-      <c t="s" r="M414" s="7">
-        <v>171</v>
-      </c>
+      <c r="M414" s="7"/>
     </row>
     <row r="415" ht="15" customHeight="1">
       <c r="A415" s="6"/>
@@ -14103,7 +14124,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14136,7 +14157,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14169,7 +14190,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14181,7 +14202,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>127</v>
@@ -14202,7 +14223,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -14214,10 +14235,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14235,7 +14256,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14283,7 +14304,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14292,7 +14313,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>225</v>
@@ -14316,19 +14337,19 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>118</v>
@@ -14339,7 +14360,7 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c t="s" r="A424" s="9">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -14359,7 +14380,7 @@
     <row r="425" ht="66" customHeight="1"/>
     <row r="426" ht="16.5" customHeight="1">
       <c t="s" r="A426" s="10">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B426" s="10"/>
       <c r="C426" s="10"/>
@@ -14372,7 +14393,7 @@
       <c r="J426" s="10"/>
       <c r="K426" s="10"/>
       <c t="s" r="L426" s="11">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M426" s="11"/>
       <c r="N426" s="11"/>

--- a/Data/FlightPlan/FPL_09OCT26.xlsx
+++ b/Data/FlightPlan/FPL_09OCT26.xlsx
@@ -71,6 +71,9 @@
     <t>13:00</t>
   </si>
   <si>
+    <t>13:50</t>
+  </si>
+  <si>
     <t>PQC</t>
   </si>
   <si>
@@ -266,225 +269,225 @@
     <t>12:50</t>
   </si>
   <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:29</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:32</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
     <t>14:05</t>
   </si>
   <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:29</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:32</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
     <t>16:15</t>
   </si>
   <si>
@@ -725,7 +728,7 @@
     <t>10:00</t>
   </si>
   <si>
-    <t>10:39</t>
+    <t>10:41</t>
   </si>
   <si>
     <t>10:45</t>
@@ -737,6 +740,12 @@
     <t>12:40</t>
   </si>
   <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
     <t>21:50</t>
   </si>
   <si>
@@ -782,7 +791,7 @@
     <t>08:25</t>
   </si>
   <si>
-    <t>09:45</t>
+    <t>09:48</t>
   </si>
   <si>
     <t>12:00</t>
@@ -848,6 +857,9 @@
     <t>08:57</t>
   </si>
   <si>
+    <t>10:27</t>
+  </si>
+  <si>
     <t>16:05</t>
   </si>
   <si>
@@ -890,9 +902,6 @@
     <t>VN-A642</t>
   </si>
   <si>
-    <t>09:48</t>
-  </si>
-  <si>
     <t>12:10</t>
   </si>
   <si>
@@ -944,9 +953,6 @@
     <t>PER</t>
   </si>
   <si>
-    <t>17:10</t>
-  </si>
-  <si>
     <t>08:55</t>
   </si>
   <si>
@@ -968,9 +974,6 @@
     <t>HKG</t>
   </si>
   <si>
-    <t>15:10</t>
-  </si>
-  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1115,15 +1118,18 @@
     <t>VN-A670</t>
   </si>
   <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
     <t>15:05</t>
   </si>
   <si>
     <t>VN-A672</t>
   </si>
   <si>
-    <t>11:00</t>
-  </si>
-  <si>
     <t>20:15</t>
   </si>
   <si>
@@ -1133,6 +1139,9 @@
     <t>VN-A675</t>
   </si>
   <si>
+    <t>10:54</t>
+  </si>
+  <si>
     <t>00:20</t>
   </si>
   <si>
@@ -1232,6 +1241,9 @@
     <t>VN-A699</t>
   </si>
   <si>
+    <t>10:17</t>
+  </si>
+  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1292,7 +1304,7 @@
     <t>Total Record(s): 344</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 08:36</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 08:50</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1872,7 +1884,9 @@
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c t="s" r="M7" s="7">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c t="s" r="A8" s="6">
@@ -1895,13 +1909,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H8" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I8" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c t="s" r="J8" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -1925,16 +1939,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G9" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H9" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I9" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c t="s" r="J9" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1967,27 +1981,27 @@
       </c>
       <c r="D11" s="7"/>
       <c t="s" r="E11" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G11" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H11" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I11" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="J11" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c t="s" r="M11" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -2002,7 +2016,7 @@
       </c>
       <c r="D12" s="7"/>
       <c t="s" r="E12" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="7">
         <v>321</v>
@@ -2011,18 +2025,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H12" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I12" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="J12" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c t="s" r="M12" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -2037,22 +2051,22 @@
       </c>
       <c r="D13" s="7"/>
       <c t="s" r="E13" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G13" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H13" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="I13" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c t="s" r="J13" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -2070,22 +2084,22 @@
       </c>
       <c r="D14" s="7"/>
       <c t="s" r="E14" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G14" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="H14" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I14" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J14" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2103,22 +2117,22 @@
       </c>
       <c r="D15" s="7"/>
       <c t="s" r="E15" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G15" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H15" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="I15" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c t="s" r="J15" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -2136,22 +2150,22 @@
       </c>
       <c r="D16" s="7"/>
       <c t="s" r="E16" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G16" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="H16" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I16" s="7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c t="s" r="J16" s="7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -2184,7 +2198,7 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
@@ -2193,13 +2207,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H18" s="8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2217,22 +2231,22 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G19" s="8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="H19" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2250,7 +2264,7 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
@@ -2259,13 +2273,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H20" s="8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2283,22 +2297,22 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G21" s="8">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c t="s" r="H21" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2327,26 +2341,26 @@
         <v>24</v>
       </c>
       <c t="s" r="C23" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G23" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="H23" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2354,7 +2368,7 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c t="s" r="A24" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="7">
         <v>938</v>
@@ -2364,22 +2378,22 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G24" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H24" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2412,22 +2426,22 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G26" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2445,22 +2459,22 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G27" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="H27" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2468,7 +2482,7 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c t="s" r="A28" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" s="7">
         <v>920</v>
@@ -2478,22 +2492,22 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G28" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H28" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2526,29 +2540,29 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G30" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="K30" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L30" s="7"/>
       <c t="s" r="M30" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
@@ -2563,29 +2577,29 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
+        <v>75</v>
+      </c>
+      <c t="s" r="H31" s="8">
         <v>74</v>
       </c>
-      <c t="s" r="H31" s="8">
-        <v>73</v>
-      </c>
       <c t="s" r="I31" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="K31" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L31" s="7"/>
       <c t="s" r="M31" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -2615,27 +2629,27 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c t="s" r="M33" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
@@ -2650,22 +2664,22 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2683,7 +2697,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2692,13 +2706,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2706,7 +2720,7 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c t="s" r="A36" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36" s="7">
         <v>896</v>
@@ -2716,22 +2730,22 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2764,22 +2778,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2797,22 +2811,22 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2830,22 +2844,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2863,22 +2877,22 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2911,7 +2925,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2920,18 +2934,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -2946,22 +2960,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2979,7 +2993,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2988,13 +3002,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3012,22 +3026,22 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3045,7 +3059,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3060,7 +3074,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -3078,7 +3092,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3111,7 +3125,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3120,13 +3134,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3144,13 +3158,13 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>17</v>
@@ -3201,13 +3215,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I52" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3231,7 +3245,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>17</v>
@@ -3240,7 +3254,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3267,7 +3281,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I54" s="7">
         <v>120</v>
@@ -3297,13 +3311,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>122</v>
@@ -3333,10 +3347,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="J56" s="7">
         <v>123</v>
@@ -3363,7 +3377,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>17</v>
@@ -3414,7 +3428,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I59" s="7">
         <v>127</v>
@@ -3446,7 +3460,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>17</v>
@@ -3490,7 +3504,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3523,7 +3537,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3589,7 +3603,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3628,13 +3642,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>140</v>
@@ -3661,13 +3675,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>141</v>
@@ -3736,7 +3750,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3775,7 +3789,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>17</v>
@@ -3813,7 +3827,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>150</v>
@@ -3823,7 +3837,9 @@
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
+      <c t="s" r="M72" s="7">
+        <v>76</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c t="s" r="A73" s="6">
@@ -3843,7 +3859,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>17</v>
@@ -3852,7 +3868,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3885,7 +3901,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3960,7 +3976,7 @@
         <v>156</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I77" s="7">
         <v>18</v>
@@ -3971,7 +3987,7 @@
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -3992,16 +4008,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4028,13 +4044,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4058,16 +4074,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4075,7 +4091,7 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B81" s="7">
         <v>910</v>
@@ -4091,13 +4107,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>128</v>
@@ -4133,27 +4149,27 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I83" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4168,22 +4184,22 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4201,7 +4217,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4210,13 +4226,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4234,22 +4250,22 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4267,7 +4283,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4276,13 +4292,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4315,29 +4331,29 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="K89" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4352,22 +4368,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4385,7 +4401,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4394,13 +4410,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4418,22 +4434,22 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4447,26 +4463,26 @@
         <v>7706</v>
       </c>
       <c t="s" r="C93" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4474,32 +4490,32 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c t="s" r="A94" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B94" s="7">
         <v>7706</v>
       </c>
       <c t="s" r="C94" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4532,7 +4548,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4544,15 +4560,15 @@
         <v>133</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4567,7 +4583,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4579,7 +4595,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>151</v>
@@ -4600,7 +4616,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4609,13 +4625,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4633,22 +4649,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4656,7 +4672,7 @@
     </row>
     <row r="100" ht="15" customHeight="1">
       <c t="s" r="A100" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B100" s="7">
         <v>862</v>
@@ -4666,7 +4682,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4675,13 +4691,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4714,22 +4730,22 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4747,7 +4763,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4756,13 +4772,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4770,7 +4786,7 @@
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c t="s" r="A104" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B104" s="7">
         <v>821</v>
@@ -4780,22 +4796,22 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4818,7 +4834,7 @@
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c t="s" r="A106" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B106" s="7">
         <v>828</v>
@@ -4828,7 +4844,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4840,10 +4856,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4876,16 +4892,16 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>134</v>
@@ -4894,11 +4910,11 @@
         <v>140</v>
       </c>
       <c t="s" r="K108" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -4909,20 +4925,20 @@
         <v>5068</v>
       </c>
       <c t="s" r="C109" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>112</v>
@@ -4942,26 +4958,26 @@
         <v>5068</v>
       </c>
       <c t="s" r="C110" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4969,32 +4985,32 @@
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c t="s" r="A111" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B111" s="7">
         <v>5069</v>
       </c>
       <c t="s" r="C111" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5027,7 +5043,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5036,10 +5052,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>134</v>
@@ -5060,22 +5076,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5093,7 +5109,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5102,13 +5118,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5126,22 +5142,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5159,7 +5175,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5168,13 +5184,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5192,19 +5208,19 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>145</v>
@@ -5240,7 +5256,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5249,18 +5265,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5275,22 +5291,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5308,22 +5324,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5341,22 +5357,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5364,7 +5380,7 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c t="s" r="A124" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B124" s="7">
         <v>868</v>
@@ -5374,7 +5390,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5383,10 +5399,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>129</v>
@@ -5418,26 +5434,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5451,26 +5467,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C127" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5488,22 +5504,22 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5536,7 +5552,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5545,10 +5561,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>140</v>
@@ -5569,13 +5585,13 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
@@ -5584,7 +5600,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5602,7 +5618,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5611,13 +5627,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5635,22 +5651,22 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5668,7 +5684,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5680,10 +5696,10 @@
         <v>156</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5716,29 +5732,29 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="K136" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -5753,22 +5769,22 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5786,22 +5802,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5819,22 +5835,22 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5867,7 +5883,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5876,18 +5892,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>147</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -5902,27 +5918,27 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -5937,7 +5953,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5946,17 +5962,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>240</v>
-      </c>
-      <c r="K143" s="7"/>
+        <v>241</v>
+      </c>
+      <c t="s" r="K143" s="7">
+        <v>151</v>
+      </c>
       <c r="L143" s="7"/>
-      <c r="M143" s="7"/>
+      <c t="s" r="M143" s="7">
+        <v>218</v>
+      </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c t="s" r="A144" s="6">
@@ -5970,26 +5990,30 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>153</v>
       </c>
-      <c r="K144" s="7"/>
+      <c t="s" r="K144" s="7">
+        <v>95</v>
+      </c>
       <c r="L144" s="7"/>
-      <c r="M144" s="7"/>
+      <c t="s" r="M144" s="7">
+        <v>47</v>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c t="s" r="A145" s="6">
@@ -6003,16 +6027,16 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I145" s="7">
         <v>112</v>
@@ -6020,9 +6044,13 @@
       <c t="s" r="J145" s="7">
         <v>121</v>
       </c>
-      <c r="K145" s="7"/>
+      <c t="s" r="K145" s="7">
+        <v>243</v>
+      </c>
       <c r="L145" s="7"/>
-      <c r="M145" s="7"/>
+      <c t="s" r="M145" s="7">
+        <v>87</v>
+      </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c t="s" r="A146" s="6">
@@ -6036,13 +6064,13 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>17</v>
@@ -6051,11 +6079,15 @@
         <v>141</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>48</v>
-      </c>
-      <c r="K146" s="7"/>
+        <v>49</v>
+      </c>
+      <c t="s" r="K146" s="7">
+        <v>244</v>
+      </c>
       <c r="L146" s="7"/>
-      <c r="M146" s="7"/>
+      <c t="s" r="M146" s="7">
+        <v>122</v>
+      </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c t="s" r="A147" s="6">
@@ -6069,7 +6101,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6078,13 +6110,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6117,19 +6149,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>19</v>
@@ -6150,22 +6182,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6183,22 +6215,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6216,22 +6248,22 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6249,22 +6281,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6297,7 +6329,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6306,18 +6338,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6332,19 +6364,19 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>18</v>
@@ -6352,7 +6384,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6367,22 +6399,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
+        <v>251</v>
+      </c>
+      <c r="F157" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G157" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H157" s="8">
+        <v>255</v>
+      </c>
+      <c t="s" r="I157" s="7">
         <v>248</v>
       </c>
-      <c r="F157" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G157" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H157" s="8">
-        <v>252</v>
-      </c>
-      <c t="s" r="I157" s="7">
-        <v>245</v>
-      </c>
       <c t="s" r="J157" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6400,22 +6432,22 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6433,7 +6465,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6442,13 +6474,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6466,13 +6498,13 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>17</v>
@@ -6481,7 +6513,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6514,7 +6546,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6523,18 +6555,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6549,22 +6581,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6582,7 +6614,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6591,10 +6623,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>19</v>
@@ -6615,22 +6647,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6648,22 +6680,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6696,7 +6728,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6705,18 +6737,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6731,19 +6763,19 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>134</v>
@@ -6764,7 +6796,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6776,10 +6808,10 @@
         <v>133</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6797,7 +6829,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6809,7 +6841,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>154</v>
@@ -6830,7 +6862,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6842,10 +6874,10 @@
         <v>152</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6863,7 +6895,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6875,7 +6907,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>144</v>
@@ -6911,7 +6943,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6920,18 +6952,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -6946,22 +6978,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6979,7 +7011,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6988,13 +7020,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7012,19 +7044,19 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>115</v>
@@ -7045,7 +7077,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7054,13 +7086,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7093,7 +7125,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7102,18 +7134,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7128,27 +7160,27 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7163,7 +7195,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7172,13 +7204,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7196,22 +7228,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7229,7 +7261,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7238,10 +7270,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>122</v>
@@ -7262,13 +7294,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
@@ -7310,7 +7342,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7319,18 +7351,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7345,26 +7377,28 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
-      <c r="M189" s="7"/>
+      <c t="s" r="M189" s="7">
+        <v>282</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
@@ -7378,19 +7412,19 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>135</v>
@@ -7411,22 +7445,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7444,22 +7478,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7477,19 +7511,19 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>124</v>
@@ -7510,22 +7544,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7533,7 +7567,7 @@
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B195" s="7">
         <v>7527</v>
@@ -7543,22 +7577,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7591,27 +7625,27 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7626,22 +7660,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7659,22 +7693,22 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7692,22 +7726,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
+        <v>288</v>
+      </c>
+      <c r="F200" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G200" s="8">
+        <v>292</v>
+      </c>
+      <c t="s" r="H200" s="8">
+        <v>58</v>
+      </c>
+      <c t="s" r="I200" s="7">
         <v>284</v>
       </c>
-      <c r="F200" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G200" s="8">
-        <v>288</v>
-      </c>
-      <c t="s" r="H200" s="8">
-        <v>57</v>
-      </c>
-      <c t="s" r="I200" s="7">
-        <v>280</v>
-      </c>
       <c t="s" r="J200" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7715,7 +7749,7 @@
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B201" s="7">
         <v>982</v>
@@ -7725,19 +7759,19 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>128</v>
@@ -7773,19 +7807,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>18</v>
@@ -7793,7 +7827,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -7808,7 +7842,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7817,17 +7851,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>291</v>
-      </c>
-      <c r="K204" s="7"/>
+        <v>295</v>
+      </c>
+      <c t="s" r="K204" s="7">
+        <v>290</v>
+      </c>
       <c r="L204" s="7"/>
-      <c r="M204" s="7"/>
+      <c t="s" r="M204" s="7">
+        <v>77</v>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c t="s" r="A205" s="6">
@@ -7841,22 +7879,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7889,7 +7927,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7901,15 +7939,15 @@
         <v>152</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>293</v>
+        <v>260</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -7924,7 +7962,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7939,7 +7977,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7957,7 +7995,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7966,13 +8004,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7990,22 +8028,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8038,7 +8076,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8047,18 +8085,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8073,22 +8111,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8106,22 +8144,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8139,22 +8177,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8172,22 +8210,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8220,29 +8258,29 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="K218" s="7">
         <v>150</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8257,19 +8295,19 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>121</v>
@@ -8290,22 +8328,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8338,16 +8376,16 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="I222" s="7">
         <v>150</v>
@@ -8357,7 +8395,9 @@
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
-      <c r="M222" s="7"/>
+      <c t="s" r="M222" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c t="s" r="A223" s="6">
@@ -8371,22 +8411,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8404,22 +8444,22 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8437,7 +8477,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8446,13 +8486,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8485,22 +8525,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8518,7 +8558,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8527,13 +8567,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8551,22 +8591,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8574,7 +8614,7 @@
     </row>
     <row r="230" ht="15" customHeight="1">
       <c t="s" r="A230" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B230" s="7">
         <v>91</v>
@@ -8584,7 +8624,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8593,13 +8633,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8632,22 +8672,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8665,7 +8705,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8674,13 +8714,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8698,19 +8738,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>136</v>
@@ -8731,7 +8771,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8740,13 +8780,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8764,22 +8804,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8812,7 +8852,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8821,13 +8861,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8845,13 +8885,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>17</v>
@@ -8860,7 +8900,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8878,7 +8918,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8887,10 +8927,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>138</v>
@@ -8911,22 +8951,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8944,7 +8984,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8953,13 +8993,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8967,7 +9007,7 @@
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c t="s" r="A243" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B243" s="7">
         <v>859</v>
@@ -8977,22 +9017,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9025,7 +9065,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9034,18 +9074,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9060,22 +9100,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9093,22 +9133,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9126,22 +9166,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9159,22 +9199,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9207,27 +9247,27 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9242,22 +9282,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9275,19 +9315,19 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>140</v>
@@ -9308,19 +9348,19 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>121</v>
@@ -9341,22 +9381,22 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9374,22 +9414,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I256" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9407,22 +9447,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9455,27 +9495,27 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9490,22 +9530,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9523,22 +9563,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9556,19 +9596,19 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>112</v>
@@ -9589,22 +9629,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>111</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9622,7 +9662,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9631,13 +9671,13 @@
         <v>111</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9670,7 +9710,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9682,15 +9722,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9705,7 +9745,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9714,13 +9754,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9753,27 +9793,27 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -9788,19 +9828,19 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>119</v>
@@ -9821,19 +9861,19 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>120</v>
@@ -9854,22 +9894,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>112</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9887,22 +9927,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9920,22 +9960,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9968,7 +10008,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9977,13 +10017,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10001,22 +10041,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10034,7 +10074,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10043,13 +10083,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10067,22 +10107,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10100,7 +10140,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10109,13 +10149,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10148,7 +10188,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10157,18 +10197,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10183,13 +10223,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>17</v>
@@ -10198,12 +10238,12 @@
         <v>128</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10218,7 +10258,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10227,13 +10267,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10251,22 +10291,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10284,22 +10324,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10332,27 +10372,27 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10367,22 +10407,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10400,22 +10440,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10433,19 +10473,19 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>138</v>
@@ -10466,7 +10506,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10475,13 +10515,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10489,7 +10529,7 @@
     </row>
     <row r="293" ht="14.25" customHeight="1">
       <c t="s" r="A293" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B293" s="7">
         <v>3901</v>
@@ -10499,22 +10539,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10547,7 +10587,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10556,13 +10596,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10580,22 +10620,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10613,7 +10653,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10622,13 +10662,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10636,7 +10676,7 @@
     </row>
     <row r="298" ht="14.25" customHeight="1">
       <c t="s" r="A298" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B298" s="7">
         <v>3949</v>
@@ -10646,19 +10686,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>127</v>
@@ -10694,27 +10734,27 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -10729,22 +10769,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10762,22 +10802,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10795,19 +10835,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>147</v>
@@ -10843,22 +10883,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>131</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10876,22 +10916,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10909,22 +10949,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10942,22 +10982,22 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10990,19 +11030,19 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>130</v>
@@ -11010,7 +11050,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11025,7 +11065,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11034,13 +11074,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11058,22 +11098,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11091,7 +11131,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11100,13 +11140,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11124,22 +11164,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11157,7 +11197,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11166,13 +11206,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11190,22 +11230,22 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11238,7 +11278,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11253,14 +11293,14 @@
         <v>127</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="K318" s="7">
         <v>148</v>
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>18</v>
+        <v>369</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11275,7 +11315,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11284,20 +11324,20 @@
         <v>152</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="K319" s="7">
-        <v>237</v>
+        <v>370</v>
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>360</v>
+        <v>218</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11312,29 +11352,29 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>152</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="K320" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11349,7 +11389,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11361,17 +11401,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>19</v>
       </c>
       <c t="s" r="K321" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11386,7 +11426,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11395,20 +11435,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="K322" s="7">
         <v>154</v>
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11438,7 +11478,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11447,13 +11487,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11471,13 +11511,13 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
@@ -11486,7 +11526,7 @@
         <v>370</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11504,7 +11544,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11513,13 +11553,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11537,22 +11577,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11570,7 +11610,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11579,13 +11619,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I328" s="7">
         <v>122</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11603,22 +11643,22 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11651,7 +11691,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11660,13 +11700,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11684,19 +11724,19 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>141</v>
@@ -11717,7 +11757,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11726,13 +11766,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11740,7 +11780,7 @@
     </row>
     <row r="334" ht="14.25" customHeight="1">
       <c t="s" r="A334" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B334" s="7">
         <v>960</v>
@@ -11750,22 +11790,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11798,26 +11838,28 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>119</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>376</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
@@ -11831,22 +11873,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11864,13 +11906,13 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>111</v>
@@ -11879,7 +11921,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11897,7 +11939,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11906,7 +11948,7 @@
         <v>111</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>136</v>
@@ -11930,22 +11972,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11953,7 +11995,7 @@
     </row>
     <row r="341" ht="14.25" customHeight="1">
       <c t="s" r="A341" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B341" s="7">
         <v>7713</v>
@@ -11963,22 +12005,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12011,19 +12053,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>114</v>
@@ -12044,22 +12086,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12077,7 +12119,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12086,13 +12128,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12100,7 +12142,7 @@
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B346" s="7">
         <v>3909</v>
@@ -12110,22 +12152,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12158,27 +12200,27 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12193,22 +12235,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12226,22 +12268,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12259,22 +12301,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12292,19 +12334,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>138</v>
@@ -12325,22 +12367,22 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12348,7 +12390,7 @@
     </row>
     <row r="354" ht="14.25" customHeight="1">
       <c t="s" r="A354" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B354" s="7">
         <v>958</v>
@@ -12358,22 +12400,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12406,7 +12448,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12415,18 +12457,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12441,13 +12483,13 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
@@ -12456,7 +12498,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12474,7 +12516,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12483,13 +12525,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12507,22 +12549,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12540,7 +12582,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12549,7 +12591,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I360" s="7">
         <v>124</v>
@@ -12573,22 +12615,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12621,27 +12663,27 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12656,22 +12698,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>111</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12689,7 +12731,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12698,7 +12740,7 @@
         <v>111</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>122</v>
@@ -12722,22 +12764,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12770,27 +12812,27 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -12805,27 +12847,27 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -12840,22 +12882,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12873,22 +12915,22 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12906,22 +12948,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12939,22 +12981,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12972,22 +13014,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13005,22 +13047,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13053,27 +13095,27 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13088,27 +13130,27 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13123,22 +13165,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>111</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13156,7 +13198,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13165,13 +13207,13 @@
         <v>111</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13189,19 +13231,19 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>141</v>
@@ -13222,22 +13264,22 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13255,22 +13297,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13278,7 +13320,7 @@
     </row>
     <row r="384" ht="14.25" customHeight="1">
       <c t="s" r="A384" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B384" s="7">
         <v>7239</v>
@@ -13288,22 +13330,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13336,7 +13378,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13345,13 +13387,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13369,22 +13411,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13402,22 +13444,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13435,22 +13477,22 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13483,27 +13525,27 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>156</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13518,7 +13560,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13527,13 +13569,13 @@
         <v>156</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13541,7 +13583,7 @@
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c t="s" r="A393" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B393" s="7">
         <v>932</v>
@@ -13551,22 +13593,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>156</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13599,7 +13641,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13608,10 +13650,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>131</v>
@@ -13632,22 +13674,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>111</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13665,7 +13707,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13674,10 +13716,10 @@
         <v>111</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>114</v>
@@ -13713,7 +13755,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13722,17 +13764,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
-      <c r="M399" s="7"/>
+      <c t="s" r="M399" s="7">
+        <v>410</v>
+      </c>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c t="s" r="A400" s="6">
@@ -13746,19 +13790,19 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>19</v>
@@ -13779,7 +13823,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13788,13 +13832,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13812,22 +13856,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13860,29 +13904,29 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c t="s" r="K404" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -13897,29 +13941,29 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="K405" s="7">
         <v>114</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -13949,7 +13993,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -13958,20 +14002,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="K407" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -13997,33 +14041,33 @@
         <v>5805</v>
       </c>
       <c t="s" r="C409" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="K409" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14034,33 +14078,33 @@
         <v>5806</v>
       </c>
       <c t="s" r="C410" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>311</v>
+        <v>244</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="K410" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14090,25 +14134,25 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="K412" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
@@ -14142,22 +14186,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14165,7 +14209,7 @@
     </row>
     <row r="415" ht="15" customHeight="1">
       <c t="s" r="A415" s="6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B415" s="7">
         <v>5061</v>
@@ -14175,22 +14219,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14223,7 +14267,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14232,18 +14276,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -14258,22 +14302,22 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14291,7 +14335,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -14300,10 +14344,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>136</v>
@@ -14324,22 +14368,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14357,7 +14401,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14366,13 +14410,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14405,7 +14449,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14414,13 +14458,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14438,19 +14482,19 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>127</v>
@@ -14461,7 +14505,7 @@
     </row>
     <row r="425" ht="16.5" customHeight="1">
       <c t="s" r="A425" s="9">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
@@ -14481,7 +14525,7 @@
     <row r="426" ht="65.25" customHeight="1"/>
     <row r="427" ht="16.5" customHeight="1">
       <c t="s" r="A427" s="10">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B427" s="10"/>
       <c r="C427" s="10"/>
@@ -14494,7 +14538,7 @@
       <c r="J427" s="10"/>
       <c r="K427" s="10"/>
       <c t="s" r="L427" s="11">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M427" s="11"/>
       <c r="N427" s="11"/>

--- a/Data/FlightPlan/FPL_09OCT26.xlsx
+++ b/Data/FlightPlan/FPL_09OCT26.xlsx
@@ -113,7 +113,7 @@
     <t>08:50</t>
   </si>
   <si>
-    <t>08:48</t>
+    <t>09:05</t>
   </si>
   <si>
     <t>MFM</t>
@@ -368,6 +368,9 @@
     <t>09:10</t>
   </si>
   <si>
+    <t>10:29</t>
+  </si>
+  <si>
     <t>10:50</t>
   </si>
   <si>
@@ -434,6 +437,9 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>14:05</t>
+  </si>
+  <si>
     <t>16:40</t>
   </si>
   <si>
@@ -464,6 +470,9 @@
     <t>08:40</t>
   </si>
   <si>
+    <t>10:38</t>
+  </si>
+  <si>
     <t>11:20</t>
   </si>
   <si>
@@ -485,9 +494,6 @@
     <t>13:05</t>
   </si>
   <si>
-    <t>14:05</t>
-  </si>
-  <si>
     <t>16:15</t>
   </si>
   <si>
@@ -515,690 +521,711 @@
     <t>11:04</t>
   </si>
   <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>14:34</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:48</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:37</t>
+  </si>
+  <si>
     <t>14:40</t>
   </si>
   <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
     <t>16:50</t>
   </si>
   <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:33</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>13:18</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
     <t>VDH</t>
   </si>
   <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
     <t>21:20</t>
   </si>
   <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>09:09</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:23</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:48</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:03</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>08:49</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>10:27</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:11</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:33</t>
-  </si>
-  <si>
-    <t>08:23</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>13:18</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:03</t>
-  </si>
-  <si>
-    <t>08:54</t>
-  </si>
-  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1241,15 +1268,15 @@
     <t>VN-A699</t>
   </si>
   <si>
-    <t>10:17</t>
-  </si>
-  <si>
     <t>VN-A810</t>
   </si>
   <si>
     <t>SVO</t>
   </si>
   <si>
+    <t>15:48</t>
+  </si>
+  <si>
     <t>VN-A811</t>
   </si>
   <si>
@@ -1268,6 +1295,9 @@
     <t>SYD</t>
   </si>
   <si>
+    <t>18:03</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1304,7 +1334,7 @@
     <t>Total Record(s): 344</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 08:50</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 09:35</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3225,7 +3255,9 @@
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
+      <c t="s" r="M52" s="7">
+        <v>119</v>
+      </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c t="s" r="A53" s="6">
@@ -3251,7 +3283,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>110</v>
@@ -3284,10 +3316,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3320,7 +3352,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3353,7 +3385,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3383,10 +3415,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3419,7 +3451,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3431,15 +3463,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3454,7 +3486,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3466,15 +3498,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3489,7 +3521,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3498,10 +3530,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>79</v>
@@ -3522,19 +3554,19 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>97</v>
@@ -3555,7 +3587,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3564,13 +3596,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3588,19 +3620,19 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H64" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>41</v>
@@ -3636,7 +3668,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3651,11 +3683,13 @@
         <v>78</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
-      <c r="M66" s="7"/>
+      <c t="s" r="M66" s="7">
+        <v>142</v>
+      </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c t="s" r="A67" s="6">
@@ -3669,7 +3703,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3684,7 +3718,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3702,7 +3736,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3711,13 +3745,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3735,19 +3769,19 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>105</v>
@@ -3783,7 +3817,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3795,15 +3829,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -3818,7 +3852,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3830,15 +3864,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>76</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -3853,7 +3887,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3865,7 +3899,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>81</v>
@@ -3886,7 +3920,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3895,10 +3929,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>38</v>
@@ -3919,22 +3953,22 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3967,13 +4001,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>58</v>
@@ -3982,7 +4016,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4002,7 +4036,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4014,10 +4048,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4035,7 +4069,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4047,10 +4081,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4068,7 +4102,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4077,13 +4111,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="I80" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4101,22 +4135,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4149,7 +4183,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4161,15 +4195,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4177,14 +4211,14 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>145</v>
+        <v>453</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4193,13 +4227,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4210,29 +4244,29 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>262</v>
+        <v>456</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c t="s" r="I85" s="7">
         <v>171</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4243,29 +4277,29 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>263</v>
+        <v>519</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4276,29 +4310,29 @@
         <v>13</v>
       </c>
       <c r="B87" s="7">
-        <v>168</v>
+        <v>522</v>
       </c>
       <c t="s" r="C87" s="7">
         <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4331,7 +4365,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4343,17 +4377,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I89" s="7">
+        <v>175</v>
+      </c>
+      <c t="s" r="J89" s="7">
+        <v>176</v>
+      </c>
+      <c t="s" r="K89" s="7">
         <v>177</v>
-      </c>
-      <c t="s" r="J89" s="7">
-        <v>178</v>
-      </c>
-      <c t="s" r="K89" s="7">
-        <v>179</v>
       </c>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4368,7 +4402,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4380,14 +4414,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>180</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
@@ -4401,7 +4437,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4413,7 +4449,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>81</v>
@@ -4434,7 +4470,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4449,7 +4485,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4463,11 +4499,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C93" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4479,10 +4515,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4496,11 +4532,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C94" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4509,13 +4545,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4548,7 +4584,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4557,10 +4593,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>33</v>
@@ -4568,7 +4604,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4583,26 +4619,28 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
+      <c t="s" r="M97" s="7">
+        <v>191</v>
+      </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c t="s" r="A98" s="6">
@@ -4616,7 +4654,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4628,7 +4666,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>59</v>
@@ -4649,7 +4687,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4661,10 +4699,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4682,7 +4720,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4694,10 +4732,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4730,7 +4768,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4742,7 +4780,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>96</v>
@@ -4763,22 +4801,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
+        <v>195</v>
+      </c>
+      <c r="F103" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G103" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H103" s="8">
         <v>197</v>
-      </c>
-      <c r="F103" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G103" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H103" s="8">
-        <v>199</v>
       </c>
       <c t="s" r="I103" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4796,22 +4834,22 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
+        <v>195</v>
+      </c>
+      <c r="F104" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G104" s="8">
         <v>197</v>
       </c>
-      <c r="F104" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G104" s="8">
+      <c t="s" r="H104" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I104" s="7">
         <v>199</v>
       </c>
-      <c t="s" r="H104" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I104" s="7">
-        <v>201</v>
-      </c>
       <c t="s" r="J104" s="7">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4844,7 +4882,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4856,10 +4894,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4892,7 +4930,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4904,17 +4942,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="K108" s="7">
         <v>78</v>
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -4925,11 +4963,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C109" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4944,7 +4982,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4958,11 +4996,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C110" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4971,13 +5009,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H110" s="8">
+        <v>205</v>
+      </c>
+      <c t="s" r="I110" s="7">
+        <v>206</v>
+      </c>
+      <c t="s" r="J110" s="7">
         <v>207</v>
-      </c>
-      <c t="s" r="I110" s="7">
-        <v>208</v>
-      </c>
-      <c t="s" r="J110" s="7">
-        <v>209</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4991,26 +5029,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C111" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
+        <v>203</v>
+      </c>
+      <c r="F111" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G111" s="8">
         <v>205</v>
-      </c>
-      <c r="F111" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G111" s="8">
-        <v>207</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5043,7 +5081,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5052,17 +5090,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
+      <c t="s" r="M113" s="7">
+        <v>212</v>
+      </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
@@ -5076,13 +5116,13 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>17</v>
@@ -5109,7 +5149,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5142,7 +5182,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5175,7 +5215,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5187,10 +5227,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I117" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J117" s="7">
         <v>214</v>
-      </c>
-      <c t="s" r="J117" s="7">
-        <v>215</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5208,7 +5248,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5220,10 +5260,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5256,7 +5296,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5268,15 +5308,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I120" s="7">
+        <v>190</v>
+      </c>
+      <c t="s" r="J120" s="7">
         <v>192</v>
-      </c>
-      <c t="s" r="J120" s="7">
-        <v>193</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5291,7 +5331,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5306,7 +5346,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5324,7 +5364,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5339,7 +5379,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5357,7 +5397,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5369,10 +5409,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5390,7 +5430,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5405,7 +5445,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5434,30 +5474,32 @@
         <v>7615</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
+        <v>219</v>
+      </c>
+      <c r="F126" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G126" s="8">
         <v>220</v>
-      </c>
-      <c r="F126" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G126" s="8">
-        <v>221</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I126" s="7">
+        <v>221</v>
+      </c>
+      <c t="s" r="J126" s="7">
         <v>222</v>
-      </c>
-      <c t="s" r="J126" s="7">
-        <v>206</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
+      <c t="s" r="M126" s="7">
+        <v>121</v>
+      </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c t="s" r="A127" s="6">
@@ -5467,11 +5509,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C127" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5504,7 +5546,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5564,14 +5606,16 @@
         <v>65</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
+      <c t="s" r="M130" s="7">
+        <v>226</v>
+      </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c t="s" r="A131" s="6">
@@ -5600,7 +5644,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5630,10 +5674,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5666,7 +5710,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5693,13 +5737,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5732,7 +5776,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5744,17 +5788,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="K136" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -5769,7 +5813,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5778,13 +5822,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5802,13 +5846,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>74</v>
@@ -5817,7 +5861,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5835,7 +5879,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5847,7 +5891,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>29</v>
@@ -5883,7 +5927,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5895,7 +5939,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>32</v>
@@ -5903,7 +5947,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -5918,7 +5962,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5933,12 +5977,12 @@
         <v>72</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -5953,7 +5997,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5965,17 +6009,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -5990,7 +6034,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6002,10 +6046,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="K144" s="7">
         <v>95</v>
@@ -6027,7 +6071,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6042,10 +6086,10 @@
         <v>112</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="K145" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
@@ -6064,7 +6108,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6076,17 +6120,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>49</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6101,7 +6145,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6113,10 +6157,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6149,7 +6193,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6158,10 +6202,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>19</v>
@@ -6182,19 +6226,19 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>38</v>
@@ -6215,7 +6259,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6230,7 +6274,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6248,7 +6292,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6260,10 +6304,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6281,7 +6325,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6293,10 +6337,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6329,7 +6373,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6338,7 +6382,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>102</v>
@@ -6349,7 +6393,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6364,19 +6408,19 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>18</v>
@@ -6384,7 +6428,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6399,7 +6443,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6408,13 +6452,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6432,13 +6476,13 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>17</v>
@@ -6465,7 +6509,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6477,7 +6521,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>90</v>
@@ -6498,7 +6542,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6546,7 +6590,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6555,18 +6599,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6581,22 +6625,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6614,7 +6658,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6626,7 +6670,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>19</v>
@@ -6647,7 +6691,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6659,10 +6703,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6680,7 +6724,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6695,7 +6739,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6728,7 +6772,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6740,15 +6784,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6763,7 +6807,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6775,14 +6819,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
-      <c r="M169" s="7"/>
+      <c t="s" r="M169" s="7">
+        <v>271</v>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c t="s" r="A170" s="6">
@@ -6796,7 +6842,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6805,13 +6851,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6829,22 +6875,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6862,7 +6908,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6871,13 +6917,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="I172" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6895,22 +6941,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6943,7 +6989,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6955,7 +7001,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>107</v>
@@ -6963,7 +7009,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -6978,7 +7024,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6993,7 +7039,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7011,7 +7057,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7023,7 +7069,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>48</v>
@@ -7044,7 +7090,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7056,7 +7102,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>115</v>
@@ -7077,7 +7123,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7089,7 +7135,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>91</v>
@@ -7125,7 +7171,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7134,18 +7180,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7160,27 +7206,27 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7195,7 +7241,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7204,7 +7250,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>66</v>
@@ -7228,13 +7274,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
@@ -7243,7 +7289,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7261,7 +7307,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7276,7 +7322,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7294,7 +7340,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7306,10 +7352,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7342,7 +7388,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7362,7 +7408,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7377,7 +7423,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7392,12 +7438,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7412,7 +7458,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7424,10 +7470,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7445,7 +7491,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7457,10 +7503,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7478,7 +7524,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7493,7 +7539,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7511,7 +7557,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7523,10 +7569,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7544,7 +7590,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7553,10 +7599,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>26</v>
@@ -7577,22 +7623,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7625,7 +7671,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7634,18 +7680,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -7660,22 +7706,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7693,7 +7739,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7702,13 +7748,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7726,19 +7772,19 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>41</v>
@@ -7759,7 +7805,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7771,10 +7817,10 @@
         <v>101</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7807,7 +7853,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7819,7 +7865,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>18</v>
@@ -7827,7 +7873,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -7842,7 +7888,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7854,13 +7900,13 @@
         <v>74</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="K204" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
@@ -7879,7 +7925,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7894,7 +7940,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7927,7 +7973,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7936,18 +7982,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -7962,22 +8008,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7995,7 +8041,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8004,10 +8050,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>80</v>
@@ -8028,19 +8074,19 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>98</v>
@@ -8076,7 +8122,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8088,15 +8134,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8111,7 +8157,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8144,7 +8190,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8156,7 +8202,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>47</v>
@@ -8177,7 +8223,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8186,10 +8232,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>98</v>
@@ -8210,13 +8256,13 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>58</v>
@@ -8258,7 +8304,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8270,17 +8316,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>46</v>
       </c>
       <c t="s" r="K218" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8295,7 +8341,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8307,10 +8353,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8328,7 +8374,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8376,7 +8422,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8385,10 +8431,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>19</v>
@@ -8396,7 +8442,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>19</v>
+        <v>160</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8411,19 +8457,19 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>40</v>
@@ -8444,7 +8490,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8459,7 +8505,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8477,7 +8523,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8489,10 +8535,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8525,13 +8571,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>17</v>
@@ -8540,7 +8586,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8558,7 +8604,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8570,7 +8616,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>223</v>
@@ -8591,7 +8637,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8603,10 +8649,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8624,7 +8670,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8633,13 +8679,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8672,7 +8718,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8687,7 +8733,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8705,7 +8751,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8717,7 +8763,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>22</v>
@@ -8738,7 +8784,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8750,10 +8796,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8771,7 +8817,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8780,10 +8826,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>49</v>
@@ -8804,19 +8850,19 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>90</v>
@@ -8852,7 +8898,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8861,13 +8907,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8885,22 +8931,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8918,7 +8964,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8927,13 +8973,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8951,22 +8997,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8984,7 +9030,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8993,13 +9039,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9017,22 +9063,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9065,7 +9111,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9074,18 +9120,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>326</v>
+        <v>46</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9100,19 +9146,19 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>95</v>
@@ -9133,7 +9179,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9166,7 +9212,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9178,7 +9224,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>60</v>
@@ -9199,7 +9245,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9211,7 +9257,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>54</v>
@@ -9247,7 +9293,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -9262,12 +9308,12 @@
         <v>105</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9282,7 +9328,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
@@ -9297,11 +9343,13 @@
         <v>118</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c r="M252" s="7"/>
+      <c t="s" r="M252" s="7">
+        <v>78</v>
+      </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
@@ -9315,7 +9363,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9327,10 +9375,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9348,7 +9396,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -9360,10 +9408,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9381,7 +9429,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9396,7 +9444,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9414,7 +9462,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -9426,10 +9474,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9447,7 +9495,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9459,10 +9507,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9495,7 +9543,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9515,7 +9563,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -9530,7 +9578,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9542,14 +9590,16 @@
         <v>58</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>341</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
@@ -9563,7 +9613,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9575,10 +9625,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9596,7 +9646,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9608,7 +9658,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>112</v>
@@ -9629,7 +9679,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9641,7 +9691,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>68</v>
@@ -9662,7 +9712,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9677,7 +9727,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9710,19 +9760,19 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>79</v>
@@ -9730,7 +9780,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9745,7 +9795,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9757,7 +9807,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>87</v>
@@ -9793,7 +9843,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9802,13 +9852,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9828,26 +9878,28 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
-      <c r="M270" s="7"/>
+      <c t="s" r="M270" s="7">
+        <v>345</v>
+      </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
       <c t="s" r="A271" s="6">
@@ -9861,7 +9913,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9873,10 +9925,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9894,7 +9946,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9909,7 +9961,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9927,7 +9979,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9939,7 +9991,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>99</v>
@@ -9960,7 +10012,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9972,10 +10024,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>340</v>
+        <v>172</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10008,7 +10060,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10020,10 +10072,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10041,7 +10093,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10053,7 +10105,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>47</v>
@@ -10074,7 +10126,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10086,7 +10138,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>98</v>
@@ -10107,7 +10159,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10122,7 +10174,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10140,7 +10192,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10155,7 +10207,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10188,7 +10240,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10197,10 +10249,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>102</v>
@@ -10208,7 +10260,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10223,27 +10275,27 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10258,7 +10310,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10291,7 +10343,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10300,10 +10352,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>25</v>
@@ -10324,19 +10376,19 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>224</v>
@@ -10372,7 +10424,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10387,12 +10439,12 @@
         <v>30</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10407,7 +10459,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10416,10 +10468,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>37</v>
@@ -10440,13 +10492,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>28</v>
@@ -10455,7 +10507,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10473,7 +10525,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10485,10 +10537,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10506,7 +10558,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10515,13 +10567,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10539,22 +10591,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10587,7 +10639,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10599,10 +10651,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10620,7 +10672,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10632,7 +10684,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>47</v>
@@ -10653,7 +10705,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10662,10 +10714,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>92</v>
@@ -10686,22 +10738,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10734,27 +10786,27 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -10769,7 +10821,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10778,7 +10830,7 @@
         <v>58</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>22</v>
@@ -10802,22 +10854,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10835,7 +10887,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10847,10 +10899,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10883,7 +10935,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10892,13 +10944,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10916,13 +10968,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>58</v>
@@ -10931,7 +10983,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10949,7 +11001,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10961,10 +11013,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10982,7 +11034,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10994,10 +11046,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11030,7 +11082,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11045,12 +11097,12 @@
         <v>54</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11065,7 +11117,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11080,11 +11132,13 @@
         <v>33</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
-      <c r="M311" s="7"/>
+      <c t="s" r="M311" s="7">
+        <v>234</v>
+      </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
       <c t="s" r="A312" s="6">
@@ -11098,7 +11152,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11113,11 +11167,15 @@
         <v>109</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>290</v>
-      </c>
-      <c r="K312" s="7"/>
+        <v>294</v>
+      </c>
+      <c t="s" r="K312" s="7">
+        <v>120</v>
+      </c>
       <c r="L312" s="7"/>
-      <c r="M312" s="7"/>
+      <c t="s" r="M312" s="7">
+        <v>362</v>
+      </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
       <c t="s" r="A313" s="6">
@@ -11131,7 +11189,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11140,13 +11198,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11164,13 +11222,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>17</v>
@@ -11179,7 +11237,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11197,7 +11255,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11206,7 +11264,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>39</v>
@@ -11230,13 +11288,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>17</v>
@@ -11278,7 +11336,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11287,20 +11345,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="K318" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11315,29 +11373,29 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>104</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="K319" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11352,7 +11410,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11361,20 +11419,20 @@
         <v>104</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="K320" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>371</v>
+        <v>170</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11389,25 +11447,25 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>19</v>
       </c>
       <c t="s" r="K321" s="7">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
@@ -11426,7 +11484,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11438,17 +11496,17 @@
         <v>58</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="K322" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11478,7 +11536,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11490,14 +11548,16 @@
         <v>108</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>109</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
-      <c r="M324" s="7"/>
+      <c t="s" r="M324" s="7">
+        <v>377</v>
+      </c>
     </row>
     <row r="325" ht="15" customHeight="1">
       <c t="s" r="A325" s="6">
@@ -11511,7 +11571,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11523,7 +11583,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>77</v>
@@ -11544,7 +11604,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11556,10 +11616,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11577,7 +11637,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11589,10 +11649,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11610,7 +11670,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11619,13 +11679,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>173</v>
+        <v>246</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11643,19 +11703,19 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>69</v>
@@ -11691,7 +11751,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11700,13 +11760,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11724,13 +11784,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
@@ -11739,7 +11799,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11757,7 +11817,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11769,10 +11829,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11790,7 +11850,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11805,7 +11865,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11838,7 +11898,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11850,15 +11910,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -11873,7 +11933,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11885,7 +11945,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>81</v>
@@ -11906,7 +11966,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11918,7 +11978,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>38</v>
@@ -11939,7 +11999,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11951,10 +12011,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11972,7 +12032,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11981,13 +12041,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12005,13 +12065,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>58</v>
@@ -12020,7 +12080,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12053,7 +12113,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12062,7 +12122,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>95</v>
@@ -12086,22 +12146,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12119,7 +12179,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12128,13 +12188,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12152,22 +12212,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12200,7 +12260,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12209,13 +12269,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12235,13 +12295,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>58</v>
@@ -12250,11 +12310,13 @@
         <v>18</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
-      <c r="M349" s="7"/>
+      <c t="s" r="M349" s="7">
+        <v>390</v>
+      </c>
     </row>
     <row r="350" ht="15" customHeight="1">
       <c t="s" r="A350" s="6">
@@ -12268,7 +12330,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12280,7 +12342,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>81</v>
@@ -12301,7 +12363,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12313,7 +12375,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>97</v>
@@ -12334,7 +12396,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12346,10 +12408,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12367,7 +12429,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12382,7 +12444,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12400,7 +12462,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12409,13 +12471,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12448,7 +12510,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12460,7 +12522,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>79</v>
@@ -12468,7 +12530,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12483,7 +12545,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12495,10 +12557,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12516,7 +12578,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12528,10 +12590,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12549,7 +12611,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12582,7 +12644,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12594,10 +12656,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12615,7 +12677,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12627,10 +12689,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>175</v>
+        <v>395</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12663,7 +12725,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12675,15 +12737,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12698,7 +12760,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12710,10 +12772,10 @@
         <v>111</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12731,7 +12793,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12743,7 +12805,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>115</v>
@@ -12764,7 +12826,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12776,10 +12838,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12812,7 +12874,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12824,7 +12886,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>30</v>
@@ -12832,7 +12894,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -12847,7 +12909,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12867,7 +12929,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -12882,7 +12944,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12894,7 +12956,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>76</v>
@@ -12915,7 +12977,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12930,7 +12992,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12941,14 +13003,14 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>453</v>
+        <v>145</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12957,13 +13019,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>371</v>
+        <v>321</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12974,29 +13036,29 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>58</v>
+        <v>403</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13007,29 +13069,29 @@
         <v>13</v>
       </c>
       <c r="B374" s="7">
-        <v>519</v>
+        <v>263</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>14</v>
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>58</v>
+        <v>403</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>59</v>
+        <v>246</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13040,29 +13102,29 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>522</v>
+        <v>168</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>194</v>
+        <v>395</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13095,7 +13157,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13107,15 +13169,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13130,7 +13192,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13142,15 +13204,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13165,7 +13227,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13182,9 +13244,13 @@
       <c t="s" r="J379" s="7">
         <v>36</v>
       </c>
-      <c r="K379" s="7"/>
+      <c t="s" r="K379" s="7">
+        <v>120</v>
+      </c>
       <c r="L379" s="7"/>
-      <c r="M379" s="7"/>
+      <c t="s" r="M379" s="7">
+        <v>243</v>
+      </c>
     </row>
     <row r="380" ht="15" customHeight="1">
       <c t="s" r="A380" s="6">
@@ -13198,7 +13264,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13210,14 +13276,18 @@
         <v>58</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>319</v>
-      </c>
-      <c r="K380" s="7"/>
+        <v>324</v>
+      </c>
+      <c t="s" r="K380" s="7">
+        <v>95</v>
+      </c>
       <c r="L380" s="7"/>
-      <c r="M380" s="7"/>
+      <c t="s" r="M380" s="7">
+        <v>80</v>
+      </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
@@ -13231,7 +13301,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13240,17 +13310,21 @@
         <v>58</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>371</v>
+        <v>170</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>141</v>
-      </c>
-      <c r="K381" s="7"/>
+        <v>143</v>
+      </c>
+      <c t="s" r="K381" s="7">
+        <v>97</v>
+      </c>
       <c r="L381" s="7"/>
-      <c r="M381" s="7"/>
+      <c t="s" r="M381" s="7">
+        <v>206</v>
+      </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
       <c t="s" r="A382" s="6">
@@ -13264,26 +13338,30 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>214</v>
-      </c>
-      <c r="K382" s="7"/>
+        <v>213</v>
+      </c>
+      <c t="s" r="K382" s="7">
+        <v>68</v>
+      </c>
       <c r="L382" s="7"/>
-      <c r="M382" s="7"/>
+      <c t="s" r="M382" s="7">
+        <v>266</v>
+      </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
       <c t="s" r="A383" s="6">
@@ -13297,7 +13375,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13306,13 +13384,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13330,22 +13408,22 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13378,7 +13456,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13390,10 +13468,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13411,7 +13489,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13426,7 +13504,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>371</v>
+        <v>170</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13444,7 +13522,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13456,7 +13534,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>25</v>
@@ -13477,7 +13555,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13492,7 +13570,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13525,7 +13603,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13534,10 +13612,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>48</v>
@@ -13545,7 +13623,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13560,13 +13638,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>58</v>
@@ -13593,7 +13671,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13602,10 +13680,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>72</v>
@@ -13641,7 +13719,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13656,11 +13734,13 @@
         <v>107</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
-      <c r="M395" s="7"/>
+      <c t="s" r="M395" s="7">
+        <v>132</v>
+      </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
       <c t="s" r="A396" s="6">
@@ -13674,7 +13754,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13686,7 +13766,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>82</v>
@@ -13707,7 +13787,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13755,7 +13835,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13764,18 +13844,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>410</v>
+        <v>374</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -13790,19 +13870,19 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>19</v>
@@ -13823,7 +13903,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -13835,10 +13915,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13856,7 +13936,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -13868,10 +13948,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13904,7 +13984,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13913,20 +13993,20 @@
         <v>74</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c t="s" r="K404" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>268</v>
+        <v>421</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -13941,13 +14021,13 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>74</v>
@@ -13956,14 +14036,14 @@
         <v>38</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c t="s" r="K405" s="7">
         <v>114</v>
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -13993,7 +14073,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -14002,20 +14082,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="K407" s="7">
-        <v>208</v>
+        <v>40</v>
       </c>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>355</v>
+        <v>93</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14041,11 +14121,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C409" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -14054,10 +14134,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>48</v>
@@ -14067,7 +14147,7 @@
       </c>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>169</v>
+        <v>321</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14078,33 +14158,33 @@
         <v>5806</v>
       </c>
       <c t="s" r="C410" s="7">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>102</v>
       </c>
       <c t="s" r="K410" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14134,29 +14214,29 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="K412" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>141</v>
+        <v>428</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14186,7 +14266,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14195,13 +14275,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14219,22 +14299,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14267,7 +14347,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14282,12 +14362,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -14302,7 +14382,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14314,7 +14394,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>85</v>
@@ -14335,7 +14415,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -14347,10 +14427,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14368,7 +14448,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14380,10 +14460,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14401,7 +14481,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14413,7 +14493,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>43</v>
@@ -14449,7 +14529,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14458,13 +14538,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14482,22 +14562,22 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14505,7 +14585,7 @@
     </row>
     <row r="425" ht="16.5" customHeight="1">
       <c t="s" r="A425" s="9">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B425" s="9"/>
       <c r="C425" s="9"/>
@@ -14525,7 +14605,7 @@
     <row r="426" ht="65.25" customHeight="1"/>
     <row r="427" ht="16.5" customHeight="1">
       <c t="s" r="A427" s="10">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B427" s="10"/>
       <c r="C427" s="10"/>
@@ -14538,7 +14618,7 @@
       <c r="J427" s="10"/>
       <c r="K427" s="10"/>
       <c t="s" r="L427" s="11">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="M427" s="11"/>
       <c r="N427" s="11"/>
